--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -484,11 +484,11 @@
         <v>0.99</v>
       </c>
       <c r="J2">
-        <v>0.75</v>
+        <v>0.99</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N2">
@@ -546,7 +546,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.714</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -557,11 +557,11 @@
         <v>0.601</v>
       </c>
       <c r="J3">
-        <v>0.648</v>
+        <v>0.782</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N3">
@@ -605,21 +605,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>ES51</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G4">
-        <v>0.668</v>
+        <v>0.652</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -627,34 +627,34 @@
         </is>
       </c>
       <c r="I4">
-        <v>0.6919999999999999</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J4">
-        <v>0.493</v>
+        <v>0.767</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N4">
-        <v>0.694</v>
+        <v>0.717</v>
       </c>
       <c r="O4">
-        <v>0.921</v>
+        <v>0.338</v>
       </c>
       <c r="P4">
-        <v>0.463</v>
+        <v>0.619</v>
       </c>
       <c r="Q4">
         <v>0.378</v>
@@ -678,21 +678,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G5">
-        <v>0.647</v>
+        <v>0.62</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -700,34 +700,34 @@
         </is>
       </c>
       <c r="I5">
-        <v>0.5580000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J5">
-        <v>0.574</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N5">
-        <v>0.717</v>
+        <v>0.694</v>
       </c>
       <c r="O5">
-        <v>0.338</v>
+        <v>0.921</v>
       </c>
       <c r="P5">
-        <v>0.619</v>
+        <v>0.463</v>
       </c>
       <c r="Q5">
         <v>0.378</v>
@@ -765,7 +765,7 @@
         </is>
       </c>
       <c r="G6">
-        <v>0.646</v>
+        <v>0.601</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>0.508</v>
       </c>
       <c r="J6">
-        <v>0.629</v>
+        <v>0.718</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N6">
@@ -863,7 +863,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N7">
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.049</v>
+        <v>0.026</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -922,11 +922,11 @@
         <v>0.02</v>
       </c>
       <c r="J8">
-        <v>0.128</v>
+        <v>0.055</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N8">
@@ -984,7 +984,7 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.066</v>
+        <v>0.047</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -995,7 +995,7 @@
         <v>0.065</v>
       </c>
       <c r="J9">
-        <v>0.066</v>
+        <v>0.044</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N9">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="G10">
-        <v>0.07099999999999999</v>
+        <v>0.059</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>0.01</v>
       </c>
       <c r="J10">
-        <v>0.47</v>
+        <v>0.418</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N10">
@@ -1116,21 +1116,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>AT11</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Valle d’Aosta/Vallée d’Aoste</t>
+          <t>Burgenland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G11">
-        <v>0.07199999999999999</v>
+        <v>0.062</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="I11">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="J11">
-        <v>0.476</v>
+        <v>0.206</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1155,17 +1155,17 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N11">
-        <v>0.011</v>
+        <v>0.034</v>
       </c>
       <c r="O11">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="P11">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="Q11">
         <v>0.378</v>
@@ -1189,17 +1189,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ES51</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G12">
@@ -1211,10 +1211,10 @@
         </is>
       </c>
       <c r="I12">
-        <v>0.93</v>
+        <v>0.967</v>
       </c>
       <c r="J12">
-        <v>0.697</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1223,22 +1223,22 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N12">
-        <v>0.93</v>
+        <v>0.956</v>
       </c>
       <c r="O12">
-        <v>0.679</v>
+        <v>0.445</v>
       </c>
       <c r="P12">
-        <v>0.6909999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Q12">
         <v>0.132</v>
@@ -1276,7 +1276,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.977</v>
+        <v>0.976</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>0.99</v>
       </c>
       <c r="J13">
-        <v>0.638</v>
+        <v>0.658</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1335,21 +1335,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>ITH5</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wielkopolskie</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G14">
-        <v>0.965</v>
+        <v>0.967</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1357,10 +1357,10 @@
         </is>
       </c>
       <c r="I14">
-        <v>0.929</v>
+        <v>0.93</v>
       </c>
       <c r="J14">
-        <v>0.664</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1369,22 +1369,22 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N14">
-        <v>0.724</v>
+        <v>0.93</v>
       </c>
       <c r="O14">
-        <v>0.99</v>
+        <v>0.679</v>
       </c>
       <c r="P14">
-        <v>0.584</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="Q14">
         <v>0.132</v>
@@ -1422,7 +1422,7 @@
         </is>
       </c>
       <c r="G15">
-        <v>0.9370000000000001</v>
+        <v>0.961</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1433,11 +1433,11 @@
         <v>0.744</v>
       </c>
       <c r="J15">
-        <v>0.783</v>
+        <v>0.851</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N15">
@@ -1481,21 +1481,21 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>PL41</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Wielkopolskie</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G16">
-        <v>0.923</v>
+        <v>0.949</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1503,10 +1503,10 @@
         </is>
       </c>
       <c r="I16">
-        <v>0.967</v>
+        <v>0.929</v>
       </c>
       <c r="J16">
-        <v>0.585</v>
+        <v>0.665</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1515,22 +1515,22 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N16">
-        <v>0.956</v>
+        <v>0.724</v>
       </c>
       <c r="O16">
-        <v>0.445</v>
+        <v>0.99</v>
       </c>
       <c r="P16">
-        <v>0.99</v>
+        <v>0.584</v>
       </c>
       <c r="Q16">
         <v>0.132</v>
@@ -1554,17 +1554,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>ES21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>País Vasco</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G17">
@@ -1576,34 +1576,34 @@
         </is>
       </c>
       <c r="I17">
-        <v>0.102</v>
+        <v>0.137</v>
       </c>
       <c r="J17">
         <v>0.01</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N17">
-        <v>0.091</v>
+        <v>0.135</v>
       </c>
       <c r="O17">
-        <v>0.055</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="P17">
-        <v>0.118</v>
+        <v>0.145</v>
       </c>
       <c r="Q17">
         <v>0.132</v>
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Mellersta Norrland</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1641,7 +1641,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1649,14 +1649,14 @@
         </is>
       </c>
       <c r="I18">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="J18">
-        <v>0.066</v>
+        <v>0.19</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N18">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="O18">
         <v>0.01</v>
       </c>
       <c r="P18">
-        <v>0.028</v>
+        <v>0.019</v>
       </c>
       <c r="Q18">
         <v>0.132</v>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1714,7 +1714,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.039</v>
+        <v>0.024</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1722,10 +1722,10 @@
         </is>
       </c>
       <c r="I19">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="J19">
-        <v>0.298</v>
+        <v>0.136</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1743,13 +1743,13 @@
         </is>
       </c>
       <c r="N19">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="O19">
         <v>0.01</v>
       </c>
       <c r="P19">
-        <v>0.019</v>
+        <v>0.028</v>
       </c>
       <c r="Q19">
         <v>0.132</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.059</v>
+        <v>0.029</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1798,11 +1798,11 @@
         <v>0.032</v>
       </c>
       <c r="J20">
-        <v>0.157</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1846,21 +1846,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Valle d’Aosta/Vallée d’Aoste</t>
+          <t>Notio Aigaio</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G21">
-        <v>0.073</v>
+        <v>0.061</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1868,10 +1868,10 @@
         </is>
       </c>
       <c r="I21">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="J21">
-        <v>0.505</v>
+        <v>0.537</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1885,17 +1885,17 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N21">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="O21">
-        <v>0.019</v>
+        <v>0.016</v>
       </c>
       <c r="P21">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="Q21">
         <v>0.132</v>
@@ -1944,11 +1944,11 @@
         <v>0.99</v>
       </c>
       <c r="J22">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2006,22 +2006,22 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.802</v>
+        <v>0.696</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I23">
         <v>0.778</v>
       </c>
       <c r="J23">
-        <v>0.6860000000000001</v>
+        <v>0.624</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N23">
@@ -2065,21 +2065,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G24">
-        <v>0.6909999999999999</v>
+        <v>0.663</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2087,14 +2087,14 @@
         </is>
       </c>
       <c r="I24">
-        <v>0.606</v>
+        <v>0.5580000000000001</v>
       </c>
       <c r="J24">
-        <v>0.655</v>
+        <v>0.791</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2104,17 +2104,17 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N24">
-        <v>0.606</v>
+        <v>0.597</v>
       </c>
       <c r="O24">
-        <v>0.606</v>
+        <v>0.586</v>
       </c>
       <c r="P24">
-        <v>0.606</v>
+        <v>0.49</v>
       </c>
       <c r="Q24">
         <v>0.01</v>
@@ -2138,32 +2138,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G25">
-        <v>0.636</v>
+        <v>0.595</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I25">
-        <v>0.5580000000000001</v>
+        <v>0.606</v>
       </c>
       <c r="J25">
-        <v>0.604</v>
+        <v>0.586</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2177,17 +2177,17 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N25">
-        <v>0.597</v>
+        <v>0.606</v>
       </c>
       <c r="O25">
-        <v>0.586</v>
+        <v>0.606</v>
       </c>
       <c r="P25">
-        <v>0.49</v>
+        <v>0.606</v>
       </c>
       <c r="Q25">
         <v>0.01</v>
@@ -2225,7 +2225,7 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.571</v>
+        <v>0.512</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2236,7 +2236,7 @@
         <v>0.33</v>
       </c>
       <c r="J26">
-        <v>0.823</v>
+        <v>0.799</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N27">
@@ -2357,21 +2357,21 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DK02</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sjælland</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G28">
-        <v>0.049</v>
+        <v>0.035</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2379,31 +2379,31 @@
         </is>
       </c>
       <c r="I28">
+        <v>0.013</v>
+      </c>
+      <c r="J28">
+        <v>0.105</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Scope 2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N28">
         <v>0.012</v>
       </c>
-      <c r="J28">
-        <v>0.198</v>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Vulnerability-driven</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Scope 2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N28">
-        <v>0.011</v>
-      </c>
       <c r="O28">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="P28">
         <v>0.012</v>
@@ -2430,21 +2430,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G29">
-        <v>0.053</v>
+        <v>0.038</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2452,14 +2452,14 @@
         </is>
       </c>
       <c r="I29">
-        <v>0.015</v>
+        <v>0.014</v>
       </c>
       <c r="J29">
-        <v>0.175</v>
+        <v>0.113</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2473,13 +2473,13 @@
         </is>
       </c>
       <c r="N29">
-        <v>0.015</v>
+        <v>0.013</v>
       </c>
       <c r="O29">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="P29">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="Q29">
         <v>0.01</v>
@@ -2503,21 +2503,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>DK02</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Sjælland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G30">
-        <v>0.056</v>
+        <v>0.038</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2525,10 +2525,10 @@
         </is>
       </c>
       <c r="I30">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="J30">
-        <v>0.164</v>
+        <v>0.139</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2542,17 +2542,17 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N30">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="O30">
-        <v>0.023</v>
+        <v>0.012</v>
       </c>
       <c r="P30">
-        <v>0.013</v>
+        <v>0.012</v>
       </c>
       <c r="Q30">
         <v>0.01</v>
@@ -2576,21 +2576,21 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>BE34</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Prov. Luxembourg (BE)</t>
+          <t>Zeeland</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G31">
-        <v>0.06</v>
+        <v>0.038</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2598,10 +2598,10 @@
         </is>
       </c>
       <c r="I31">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J31">
-        <v>0.337</v>
+        <v>0.122</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2619,13 +2619,13 @@
         </is>
       </c>
       <c r="N31">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="O31">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="P31">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q31">
         <v>0.01</v>
@@ -2674,11 +2674,11 @@
         <v>0.99</v>
       </c>
       <c r="J32">
-        <v>0.8090000000000001</v>
+        <v>0.912</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0.772</v>
+        <v>0.748</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2747,11 +2747,11 @@
         <v>0.669</v>
       </c>
       <c r="J33">
-        <v>0.734</v>
+        <v>0.776</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N33">
@@ -2809,7 +2809,7 @@
         </is>
       </c>
       <c r="G34">
-        <v>0.663</v>
+        <v>0.644</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2820,11 +2820,11 @@
         <v>0.661</v>
       </c>
       <c r="J34">
-        <v>0.55</v>
+        <v>0.587</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N34">
@@ -2882,7 +2882,7 @@
         </is>
       </c>
       <c r="G35">
-        <v>0.594</v>
+        <v>0.556</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2893,7 +2893,7 @@
         <v>0.604</v>
       </c>
       <c r="J35">
-        <v>0.486</v>
+        <v>0.48</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N35">
@@ -2955,7 +2955,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.58</v>
+        <v>0.543</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>0.395</v>
       </c>
       <c r="J36">
-        <v>0.71</v>
+        <v>0.702</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N36">
@@ -3087,21 +3087,21 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>IE04</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Northern and Western</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G38">
-        <v>0.049</v>
+        <v>0.02</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3109,14 +3109,14 @@
         </is>
       </c>
       <c r="I38">
-        <v>0.021</v>
+        <v>0.031</v>
       </c>
       <c r="J38">
-        <v>0.147</v>
+        <v>0.029</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3126,17 +3126,17 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N38">
-        <v>0.016</v>
+        <v>0.014</v>
       </c>
       <c r="O38">
-        <v>0.016</v>
+        <v>0.028</v>
       </c>
       <c r="P38">
-        <v>0.03</v>
+        <v>0.047</v>
       </c>
       <c r="Q38">
         <v>0.255</v>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DK02</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sjælland</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3174,7 +3174,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>0.07199999999999999</v>
+        <v>0.043</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3182,10 +3182,10 @@
         </is>
       </c>
       <c r="I39">
-        <v>0.015</v>
+        <v>0.021</v>
       </c>
       <c r="J39">
-        <v>0.377</v>
+        <v>0.129</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3199,17 +3199,17 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N39">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="O39">
-        <v>0.013</v>
+        <v>0.016</v>
       </c>
       <c r="P39">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="Q39">
         <v>0.255</v>
@@ -3247,7 +3247,7 @@
         </is>
       </c>
       <c r="G40">
-        <v>0.073</v>
+        <v>0.05</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>0.01</v>
       </c>
       <c r="J40">
-        <v>0.598</v>
+        <v>0.344</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3272,7 +3272,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N40">
@@ -3306,21 +3306,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>BE31</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Prov. Brabant Wallon</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G41">
-        <v>0.077</v>
+        <v>0.053</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.016</v>
+        <v>0.022</v>
       </c>
       <c r="J41">
-        <v>0.413</v>
+        <v>0.175</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -3345,17 +3345,17 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N41">
-        <v>0.013</v>
+        <v>0.02</v>
       </c>
       <c r="O41">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="P41">
-        <v>0.017</v>
+        <v>0.025</v>
       </c>
       <c r="Q41">
         <v>0.255</v>
@@ -3379,17 +3379,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ES51</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G42">
@@ -3401,34 +3401,34 @@
         </is>
       </c>
       <c r="I42">
-        <v>0.99</v>
+        <v>0.804</v>
       </c>
       <c r="J42">
-        <v>0.676</v>
+        <v>0.905</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N42">
-        <v>0.99</v>
+        <v>0.886</v>
       </c>
       <c r="O42">
-        <v>0.571</v>
+        <v>0.246</v>
       </c>
       <c r="P42">
-        <v>0.99</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="Q42">
         <v>0.745</v>
@@ -3452,21 +3452,21 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G43">
-        <v>0.925</v>
+        <v>0.98</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3474,34 +3474,34 @@
         </is>
       </c>
       <c r="I43">
-        <v>0.804</v>
+        <v>0.99</v>
       </c>
       <c r="J43">
-        <v>0.727</v>
+        <v>0.72</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N43">
-        <v>0.886</v>
+        <v>0.99</v>
       </c>
       <c r="O43">
-        <v>0.246</v>
+        <v>0.571</v>
       </c>
       <c r="P43">
-        <v>0.9399999999999999</v>
+        <v>0.99</v>
       </c>
       <c r="Q43">
         <v>0.745</v>
@@ -3525,56 +3525,56 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Attiki</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G44">
-        <v>0.73</v>
+        <v>0.896</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I44">
-        <v>0.397</v>
+        <v>0.778</v>
       </c>
       <c r="J44">
-        <v>0.919</v>
+        <v>0.767</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N44">
-        <v>0.464</v>
+        <v>0.635</v>
       </c>
       <c r="O44">
-        <v>0.064</v>
+        <v>0.99</v>
       </c>
       <c r="P44">
-        <v>0.499</v>
+        <v>0.38</v>
       </c>
       <c r="Q44">
         <v>0.745</v>
@@ -3598,56 +3598,56 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>DEA1</t>
+          <t>BE21</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Prov. Antwerpen</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G45">
-        <v>0.681</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.767</v>
+        <v>0.536</v>
       </c>
       <c r="J45">
-        <v>0.414</v>
+        <v>0.913</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>Policy Pressure</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N45">
-        <v>0.626</v>
+        <v>0.617</v>
       </c>
       <c r="O45">
-        <v>0.977</v>
+        <v>0.408</v>
       </c>
       <c r="P45">
-        <v>0.375</v>
+        <v>0.358</v>
       </c>
       <c r="Q45">
         <v>0.745</v>
@@ -3671,21 +3671,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BE21</t>
+          <t>DEA1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prov. Antwerpen</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G46">
-        <v>0.668</v>
+        <v>0.774</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3693,34 +3693,34 @@
         </is>
       </c>
       <c r="I46">
-        <v>0.536</v>
+        <v>0.767</v>
       </c>
       <c r="J46">
-        <v>0.57</v>
+        <v>0.582</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N46">
-        <v>0.617</v>
+        <v>0.626</v>
       </c>
       <c r="O46">
-        <v>0.408</v>
+        <v>0.977</v>
       </c>
       <c r="P46">
-        <v>0.358</v>
+        <v>0.375</v>
       </c>
       <c r="Q46">
         <v>0.745</v>
@@ -3744,17 +3744,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DK04</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G47">
@@ -3766,7 +3766,7 @@
         </is>
       </c>
       <c r="I47">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="J47">
         <v>0.01</v>
@@ -3783,17 +3783,17 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N47">
-        <v>0.015</v>
+        <v>0.023</v>
       </c>
       <c r="O47">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P47">
-        <v>0.015</v>
+        <v>0.024</v>
       </c>
       <c r="Q47">
         <v>0.745</v>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DEB2</t>
+          <t>DE14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trier</t>
+          <t>Tübingen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.03</v>
+        <v>0.027</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3839,10 +3839,10 @@
         </is>
       </c>
       <c r="I48">
-        <v>0.012</v>
+        <v>0.064</v>
       </c>
       <c r="J48">
-        <v>0.065</v>
+        <v>0.014</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3860,13 +3860,13 @@
         </is>
       </c>
       <c r="N48">
-        <v>0.012</v>
+        <v>0.055</v>
       </c>
       <c r="O48">
-        <v>0.013</v>
+        <v>0.08</v>
       </c>
       <c r="P48">
-        <v>0.011</v>
+        <v>0.036</v>
       </c>
       <c r="Q48">
         <v>0.745</v>
@@ -3890,21 +3890,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nordjylland</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G49">
-        <v>0.053</v>
+        <v>0.028</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3915,11 +3915,11 @@
         <v>0.014</v>
       </c>
       <c r="J49">
-        <v>0.165</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -3929,17 +3929,17 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N49">
-        <v>0.013</v>
+        <v>0.015</v>
       </c>
       <c r="O49">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="P49">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="Q49">
         <v>0.745</v>
@@ -3963,21 +3963,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>DK05</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Valle d’Aosta/Vallée d’Aoste</t>
+          <t>Nordjylland</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G50">
-        <v>0.057</v>
+        <v>0.029</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3985,14 +3985,14 @@
         </is>
       </c>
       <c r="I50">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J50">
-        <v>0.255</v>
+        <v>0.075</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4002,17 +4002,17 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N50">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="O50">
-        <v>0.01</v>
+        <v>0.013</v>
       </c>
       <c r="P50">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="Q50">
         <v>0.745</v>
@@ -4036,21 +4036,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>AT34</t>
+          <t>DEB2</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Vorarlberg</t>
+          <t>Trier</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G51">
-        <v>0.065</v>
+        <v>0.034</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4058,14 +4058,14 @@
         </is>
       </c>
       <c r="I51">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="J51">
-        <v>0.18</v>
+        <v>0.107</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4075,17 +4075,17 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N51">
-        <v>0.019</v>
+        <v>0.012</v>
       </c>
       <c r="O51">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="P51">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="Q51">
         <v>0.745</v>
@@ -4134,7 +4134,7 @@
         <v>0.99</v>
       </c>
       <c r="J52">
-        <v>0.695</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N52">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.582</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>0.391</v>
       </c>
       <c r="J53">
-        <v>0.613</v>
+        <v>0.676</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N53">
@@ -4255,21 +4255,21 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>IE05</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G54">
-        <v>0.577</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4277,10 +4277,10 @@
         </is>
       </c>
       <c r="I54">
-        <v>0.405</v>
+        <v>0.311</v>
       </c>
       <c r="J54">
-        <v>0.583</v>
+        <v>0.834</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4289,22 +4289,22 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N54">
-        <v>0.405</v>
+        <v>0.228</v>
       </c>
       <c r="O54">
-        <v>0.405</v>
+        <v>0.115</v>
       </c>
       <c r="P54">
-        <v>0.405</v>
+        <v>0.59</v>
       </c>
       <c r="Q54">
         <v>0.132</v>
@@ -4328,21 +4328,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G55">
-        <v>0.55</v>
+        <v>0.541</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4350,14 +4350,14 @@
         </is>
       </c>
       <c r="I55">
-        <v>0.428</v>
+        <v>0.405</v>
       </c>
       <c r="J55">
-        <v>0.501</v>
+        <v>0.595</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4367,17 +4367,17 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N55">
-        <v>0.587</v>
+        <v>0.405</v>
       </c>
       <c r="O55">
-        <v>0.232</v>
+        <v>0.405</v>
       </c>
       <c r="P55">
-        <v>0.465</v>
+        <v>0.405</v>
       </c>
       <c r="Q55">
         <v>0.132</v>
@@ -4401,21 +4401,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G56">
-        <v>0.532</v>
+        <v>0.524</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="I56">
-        <v>0.321</v>
+        <v>0.302</v>
       </c>
       <c r="J56">
-        <v>0.625</v>
+        <v>0.748</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4435,22 +4435,22 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N56">
-        <v>0.321</v>
+        <v>0.222</v>
       </c>
       <c r="O56">
-        <v>0.321</v>
+        <v>0.112</v>
       </c>
       <c r="P56">
-        <v>0.321</v>
+        <v>0.573</v>
       </c>
       <c r="Q56">
         <v>0.132</v>
@@ -4547,12 +4547,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Norra Mellansverige</t>
+          <t>Mellersta Norrland</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4561,7 +4561,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>0.046</v>
+        <v>0.022</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4569,14 +4569,14 @@
         </is>
       </c>
       <c r="I58">
-        <v>0.014</v>
+        <v>0.013</v>
       </c>
       <c r="J58">
-        <v>0.129</v>
+        <v>0.044</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4593,10 +4593,10 @@
         <v>0.012</v>
       </c>
       <c r="O58">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="P58">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="Q58">
         <v>0.132</v>
@@ -4620,12 +4620,12 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE31</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Norra Mellansverige</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4634,7 +4634,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>0.05</v>
+        <v>0.034</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4642,14 +4642,14 @@
         </is>
       </c>
       <c r="I59">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="J59">
-        <v>0.166</v>
+        <v>0.083</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4659,17 +4659,17 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N59">
         <v>0.012</v>
       </c>
       <c r="O59">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="P59">
-        <v>0.017</v>
+        <v>0.019</v>
       </c>
       <c r="Q59">
         <v>0.132</v>
@@ -4693,21 +4693,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DE50</t>
+          <t>DK05</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bremen</t>
+          <t>Nordjylland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G60">
-        <v>0.061</v>
+        <v>0.056</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4715,10 +4715,10 @@
         </is>
       </c>
       <c r="I60">
-        <v>0.014</v>
+        <v>0.017</v>
       </c>
       <c r="J60">
-        <v>0.22</v>
+        <v>0.178</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4736,13 +4736,13 @@
         </is>
       </c>
       <c r="N60">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="O60">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="P60">
-        <v>0.013</v>
+        <v>0.023</v>
       </c>
       <c r="Q60">
         <v>0.132</v>
@@ -4766,21 +4766,21 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>AT21</t>
+          <t>DK04</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kärnten</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G61">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4788,14 +4788,14 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.014</v>
+        <v>0.029</v>
       </c>
       <c r="J61">
-        <v>0.248</v>
+        <v>0.114</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -4809,13 +4809,13 @@
         </is>
       </c>
       <c r="N61">
-        <v>0.013</v>
+        <v>0.024</v>
       </c>
       <c r="O61">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="P61">
-        <v>0.017</v>
+        <v>0.046</v>
       </c>
       <c r="Q61">
         <v>0.132</v>
@@ -4864,11 +4864,11 @@
         <v>0.99</v>
       </c>
       <c r="J62">
-        <v>0.799</v>
+        <v>0.99</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -4926,18 +4926,18 @@
         </is>
       </c>
       <c r="G63">
-        <v>0.867</v>
+        <v>0.773</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I63">
         <v>0.869</v>
       </c>
       <c r="J63">
-        <v>0.699</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N63">
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>0.787</v>
+        <v>0.6889999999999999</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5010,7 +5010,7 @@
         <v>0.767</v>
       </c>
       <c r="J64">
-        <v>0.653</v>
+        <v>0.622</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N64">
@@ -5072,7 +5072,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>0.786</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>0.74</v>
       </c>
       <c r="J65">
-        <v>0.675</v>
+        <v>0.643</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N65">
@@ -5131,21 +5131,21 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Świętokrzyskie</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G66">
-        <v>0.673</v>
+        <v>0.616</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5153,14 +5153,14 @@
         </is>
       </c>
       <c r="I66">
-        <v>0.649</v>
+        <v>0.442</v>
       </c>
       <c r="J66">
-        <v>0.5649999999999999</v>
+        <v>0.867</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5170,17 +5170,17 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N66">
-        <v>0.506</v>
+        <v>0.252</v>
       </c>
       <c r="O66">
-        <v>0.602</v>
+        <v>0.592</v>
       </c>
       <c r="P66">
-        <v>0.527</v>
+        <v>0.272</v>
       </c>
       <c r="Q66">
         <v>0.99</v>
@@ -5204,17 +5204,17 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G67">
@@ -5226,7 +5226,7 @@
         </is>
       </c>
       <c r="I67">
-        <v>0.016</v>
+        <v>0.026</v>
       </c>
       <c r="J67">
         <v>0.01</v>
@@ -5243,17 +5243,17 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N67">
-        <v>0.021</v>
+        <v>0.025</v>
       </c>
       <c r="O67">
-        <v>0.01</v>
+        <v>0.034</v>
       </c>
       <c r="P67">
-        <v>0.019</v>
+        <v>0.017</v>
       </c>
       <c r="Q67">
         <v>0.99</v>
@@ -5277,56 +5277,56 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>AT34</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Vorarlberg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G68">
+        <v>0.023</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="I68">
+        <v>0.031</v>
+      </c>
+      <c r="J68">
+        <v>0.028</v>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Policy Pressure</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N68">
+        <v>0.036</v>
+      </c>
+      <c r="O68">
         <v>0.022</v>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>Very Low</t>
-        </is>
-      </c>
-      <c r="I68">
-        <v>0.033</v>
-      </c>
-      <c r="J68">
-        <v>0.016</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>Policy Pressure</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N68">
-        <v>0.041</v>
-      </c>
-      <c r="O68">
-        <v>0.024</v>
-      </c>
       <c r="P68">
-        <v>0.028</v>
+        <v>0.03</v>
       </c>
       <c r="Q68">
         <v>0.99</v>
@@ -5350,56 +5350,56 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DE60</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G69">
+        <v>0.027</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="I69">
+        <v>0.033</v>
+      </c>
+      <c r="J69">
+        <v>0.034</v>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Policy Pressure</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Institutions</t>
+        </is>
+      </c>
+      <c r="N69">
         <v>0.041</v>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>Very Low</t>
-        </is>
-      </c>
-      <c r="I69">
-        <v>0.026</v>
-      </c>
-      <c r="J69">
-        <v>0.063</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>Policy Pressure</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N69">
-        <v>0.025</v>
-      </c>
       <c r="O69">
-        <v>0.034</v>
+        <v>0.024</v>
       </c>
       <c r="P69">
-        <v>0.017</v>
+        <v>0.028</v>
       </c>
       <c r="Q69">
         <v>0.99</v>
@@ -5423,21 +5423,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DE30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G70">
-        <v>0.065</v>
+        <v>0.032</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5445,14 +5445,14 @@
         </is>
       </c>
       <c r="I70">
-        <v>0.011</v>
+        <v>0.044</v>
       </c>
       <c r="J70">
-        <v>0.337</v>
+        <v>0.032</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5466,13 +5466,13 @@
         </is>
       </c>
       <c r="N70">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="O70">
-        <v>0.016</v>
+        <v>0.055</v>
       </c>
       <c r="P70">
-        <v>0.013</v>
+        <v>0.027</v>
       </c>
       <c r="Q70">
         <v>0.99</v>
@@ -5496,12 +5496,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="G71">
-        <v>0.065</v>
+        <v>0.032</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5518,14 +5518,14 @@
         </is>
       </c>
       <c r="I71">
-        <v>0.012</v>
+        <v>0.016</v>
       </c>
       <c r="J71">
-        <v>0.31</v>
+        <v>0.092</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="N71">
-        <v>0.017</v>
+        <v>0.021</v>
       </c>
       <c r="O71">
         <v>0.01</v>
       </c>
       <c r="P71">
-        <v>0.015</v>
+        <v>0.019</v>
       </c>
       <c r="Q71">
         <v>0.99</v>
@@ -5569,17 +5569,17 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>DEA5</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Arnsberg</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G72">
@@ -5591,10 +5591,10 @@
         </is>
       </c>
       <c r="I72">
-        <v>0.881</v>
+        <v>0.99</v>
       </c>
       <c r="J72">
-        <v>0.803</v>
+        <v>0.93</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5603,22 +5603,22 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N72">
-        <v>0.465</v>
+        <v>0.99</v>
       </c>
       <c r="O72">
-        <v>0.849</v>
+        <v>0.99</v>
       </c>
       <c r="P72">
-        <v>0.99</v>
+        <v>0.608</v>
       </c>
       <c r="Q72">
         <v>0.99</v>
@@ -5642,21 +5642,21 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DEA5</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G73">
-        <v>0.974</v>
+        <v>0.964</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5664,34 +5664,34 @@
         </is>
       </c>
       <c r="I73">
+        <v>0.881</v>
+      </c>
+      <c r="J73">
         <v>0.99</v>
       </c>
-      <c r="J73">
-        <v>0.6929999999999999</v>
-      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N73">
+        <v>0.465</v>
+      </c>
+      <c r="O73">
+        <v>0.849</v>
+      </c>
+      <c r="P73">
         <v>0.99</v>
-      </c>
-      <c r="O73">
-        <v>0.99</v>
-      </c>
-      <c r="P73">
-        <v>0.608</v>
       </c>
       <c r="Q73">
         <v>0.99</v>
@@ -5729,7 +5729,7 @@
         </is>
       </c>
       <c r="G74">
-        <v>0.847</v>
+        <v>0.871</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5740,11 +5740,11 @@
         <v>0.861</v>
       </c>
       <c r="J74">
-        <v>0.606</v>
+        <v>0.829</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N74">
@@ -5802,7 +5802,7 @@
         </is>
       </c>
       <c r="G75">
-        <v>0.591</v>
+        <v>0.556</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>0.44</v>
       </c>
       <c r="J75">
-        <v>0.59</v>
+        <v>0.66</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -5827,7 +5827,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N75">
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="G76">
-        <v>0.547</v>
+        <v>0.52</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>0.276</v>
       </c>
       <c r="J76">
-        <v>0.8120000000000001</v>
+        <v>0.921</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N76">
@@ -5934,17 +5934,17 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>AT13</t>
+          <t>LT01</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Wien</t>
+          <t>Sostinės regionas</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G77">
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="I77">
-        <v>0.06900000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="J77">
         <v>0.01</v>
@@ -5973,17 +5973,17 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N77">
-        <v>0.11</v>
+        <v>0.01</v>
       </c>
       <c r="O77">
-        <v>0.021</v>
+        <v>0.01</v>
       </c>
       <c r="P77">
-        <v>0.054</v>
+        <v>0.01</v>
       </c>
       <c r="Q77">
         <v>0.99</v>
@@ -6007,21 +6007,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>AT34</t>
+          <t>EE00</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vorarlberg</t>
+          <t>Eesti</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>EE</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.017</v>
+        <v>0.047</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6029,14 +6029,14 @@
         </is>
       </c>
       <c r="I78">
-        <v>0.061</v>
+        <v>0.011</v>
       </c>
       <c r="J78">
-        <v>0.017</v>
+        <v>0.187</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6046,17 +6046,17 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N78">
-        <v>0.095</v>
+        <v>0.01</v>
       </c>
       <c r="O78">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="P78">
-        <v>0.047</v>
+        <v>0.012</v>
       </c>
       <c r="Q78">
         <v>0.99</v>
@@ -6080,21 +6080,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Noord-Holland</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G79">
-        <v>0.023</v>
+        <v>0.051</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6102,14 +6102,14 @@
         </is>
       </c>
       <c r="I79">
-        <v>0.068</v>
+        <v>0.015</v>
       </c>
       <c r="J79">
-        <v>0.021</v>
+        <v>0.172</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6123,13 +6123,13 @@
         </is>
       </c>
       <c r="N79">
-        <v>0.083</v>
+        <v>0.011</v>
       </c>
       <c r="O79">
-        <v>0.059</v>
+        <v>0.013</v>
       </c>
       <c r="P79">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="Q79">
         <v>0.99</v>
@@ -6153,21 +6153,21 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>AT32</t>
+          <t>LT02</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Vidurio ir vakarų Lietuvos regionas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.031</v>
+        <v>0.055</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6175,14 +6175,14 @@
         </is>
       </c>
       <c r="I80">
-        <v>0.051</v>
+        <v>0.011</v>
       </c>
       <c r="J80">
-        <v>0.038</v>
+        <v>0.269</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6192,17 +6192,17 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N80">
-        <v>0.079</v>
+        <v>0.01</v>
       </c>
       <c r="O80">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="P80">
-        <v>0.04</v>
+        <v>0.011</v>
       </c>
       <c r="Q80">
         <v>0.99</v>
@@ -6226,21 +6226,21 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LT01</t>
+          <t>ES23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Sostinės regionas</t>
+          <t>La Rioja</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G81">
-        <v>0.032</v>
+        <v>0.058</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6248,10 +6248,10 @@
         </is>
       </c>
       <c r="I81">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J81">
-        <v>0.202</v>
+        <v>0.276</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6265,17 +6265,17 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N81">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="O81">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="P81">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="Q81">
         <v>0.99</v>
@@ -6324,11 +6324,11 @@
         <v>0.99</v>
       </c>
       <c r="J82">
-        <v>0.776</v>
+        <v>0.99</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6338,7 +6338,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N82">
@@ -6386,7 +6386,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>0.752</v>
+        <v>0.727</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>0.719</v>
       </c>
       <c r="J83">
-        <v>0.62</v>
+        <v>0.74</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6459,7 +6459,7 @@
         </is>
       </c>
       <c r="G84">
-        <v>0.712</v>
+        <v>0.699</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6470,11 +6470,11 @@
         <v>0.59</v>
       </c>
       <c r="J84">
-        <v>0.679</v>
+        <v>0.834</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -6484,7 +6484,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N84">
@@ -6532,7 +6532,7 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.6929999999999999</v>
+        <v>0.665</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6543,11 +6543,11 @@
         <v>0.577</v>
       </c>
       <c r="J85">
-        <v>0.657</v>
+        <v>0.773</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -6557,7 +6557,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N85">
@@ -6605,7 +6605,7 @@
         </is>
       </c>
       <c r="G86">
-        <v>0.573</v>
+        <v>0.551</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
         <v>0.46</v>
       </c>
       <c r="J86">
-        <v>0.5659999999999999</v>
+        <v>0.667</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6630,7 +6630,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N86">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -6751,42 +6751,42 @@
         </is>
       </c>
       <c r="G88">
+        <v>0.034</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="I88">
+        <v>0.031</v>
+      </c>
+      <c r="J88">
+        <v>0.055</v>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>Policy Pressure</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="N88">
+        <v>0.034</v>
+      </c>
+      <c r="O88">
+        <v>0.011</v>
+      </c>
+      <c r="P88">
         <v>0.048</v>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>Very Low</t>
-        </is>
-      </c>
-      <c r="I88">
-        <v>0.021</v>
-      </c>
-      <c r="J88">
-        <v>0.124</v>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>Vulnerability-driven</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>Policy Pressure</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="N88">
-        <v>0.022</v>
-      </c>
-      <c r="O88">
-        <v>0.01</v>
-      </c>
-      <c r="P88">
-        <v>0.031</v>
       </c>
       <c r="Q88">
         <v>0.132</v>
@@ -6810,21 +6810,21 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Corse</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G89">
-        <v>0.059</v>
+        <v>0.04</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6832,10 +6832,10 @@
         </is>
       </c>
       <c r="I89">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="J89">
-        <v>0.226</v>
+        <v>0.227</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6849,17 +6849,17 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N89">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="O89">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="P89">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="Q89">
         <v>0.132</v>
@@ -6883,21 +6883,21 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>AT11</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Burgenland</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G90">
-        <v>0.063</v>
+        <v>0.042</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6905,14 +6905,14 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.016</v>
+        <v>0.025</v>
       </c>
       <c r="J90">
-        <v>0.26</v>
+        <v>0.096</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -6922,17 +6922,17 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N90">
-        <v>0.014</v>
+        <v>0.026</v>
       </c>
       <c r="O90">
-        <v>0.014</v>
+        <v>0.025</v>
       </c>
       <c r="P90">
-        <v>0.02</v>
+        <v>0.025</v>
       </c>
       <c r="Q90">
         <v>0.132</v>
@@ -6956,21 +6956,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>BE31</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Prov. Brabant Wallon</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G91">
-        <v>0.064</v>
+        <v>0.043</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6978,34 +6978,34 @@
         </is>
       </c>
       <c r="I91">
+        <v>0.016</v>
+      </c>
+      <c r="J91">
+        <v>0.153</v>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Vulnerability-driven</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Policy Pressure</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N91">
+        <v>0.019</v>
+      </c>
+      <c r="O91">
+        <v>0.013</v>
+      </c>
+      <c r="P91">
         <v>0.017</v>
-      </c>
-      <c r="J91">
-        <v>0.245</v>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>Vulnerability-driven</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>Policy Pressure</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>Finance</t>
-        </is>
-      </c>
-      <c r="N91">
-        <v>0.018</v>
-      </c>
-      <c r="O91">
-        <v>0.01</v>
-      </c>
-      <c r="P91">
-        <v>0.024</v>
       </c>
       <c r="Q91">
         <v>0.132</v>
@@ -7054,7 +7054,7 @@
         <v>0.99</v>
       </c>
       <c r="J92">
-        <v>0.599</v>
+        <v>0.592</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N92">
@@ -7102,21 +7102,21 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>PL51</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Dolnośląskie</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G93">
-        <v>0.697</v>
+        <v>0.703</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -7124,34 +7124,34 @@
         </is>
       </c>
       <c r="I93">
-        <v>0.553</v>
+        <v>0.397</v>
       </c>
       <c r="J93">
-        <v>0.536</v>
+        <v>0.749</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N93">
-        <v>0.553</v>
+        <v>0.12</v>
       </c>
       <c r="O93">
-        <v>0.553</v>
+        <v>0.681</v>
       </c>
       <c r="P93">
-        <v>0.553</v>
+        <v>0.39</v>
       </c>
       <c r="Q93">
         <v>0.01</v>
@@ -7175,21 +7175,21 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Dolnośląskie</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G94">
-        <v>0.674</v>
+        <v>0.673</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
@@ -7197,34 +7197,34 @@
         </is>
       </c>
       <c r="I94">
-        <v>0.397</v>
+        <v>0.553</v>
       </c>
       <c r="J94">
-        <v>0.698</v>
+        <v>0.493</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N94">
-        <v>0.12</v>
+        <v>0.553</v>
       </c>
       <c r="O94">
-        <v>0.681</v>
+        <v>0.553</v>
       </c>
       <c r="P94">
-        <v>0.39</v>
+        <v>0.553</v>
       </c>
       <c r="Q94">
         <v>0.01</v>
@@ -7262,7 +7262,7 @@
         </is>
       </c>
       <c r="G95">
-        <v>0.645</v>
+        <v>0.637</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7273,7 +7273,7 @@
         <v>0.368</v>
       </c>
       <c r="J95">
-        <v>0.6909999999999999</v>
+        <v>0.664</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7287,7 +7287,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N95">
@@ -7335,7 +7335,7 @@
         </is>
       </c>
       <c r="G96">
-        <v>0.615</v>
+        <v>0.603</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7346,7 +7346,7 @@
         <v>0.463</v>
       </c>
       <c r="J96">
-        <v>0.5</v>
+        <v>0.473</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N96">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Mellersta Norrland</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7416,7 +7416,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>0.023</v>
+        <v>0.014</v>
       </c>
       <c r="J97">
         <v>0.01</v>
@@ -7433,17 +7433,17 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N97">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="O97">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="P97">
-        <v>0.036</v>
+        <v>0.018</v>
       </c>
       <c r="Q97">
         <v>0.01</v>
@@ -7481,7 +7481,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.031</v>
+        <v>0.018</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7492,7 +7492,7 @@
         <v>0.012</v>
       </c>
       <c r="J98">
-        <v>0.08</v>
+        <v>0.027</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7540,21 +7540,21 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G99">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7562,10 +7562,10 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.04</v>
+        <v>0.018</v>
       </c>
       <c r="J99">
-        <v>0.026</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7574,22 +7574,22 @@
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N99">
-        <v>0.027</v>
+        <v>0.019</v>
       </c>
       <c r="O99">
-        <v>0.022</v>
+        <v>0.018</v>
       </c>
       <c r="P99">
-        <v>0.07199999999999999</v>
+        <v>0.017</v>
       </c>
       <c r="Q99">
         <v>0.01</v>
@@ -7613,21 +7613,21 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>BE34</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Prov. Luxembourg (BE)</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G100">
-        <v>0.034</v>
+        <v>0.047</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7635,34 +7635,34 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="J100">
-        <v>0.112</v>
+        <v>0.073</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N100">
-        <v>0.01</v>
+        <v>0.017</v>
       </c>
       <c r="O100">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="P100">
-        <v>0.01</v>
+        <v>0.036</v>
       </c>
       <c r="Q100">
         <v>0.01</v>
@@ -7686,21 +7686,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>BE35</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Prov. Namur</t>
+          <t>Zeeland</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G101">
-        <v>0.036</v>
+        <v>0.049</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -7708,14 +7708,14 @@
         </is>
       </c>
       <c r="I101">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="J101">
-        <v>0.125</v>
+        <v>0.09</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7729,13 +7729,13 @@
         </is>
       </c>
       <c r="N101">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="O101">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="P101">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="Q101">
         <v>0.01</v>
@@ -7784,7 +7784,7 @@
         <v>0.99</v>
       </c>
       <c r="J102">
-        <v>0.704</v>
+        <v>0.827</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N102">
@@ -7846,7 +7846,7 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.8139999999999999</v>
+        <v>0.85</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -7857,7 +7857,7 @@
         <v>0.851</v>
       </c>
       <c r="J103">
-        <v>0.555</v>
+        <v>0.711</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N103">
@@ -7919,7 +7919,7 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.6870000000000001</v>
+        <v>0.72</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -7930,11 +7930,11 @@
         <v>0.556</v>
       </c>
       <c r="J104">
-        <v>0.606</v>
+        <v>0.783</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Diversification</t>
         </is>
       </c>
       <c r="N104">
@@ -7978,32 +7978,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>CZ02</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Střední Čechy</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G105">
-        <v>0.613</v>
+        <v>0.583</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I105">
-        <v>0.376</v>
+        <v>0.317</v>
       </c>
       <c r="J105">
-        <v>0.713</v>
+        <v>0.905</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8017,17 +8017,17 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N105">
-        <v>0.139</v>
+        <v>0.098</v>
       </c>
       <c r="O105">
-        <v>0.696</v>
+        <v>0.442</v>
       </c>
       <c r="P105">
-        <v>0.294</v>
+        <v>0.411</v>
       </c>
       <c r="Q105">
         <v>0.01</v>
@@ -8051,21 +8051,21 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Śląskie</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G106">
-        <v>0.585</v>
+        <v>0.581</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -8073,10 +8073,10 @@
         </is>
       </c>
       <c r="I106">
-        <v>0.346</v>
+        <v>0.376</v>
       </c>
       <c r="J106">
-        <v>0.705</v>
+        <v>0.755</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8085,22 +8085,22 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N106">
-        <v>0.349</v>
+        <v>0.139</v>
       </c>
       <c r="O106">
-        <v>0.267</v>
+        <v>0.696</v>
       </c>
       <c r="P106">
-        <v>0.423</v>
+        <v>0.294</v>
       </c>
       <c r="Q106">
         <v>0.01</v>
@@ -8124,17 +8124,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>FRK1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Auvergne</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G107">
@@ -8146,7 +8146,7 @@
         </is>
       </c>
       <c r="I107">
-        <v>0.011</v>
+        <v>0.022</v>
       </c>
       <c r="J107">
         <v>0.01</v>
@@ -8163,17 +8163,17 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N107">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="O107">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="P107">
-        <v>0.012</v>
+        <v>0.032</v>
       </c>
       <c r="Q107">
         <v>0.01</v>
@@ -8197,12 +8197,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>FRI2</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Limousin</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="G108">
-        <v>0.052</v>
+        <v>0.015</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8219,34 +8219,34 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.01</v>
+        <v>0.016</v>
       </c>
       <c r="J108">
-        <v>0.211</v>
+        <v>0.023</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N108">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="O108">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="P108">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="Q108">
         <v>0.01</v>
@@ -8270,21 +8270,21 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>AT21</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Kärnten</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G109">
-        <v>0.057</v>
+        <v>0.018</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8295,11 +8295,11 @@
         <v>0.011</v>
       </c>
       <c r="J109">
-        <v>0.239</v>
+        <v>0.044</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -8309,14 +8309,14 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N109">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="O109">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="P109">
         <v>0.012</v>
@@ -8343,12 +8343,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FRI2</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Limousin</t>
+          <t>Corse</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8357,7 +8357,7 @@
         </is>
       </c>
       <c r="G110">
-        <v>0.059</v>
+        <v>0.026</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8365,34 +8365,34 @@
         </is>
       </c>
       <c r="I110">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="J110">
-        <v>0.166</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N110">
-        <v>0.015</v>
+        <v>0.01</v>
       </c>
       <c r="O110">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="P110">
-        <v>0.022</v>
+        <v>0.01</v>
       </c>
       <c r="Q110">
         <v>0.01</v>
@@ -8416,12 +8416,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FRK1</t>
+          <t>FRJ1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Auvergne</t>
+          <t>Languedoc-Roussillon</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8430,7 +8430,7 @@
         </is>
       </c>
       <c r="G111">
-        <v>0.067</v>
+        <v>0.027</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8438,14 +8438,14 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.022</v>
+        <v>0.017</v>
       </c>
       <c r="J111">
-        <v>0.155</v>
+        <v>0.055</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8455,17 +8455,17 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N111">
-        <v>0.02</v>
+        <v>0.016</v>
       </c>
       <c r="O111">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="P111">
-        <v>0.032</v>
+        <v>0.023</v>
       </c>
       <c r="Q111">
         <v>0.01</v>
@@ -8489,12 +8489,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8511,10 +8511,10 @@
         </is>
       </c>
       <c r="I112">
-        <v>0.99</v>
+        <v>0.913</v>
       </c>
       <c r="J112">
-        <v>0.501</v>
+        <v>0.615</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8528,17 +8528,17 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N112">
-        <v>0.99</v>
+        <v>0.913</v>
       </c>
       <c r="O112">
-        <v>0.839</v>
+        <v>0.773</v>
       </c>
       <c r="P112">
-        <v>0.99</v>
+        <v>0.913</v>
       </c>
       <c r="Q112">
         <v>0.01</v>
@@ -8562,12 +8562,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8576,7 +8576,7 @@
         </is>
       </c>
       <c r="G113">
-        <v>0.983</v>
+        <v>0.946</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8584,10 +8584,10 @@
         </is>
       </c>
       <c r="I113">
-        <v>0.913</v>
+        <v>0.99</v>
       </c>
       <c r="J113">
-        <v>0.536</v>
+        <v>0.519</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8601,17 +8601,17 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N113">
-        <v>0.913</v>
+        <v>0.99</v>
       </c>
       <c r="O113">
-        <v>0.773</v>
+        <v>0.839</v>
       </c>
       <c r="P113">
-        <v>0.913</v>
+        <v>0.99</v>
       </c>
       <c r="Q113">
         <v>0.01</v>
@@ -8649,7 +8649,7 @@
         </is>
       </c>
       <c r="G114">
-        <v>0.862</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8660,11 +8660,11 @@
         <v>0.596</v>
       </c>
       <c r="J114">
-        <v>0.634</v>
+        <v>0.845</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N114">
@@ -8708,21 +8708,21 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G115">
-        <v>0.662</v>
+        <v>0.705</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -8730,10 +8730,10 @@
         </is>
       </c>
       <c r="I115">
-        <v>0.423</v>
+        <v>0.315</v>
       </c>
       <c r="J115">
-        <v>0.531</v>
+        <v>0.919</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8742,22 +8742,22 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Finance</t>
+          <t>Supply Chain</t>
         </is>
       </c>
       <c r="N115">
-        <v>0.424</v>
+        <v>0.272</v>
       </c>
       <c r="O115">
-        <v>0.359</v>
+        <v>0.174</v>
       </c>
       <c r="P115">
-        <v>0.424</v>
+        <v>0.455</v>
       </c>
       <c r="Q115">
         <v>0.01</v>
@@ -8781,12 +8781,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ITI1</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8795,18 +8795,18 @@
         </is>
       </c>
       <c r="G116">
-        <v>0.595</v>
+        <v>0.611</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I116">
-        <v>0.422</v>
+        <v>0.423</v>
       </c>
       <c r="J116">
-        <v>0.432</v>
+        <v>0.52</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -8824,13 +8824,13 @@
         </is>
       </c>
       <c r="N116">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="O116">
         <v>0.359</v>
       </c>
       <c r="P116">
-        <v>0.423</v>
+        <v>0.424</v>
       </c>
       <c r="Q116">
         <v>0.01</v>
@@ -8854,17 +8854,17 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>ES41</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Castilla y León</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G117">
@@ -8876,7 +8876,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>0.029</v>
+        <v>0.06</v>
       </c>
       <c r="J117">
         <v>0.01</v>
@@ -8897,13 +8897,13 @@
         </is>
       </c>
       <c r="N117">
-        <v>0.044</v>
+        <v>0.082</v>
       </c>
       <c r="O117">
-        <v>0.014</v>
+        <v>0.041</v>
       </c>
       <c r="P117">
-        <v>0.03</v>
+        <v>0.054</v>
       </c>
       <c r="Q117">
         <v>0.01</v>
@@ -8927,21 +8927,21 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Mellersta Norrland</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G118">
-        <v>0.044</v>
+        <v>0.028</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -8949,34 +8949,34 @@
         </is>
       </c>
       <c r="I118">
-        <v>0.089</v>
+        <v>0.018</v>
       </c>
       <c r="J118">
+        <v>0.08</v>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Balanced</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>Scope 1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N118">
+        <v>0.026</v>
+      </c>
+      <c r="O118">
+        <v>0.011</v>
+      </c>
+      <c r="P118">
         <v>0.019</v>
-      </c>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>Balanced</t>
-        </is>
-      </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>Scope 3</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N118">
-        <v>0.091</v>
-      </c>
-      <c r="O118">
-        <v>0.032</v>
-      </c>
-      <c r="P118">
-        <v>0.135</v>
       </c>
       <c r="Q118">
         <v>0.01</v>
@@ -9000,21 +9000,21 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>AT34</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Vorarlberg</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G119">
-        <v>0.074</v>
+        <v>0.036</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9022,34 +9022,34 @@
         </is>
       </c>
       <c r="I119">
-        <v>0.018</v>
+        <v>0.035</v>
       </c>
       <c r="J119">
-        <v>0.215</v>
+        <v>0.056</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N119">
-        <v>0.026</v>
+        <v>0.025</v>
       </c>
       <c r="O119">
-        <v>0.011</v>
+        <v>0.016</v>
       </c>
       <c r="P119">
-        <v>0.019</v>
+        <v>0.063</v>
       </c>
       <c r="Q119">
         <v>0.01</v>
@@ -9073,21 +9073,21 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Valle d’Aosta/Vallée d’Aoste</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G120">
-        <v>0.075</v>
+        <v>0.037</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9095,14 +9095,14 @@
         </is>
       </c>
       <c r="I120">
-        <v>0.012</v>
+        <v>0.029</v>
       </c>
       <c r="J120">
-        <v>0.324</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9112,17 +9112,17 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N120">
+        <v>0.044</v>
+      </c>
+      <c r="O120">
         <v>0.014</v>
       </c>
-      <c r="O120">
-        <v>0.012</v>
-      </c>
       <c r="P120">
-        <v>0.014</v>
+        <v>0.03</v>
       </c>
       <c r="Q120">
         <v>0.01</v>
@@ -9146,21 +9146,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G121">
-        <v>0.08500000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9168,14 +9168,14 @@
         </is>
       </c>
       <c r="I121">
-        <v>0.023</v>
+        <v>0.031</v>
       </c>
       <c r="J121">
-        <v>0.209</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9189,13 +9189,13 @@
         </is>
       </c>
       <c r="N121">
-        <v>0.033</v>
+        <v>0.042</v>
       </c>
       <c r="O121">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="P121">
-        <v>0.025</v>
+        <v>0.028</v>
       </c>
       <c r="Q121">
         <v>0.01</v>

--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q121"/>
+  <dimension ref="A1:P121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -435,11 +435,6 @@
           <t>Scope3</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Policy_Pressure</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -510,9 +505,6 @@
       <c r="P2">
         <v>0.99</v>
       </c>
-      <c r="Q2">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -583,9 +575,6 @@
       <c r="P3">
         <v>0.601</v>
       </c>
-      <c r="Q3">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -656,9 +645,6 @@
       <c r="P4">
         <v>0.619</v>
       </c>
-      <c r="Q4">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -729,9 +715,6 @@
       <c r="P5">
         <v>0.463</v>
       </c>
-      <c r="Q5">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -802,9 +785,6 @@
       <c r="P6">
         <v>0.507</v>
       </c>
-      <c r="Q6">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -858,7 +838,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -875,9 +855,6 @@
       <c r="P7">
         <v>0.036</v>
       </c>
-      <c r="Q7">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -931,7 +908,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -948,9 +925,6 @@
       <c r="P8">
         <v>0.025</v>
       </c>
-      <c r="Q8">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1004,7 +978,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1021,9 +995,6 @@
       <c r="P9">
         <v>0.08500000000000001</v>
       </c>
-      <c r="Q9">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1077,7 +1048,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1094,9 +1065,6 @@
       <c r="P10">
         <v>0.011</v>
       </c>
-      <c r="Q10">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1150,7 +1118,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1167,9 +1135,6 @@
       <c r="P11">
         <v>0.022</v>
       </c>
-      <c r="Q11">
-        <v>0.378</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1240,9 +1205,6 @@
       <c r="P12">
         <v>0.99</v>
       </c>
-      <c r="Q12">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1313,9 +1275,6 @@
       <c r="P13">
         <v>0.735</v>
       </c>
-      <c r="Q13">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1386,9 +1345,6 @@
       <c r="P14">
         <v>0.6909999999999999</v>
       </c>
-      <c r="Q14">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1459,9 +1415,6 @@
       <c r="P15">
         <v>0.469</v>
       </c>
-      <c r="Q15">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1532,9 +1485,6 @@
       <c r="P16">
         <v>0.584</v>
       </c>
-      <c r="Q16">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1605,9 +1555,6 @@
       <c r="P17">
         <v>0.145</v>
       </c>
-      <c r="Q17">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1661,7 +1608,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1678,9 +1625,6 @@
       <c r="P18">
         <v>0.019</v>
       </c>
-      <c r="Q18">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1734,7 +1678,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1751,9 +1695,6 @@
       <c r="P19">
         <v>0.028</v>
       </c>
-      <c r="Q19">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1807,7 +1748,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1824,9 +1765,6 @@
       <c r="P20">
         <v>0.032</v>
       </c>
-      <c r="Q20">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1880,7 +1818,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1897,9 +1835,6 @@
       <c r="P21">
         <v>0.01</v>
       </c>
-      <c r="Q21">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1970,9 +1905,6 @@
       <c r="P22">
         <v>0.99</v>
       </c>
-      <c r="Q22">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2043,9 +1975,6 @@
       <c r="P23">
         <v>0.778</v>
       </c>
-      <c r="Q23">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2116,9 +2045,6 @@
       <c r="P24">
         <v>0.49</v>
       </c>
-      <c r="Q24">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2189,9 +2115,6 @@
       <c r="P25">
         <v>0.606</v>
       </c>
-      <c r="Q25">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2262,9 +2185,6 @@
       <c r="P26">
         <v>0.33</v>
       </c>
-      <c r="Q26">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2335,9 +2255,6 @@
       <c r="P27">
         <v>0.019</v>
       </c>
-      <c r="Q27">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2408,9 +2325,6 @@
       <c r="P28">
         <v>0.012</v>
       </c>
-      <c r="Q28">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2481,9 +2395,6 @@
       <c r="P29">
         <v>0.013</v>
       </c>
-      <c r="Q29">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2554,9 +2465,6 @@
       <c r="P30">
         <v>0.012</v>
       </c>
-      <c r="Q30">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2627,9 +2535,6 @@
       <c r="P31">
         <v>0.012</v>
       </c>
-      <c r="Q31">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2700,9 +2605,6 @@
       <c r="P32">
         <v>0.99</v>
       </c>
-      <c r="Q32">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2773,9 +2675,6 @@
       <c r="P33">
         <v>0.669</v>
       </c>
-      <c r="Q33">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2846,9 +2745,6 @@
       <c r="P34">
         <v>0.531</v>
       </c>
-      <c r="Q34">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2919,9 +2815,6 @@
       <c r="P35">
         <v>0.5649999999999999</v>
       </c>
-      <c r="Q35">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2992,9 +2885,6 @@
       <c r="P36">
         <v>0.395</v>
       </c>
-      <c r="Q36">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3048,7 +2938,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -3065,9 +2955,6 @@
       <c r="P37">
         <v>0.067</v>
       </c>
-      <c r="Q37">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3121,7 +3008,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3138,9 +3025,6 @@
       <c r="P38">
         <v>0.047</v>
       </c>
-      <c r="Q38">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3194,7 +3078,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3211,9 +3095,6 @@
       <c r="P39">
         <v>0.03</v>
       </c>
-      <c r="Q39">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3267,7 +3148,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3284,9 +3165,6 @@
       <c r="P40">
         <v>0.01</v>
       </c>
-      <c r="Q40">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3340,7 +3218,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -3357,9 +3235,6 @@
       <c r="P41">
         <v>0.025</v>
       </c>
-      <c r="Q41">
-        <v>0.255</v>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -3430,9 +3305,6 @@
       <c r="P42">
         <v>0.9399999999999999</v>
       </c>
-      <c r="Q42">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3503,9 +3375,6 @@
       <c r="P43">
         <v>0.99</v>
       </c>
-      <c r="Q43">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3576,9 +3445,6 @@
       <c r="P44">
         <v>0.38</v>
       </c>
-      <c r="Q44">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3632,7 +3498,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3649,9 +3515,6 @@
       <c r="P45">
         <v>0.358</v>
       </c>
-      <c r="Q45">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3722,9 +3585,6 @@
       <c r="P46">
         <v>0.375</v>
       </c>
-      <c r="Q46">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3778,7 +3638,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3795,9 +3655,6 @@
       <c r="P47">
         <v>0.024</v>
       </c>
-      <c r="Q47">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3851,7 +3708,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3868,9 +3725,6 @@
       <c r="P48">
         <v>0.036</v>
       </c>
-      <c r="Q48">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3924,7 +3778,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3941,9 +3795,6 @@
       <c r="P49">
         <v>0.015</v>
       </c>
-      <c r="Q49">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3997,7 +3848,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -4014,9 +3865,6 @@
       <c r="P50">
         <v>0.014</v>
       </c>
-      <c r="Q50">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4070,7 +3918,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4087,9 +3935,6 @@
       <c r="P51">
         <v>0.011</v>
       </c>
-      <c r="Q51">
-        <v>0.745</v>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4160,9 +4005,6 @@
       <c r="P52">
         <v>0.99</v>
       </c>
-      <c r="Q52">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4233,9 +4075,6 @@
       <c r="P53">
         <v>0.294</v>
       </c>
-      <c r="Q53">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4306,9 +4145,6 @@
       <c r="P54">
         <v>0.59</v>
       </c>
-      <c r="Q54">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4379,9 +4215,6 @@
       <c r="P55">
         <v>0.405</v>
       </c>
-      <c r="Q55">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4452,9 +4285,6 @@
       <c r="P56">
         <v>0.573</v>
       </c>
-      <c r="Q56">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4508,7 +4338,7 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -4525,9 +4355,6 @@
       <c r="P57">
         <v>0.026</v>
       </c>
-      <c r="Q57">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4581,7 +4408,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -4598,9 +4425,6 @@
       <c r="P58">
         <v>0.017</v>
       </c>
-      <c r="Q58">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4654,7 +4478,7 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -4671,9 +4495,6 @@
       <c r="P59">
         <v>0.019</v>
       </c>
-      <c r="Q59">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4727,7 +4548,7 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4744,9 +4565,6 @@
       <c r="P60">
         <v>0.023</v>
       </c>
-      <c r="Q60">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4800,7 +4618,7 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4817,9 +4635,6 @@
       <c r="P61">
         <v>0.046</v>
       </c>
-      <c r="Q61">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4890,9 +4705,6 @@
       <c r="P62">
         <v>0.99</v>
       </c>
-      <c r="Q62">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4946,7 +4758,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4963,9 +4775,6 @@
       <c r="P63">
         <v>0.705</v>
       </c>
-      <c r="Q63">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5019,7 +4828,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
@@ -5036,9 +4845,6 @@
       <c r="P64">
         <v>0.622</v>
       </c>
-      <c r="Q64">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5109,9 +4915,6 @@
       <c r="P65">
         <v>0.455</v>
       </c>
-      <c r="Q65">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5165,7 +4968,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
@@ -5182,9 +4985,6 @@
       <c r="P66">
         <v>0.272</v>
       </c>
-      <c r="Q66">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5238,7 +5038,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5255,9 +5055,6 @@
       <c r="P67">
         <v>0.017</v>
       </c>
-      <c r="Q67">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5311,7 +5108,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5328,9 +5125,6 @@
       <c r="P68">
         <v>0.03</v>
       </c>
-      <c r="Q68">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5384,7 +5178,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5401,9 +5195,6 @@
       <c r="P69">
         <v>0.028</v>
       </c>
-      <c r="Q69">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5457,7 +5248,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5474,9 +5265,6 @@
       <c r="P70">
         <v>0.027</v>
       </c>
-      <c r="Q70">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5530,7 +5318,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5547,9 +5335,6 @@
       <c r="P71">
         <v>0.019</v>
       </c>
-      <c r="Q71">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5620,9 +5405,6 @@
       <c r="P72">
         <v>0.608</v>
       </c>
-      <c r="Q72">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5693,9 +5475,6 @@
       <c r="P73">
         <v>0.99</v>
       </c>
-      <c r="Q73">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5749,7 +5528,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
@@ -5766,9 +5545,6 @@
       <c r="P74">
         <v>0.529</v>
       </c>
-      <c r="Q74">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5822,7 +5598,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
@@ -5839,9 +5615,6 @@
       <c r="P75">
         <v>0.218</v>
       </c>
-      <c r="Q75">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5895,7 +5668,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5912,9 +5685,6 @@
       <c r="P76">
         <v>0.115</v>
       </c>
-      <c r="Q76">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5968,7 +5738,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
@@ -5985,9 +5755,6 @@
       <c r="P77">
         <v>0.01</v>
       </c>
-      <c r="Q77">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -6041,7 +5808,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
@@ -6058,9 +5825,6 @@
       <c r="P78">
         <v>0.012</v>
       </c>
-      <c r="Q78">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -6114,7 +5878,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -6131,9 +5895,6 @@
       <c r="P79">
         <v>0.018</v>
       </c>
-      <c r="Q79">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -6187,7 +5948,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 2</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
@@ -6204,9 +5965,6 @@
       <c r="P80">
         <v>0.011</v>
       </c>
-      <c r="Q80">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -6260,7 +6018,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
@@ -6277,9 +6035,6 @@
       <c r="P81">
         <v>0.012</v>
       </c>
-      <c r="Q81">
-        <v>0.99</v>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -6350,9 +6105,6 @@
       <c r="P82">
         <v>0.99</v>
       </c>
-      <c r="Q82">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -6423,9 +6175,6 @@
       <c r="P83">
         <v>0.544</v>
       </c>
-      <c r="Q83">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -6496,9 +6245,6 @@
       <c r="P84">
         <v>0.59</v>
       </c>
-      <c r="Q84">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -6569,9 +6315,6 @@
       <c r="P85">
         <v>0.577</v>
       </c>
-      <c r="Q85">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -6642,9 +6385,6 @@
       <c r="P86">
         <v>0.349</v>
       </c>
-      <c r="Q86">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -6698,7 +6438,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -6715,9 +6455,6 @@
       <c r="P87">
         <v>0.04</v>
       </c>
-      <c r="Q87">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -6771,7 +6508,7 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 3</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6788,9 +6525,6 @@
       <c r="P88">
         <v>0.048</v>
       </c>
-      <c r="Q88">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -6844,7 +6578,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6861,9 +6595,6 @@
       <c r="P89">
         <v>0.01</v>
       </c>
-      <c r="Q89">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -6917,7 +6648,7 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6934,9 +6665,6 @@
       <c r="P90">
         <v>0.025</v>
       </c>
-      <c r="Q90">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -6990,7 +6718,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Policy Pressure</t>
+          <t>Scope 1</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -7007,9 +6735,6 @@
       <c r="P91">
         <v>0.017</v>
       </c>
-      <c r="Q91">
-        <v>0.132</v>
-      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -7080,9 +6805,6 @@
       <c r="P92">
         <v>0.99</v>
       </c>
-      <c r="Q92">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -7153,9 +6875,6 @@
       <c r="P93">
         <v>0.39</v>
       </c>
-      <c r="Q93">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -7226,9 +6945,6 @@
       <c r="P94">
         <v>0.553</v>
       </c>
-      <c r="Q94">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -7299,9 +7015,6 @@
       <c r="P95">
         <v>0.362</v>
       </c>
-      <c r="Q95">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -7372,9 +7085,6 @@
       <c r="P96">
         <v>0.497</v>
       </c>
-      <c r="Q96">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -7445,9 +7155,6 @@
       <c r="P97">
         <v>0.018</v>
       </c>
-      <c r="Q97">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -7518,9 +7225,6 @@
       <c r="P98">
         <v>0.012</v>
       </c>
-      <c r="Q98">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -7591,9 +7295,6 @@
       <c r="P99">
         <v>0.017</v>
       </c>
-      <c r="Q99">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -7664,9 +7365,6 @@
       <c r="P100">
         <v>0.036</v>
       </c>
-      <c r="Q100">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -7737,9 +7435,6 @@
       <c r="P101">
         <v>0.018</v>
       </c>
-      <c r="Q101">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -7810,9 +7505,6 @@
       <c r="P102">
         <v>0.99</v>
       </c>
-      <c r="Q102">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -7883,9 +7575,6 @@
       <c r="P103">
         <v>0.851</v>
       </c>
-      <c r="Q103">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -7956,9 +7645,6 @@
       <c r="P104">
         <v>0.556</v>
       </c>
-      <c r="Q104">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -8029,9 +7715,6 @@
       <c r="P105">
         <v>0.411</v>
       </c>
-      <c r="Q105">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -8102,9 +7785,6 @@
       <c r="P106">
         <v>0.294</v>
       </c>
-      <c r="Q106">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -8175,9 +7855,6 @@
       <c r="P107">
         <v>0.032</v>
       </c>
-      <c r="Q107">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -8248,9 +7925,6 @@
       <c r="P108">
         <v>0.022</v>
       </c>
-      <c r="Q108">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -8321,9 +7995,6 @@
       <c r="P109">
         <v>0.012</v>
       </c>
-      <c r="Q109">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -8394,9 +8065,6 @@
       <c r="P110">
         <v>0.01</v>
       </c>
-      <c r="Q110">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -8467,9 +8135,6 @@
       <c r="P111">
         <v>0.023</v>
       </c>
-      <c r="Q111">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -8540,9 +8205,6 @@
       <c r="P112">
         <v>0.913</v>
       </c>
-      <c r="Q112">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -8613,9 +8275,6 @@
       <c r="P113">
         <v>0.99</v>
       </c>
-      <c r="Q113">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -8686,9 +8345,6 @@
       <c r="P114">
         <v>0.495</v>
       </c>
-      <c r="Q114">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -8759,9 +8415,6 @@
       <c r="P115">
         <v>0.455</v>
       </c>
-      <c r="Q115">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -8832,9 +8485,6 @@
       <c r="P116">
         <v>0.424</v>
       </c>
-      <c r="Q116">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -8905,9 +8555,6 @@
       <c r="P117">
         <v>0.054</v>
       </c>
-      <c r="Q117">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -8978,9 +8625,6 @@
       <c r="P118">
         <v>0.019</v>
       </c>
-      <c r="Q118">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -9051,9 +8695,6 @@
       <c r="P119">
         <v>0.063</v>
       </c>
-      <c r="Q119">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -9124,9 +8765,6 @@
       <c r="P120">
         <v>0.03</v>
       </c>
-      <c r="Q120">
-        <v>0.01</v>
-      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -9196,9 +8834,6 @@
       </c>
       <c r="P121">
         <v>0.028</v>
-      </c>
-      <c r="Q121">
-        <v>0.01</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P121"/>
+  <dimension ref="A1:R121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -422,15 +422,25 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
+          <t>exposure_ETS</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>exposure_CBAM</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
           <t>Scope1</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Scope2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Scope3</t>
         </is>
@@ -479,16 +489,16 @@
         <v>0.99</v>
       </c>
       <c r="J2">
-        <v>0.99</v>
+        <v>0.452</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -497,13 +507,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>0.99</v>
+        <v>8100289</v>
       </c>
       <c r="O2">
-        <v>0.99</v>
+        <v>16842417</v>
       </c>
       <c r="P2">
-        <v>0.99</v>
+        <v>20064.08</v>
+      </c>
+      <c r="Q2">
+        <v>6273.26</v>
+      </c>
+      <c r="R2">
+        <v>231574624.05</v>
       </c>
     </row>
     <row r="3">
@@ -524,41 +540,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>DEA1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G3">
-        <v>0.6830000000000001</v>
+        <v>0.841</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I3">
-        <v>0.601</v>
+        <v>0.927</v>
       </c>
       <c r="J3">
-        <v>0.782</v>
+        <v>0.355</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -567,13 +583,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>0.602</v>
+        <v>18692467</v>
       </c>
       <c r="O3">
-        <v>0.602</v>
+        <v>4658267</v>
       </c>
       <c r="P3">
-        <v>0.601</v>
+        <v>8051.72</v>
+      </c>
+      <c r="Q3">
+        <v>3345.81</v>
+      </c>
+      <c r="R3">
+        <v>61837247.36</v>
       </c>
     </row>
     <row r="4">
@@ -594,32 +616,32 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G4">
-        <v>0.652</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I4">
-        <v>0.5580000000000001</v>
+        <v>0.335</v>
       </c>
       <c r="J4">
-        <v>0.767</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -628,22 +650,28 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N4">
-        <v>0.717</v>
+        <v>6876932</v>
       </c>
       <c r="O4">
-        <v>0.338</v>
+        <v>1386007</v>
       </c>
       <c r="P4">
-        <v>0.619</v>
+        <v>2180.71</v>
+      </c>
+      <c r="Q4">
+        <v>681.8200000000001</v>
+      </c>
+      <c r="R4">
+        <v>25169243.03</v>
       </c>
     </row>
     <row r="5">
@@ -664,21 +692,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G5">
-        <v>0.62</v>
+        <v>0.742</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -686,34 +714,40 @@
         </is>
       </c>
       <c r="I5">
-        <v>0.6919999999999999</v>
+        <v>0.332</v>
       </c>
       <c r="J5">
-        <v>0.5600000000000001</v>
+        <v>0.784</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N5">
-        <v>0.694</v>
+        <v>5651291</v>
       </c>
       <c r="O5">
-        <v>0.921</v>
+        <v>2546310</v>
       </c>
       <c r="P5">
-        <v>0.463</v>
+        <v>3305.04</v>
+      </c>
+      <c r="Q5">
+        <v>1033.36</v>
+      </c>
+      <c r="R5">
+        <v>38145944.94</v>
       </c>
     </row>
     <row r="6">
@@ -734,21 +768,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ES61</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G6">
-        <v>0.601</v>
+        <v>0.697</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -756,10 +790,10 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.508</v>
+        <v>0.37</v>
       </c>
       <c r="J6">
-        <v>0.718</v>
+        <v>0.626</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -768,22 +802,28 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N6">
-        <v>0.508</v>
+        <v>7072349</v>
       </c>
       <c r="O6">
-        <v>0.509</v>
+        <v>2095649</v>
       </c>
       <c r="P6">
-        <v>0.507</v>
+        <v>6842.37</v>
+      </c>
+      <c r="Q6">
+        <v>993.76</v>
+      </c>
+      <c r="R6">
+        <v>68087363.3</v>
       </c>
     </row>
     <row r="7">
@@ -804,17 +844,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G7">
@@ -826,34 +866,40 @@
         </is>
       </c>
       <c r="I7">
-        <v>0.028</v>
+        <v>0.152</v>
       </c>
       <c r="J7">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N7">
-        <v>0.041</v>
+        <v>531401</v>
       </c>
       <c r="O7">
-        <v>0.011</v>
+        <v>3071397</v>
       </c>
       <c r="P7">
-        <v>0.036</v>
+        <v>14033.72</v>
+      </c>
+      <c r="Q7">
+        <v>5831.56</v>
+      </c>
+      <c r="R7">
+        <v>107779015.7</v>
       </c>
     </row>
     <row r="8">
@@ -874,21 +920,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G8">
-        <v>0.026</v>
+        <v>0.028</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -896,34 +942,40 @@
         </is>
       </c>
       <c r="I8">
-        <v>0.02</v>
+        <v>0.286</v>
       </c>
       <c r="J8">
-        <v>0.055</v>
+        <v>0.01</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N8">
-        <v>0.028</v>
+        <v>3575300</v>
       </c>
       <c r="O8">
-        <v>0.01</v>
+        <v>3458269</v>
       </c>
       <c r="P8">
-        <v>0.025</v>
+        <v>10466.87</v>
+      </c>
+      <c r="Q8">
+        <v>4349.39</v>
+      </c>
+      <c r="R8">
+        <v>80385552.20999999</v>
       </c>
     </row>
     <row r="9">
@@ -944,21 +996,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G9">
-        <v>0.047</v>
+        <v>0.039</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -966,34 +1018,40 @@
         </is>
       </c>
       <c r="I9">
-        <v>0.065</v>
+        <v>0.02</v>
       </c>
       <c r="J9">
-        <v>0.044</v>
+        <v>0.182</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N9">
-        <v>0.096</v>
+        <v>30577</v>
       </c>
       <c r="O9">
-        <v>0.016</v>
+        <v>224042</v>
       </c>
       <c r="P9">
-        <v>0.08500000000000001</v>
+        <v>849.3200000000001</v>
+      </c>
+      <c r="Q9">
+        <v>205.62</v>
+      </c>
+      <c r="R9">
+        <v>7843142.39</v>
       </c>
     </row>
     <row r="10">
@@ -1014,21 +1072,21 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PT15</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Algarve</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G10">
-        <v>0.059</v>
+        <v>0.044</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1036,34 +1094,40 @@
         </is>
       </c>
       <c r="I10">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="J10">
-        <v>0.418</v>
+        <v>0.122</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N10">
-        <v>0.011</v>
+        <v>15555</v>
       </c>
       <c r="O10">
-        <v>0.012</v>
+        <v>580469</v>
       </c>
       <c r="P10">
-        <v>0.011</v>
+        <v>2127.72</v>
+      </c>
+      <c r="Q10">
+        <v>515.12</v>
+      </c>
+      <c r="R10">
+        <v>19648656.74</v>
       </c>
     </row>
     <row r="11">
@@ -1084,21 +1148,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>AT11</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Burgenland</t>
+          <t>Corse</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G11">
-        <v>0.062</v>
+        <v>0.063</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1106,10 +1170,10 @@
         </is>
       </c>
       <c r="I11">
-        <v>0.023</v>
+        <v>0.011</v>
       </c>
       <c r="J11">
-        <v>0.206</v>
+        <v>0.531</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1118,22 +1182,28 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N11">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="O11">
-        <v>0.016</v>
+        <v>22340</v>
       </c>
       <c r="P11">
-        <v>0.022</v>
+        <v>143.28</v>
+      </c>
+      <c r="Q11">
+        <v>11.63</v>
+      </c>
+      <c r="R11">
+        <v>1239223.42</v>
       </c>
     </row>
     <row r="12">
@@ -1154,56 +1224,62 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>FRE1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Nord-Pas de Calais</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G12">
-        <v>0.99</v>
+        <v>0.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I12">
-        <v>0.967</v>
+        <v>0.074</v>
       </c>
       <c r="J12">
-        <v>0.6929999999999999</v>
+        <v>0.552</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N12">
-        <v>0.956</v>
+        <v>923749</v>
       </c>
       <c r="O12">
-        <v>0.445</v>
+        <v>89646</v>
       </c>
       <c r="P12">
-        <v>0.99</v>
+        <v>447.42</v>
+      </c>
+      <c r="Q12">
+        <v>76.89</v>
+      </c>
+      <c r="R12">
+        <v>12956355.85</v>
       </c>
     </row>
     <row r="13">
@@ -1224,12 +1300,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITH5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1238,27 +1314,27 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.976</v>
+        <v>0.248</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I13">
-        <v>0.99</v>
+        <v>0.06</v>
       </c>
       <c r="J13">
-        <v>0.658</v>
+        <v>0.472</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1267,13 +1343,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>0.99</v>
+        <v>415071</v>
       </c>
       <c r="O13">
-        <v>0.722</v>
+        <v>380381</v>
       </c>
       <c r="P13">
-        <v>0.735</v>
+        <v>992.11</v>
+      </c>
+      <c r="Q13">
+        <v>514.33</v>
+      </c>
+      <c r="R13">
+        <v>26654450.7</v>
       </c>
     </row>
     <row r="14">
@@ -1294,56 +1376,62 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>FRE2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Picardie</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G14">
-        <v>0.967</v>
+        <v>0.245</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I14">
-        <v>0.93</v>
+        <v>0.058</v>
       </c>
       <c r="J14">
-        <v>0.6879999999999999</v>
+        <v>0.481</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14">
-        <v>0.93</v>
+        <v>716827</v>
       </c>
       <c r="O14">
-        <v>0.679</v>
+        <v>38545</v>
       </c>
       <c r="P14">
-        <v>0.6909999999999999</v>
+        <v>192.38</v>
+      </c>
+      <c r="Q14">
+        <v>33.06</v>
+      </c>
+      <c r="R14">
+        <v>5570802.09</v>
       </c>
     </row>
     <row r="15">
@@ -1364,32 +1452,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Mazowiecki regionalny</t>
+          <t>Champagne-Ardenne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G15">
-        <v>0.961</v>
+        <v>0.244</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I15">
-        <v>0.744</v>
+        <v>0.051</v>
       </c>
       <c r="J15">
-        <v>0.851</v>
+        <v>0.543</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1398,22 +1486,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N15">
-        <v>0.58</v>
+        <v>602936</v>
       </c>
       <c r="O15">
-        <v>0.794</v>
+        <v>41664</v>
       </c>
       <c r="P15">
-        <v>0.469</v>
+        <v>207.95</v>
+      </c>
+      <c r="Q15">
+        <v>35.74</v>
+      </c>
+      <c r="R15">
+        <v>6021671.25</v>
       </c>
     </row>
     <row r="16">
@@ -1434,56 +1528,62 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wielkopolskie</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G16">
-        <v>0.949</v>
+        <v>0.219</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I16">
-        <v>0.929</v>
+        <v>0.028</v>
       </c>
       <c r="J16">
-        <v>0.665</v>
+        <v>0.801</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N16">
-        <v>0.724</v>
+        <v>55969</v>
       </c>
       <c r="O16">
-        <v>0.99</v>
+        <v>227355</v>
       </c>
       <c r="P16">
-        <v>0.584</v>
+        <v>592.99</v>
+      </c>
+      <c r="Q16">
+        <v>307.42</v>
+      </c>
+      <c r="R16">
+        <v>15931427.45</v>
       </c>
     </row>
     <row r="17">
@@ -1504,21 +1604,21 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>ES21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>País Vasco</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G17">
-        <v>0.01</v>
+        <v>0.043</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1526,34 +1626,40 @@
         </is>
       </c>
       <c r="I17">
-        <v>0.137</v>
+        <v>0.013</v>
       </c>
       <c r="J17">
-        <v>0.01</v>
+        <v>0.093</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N17">
-        <v>0.135</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>0.07099999999999999</v>
+        <v>46545</v>
       </c>
       <c r="P17">
-        <v>0.145</v>
+        <v>501.47</v>
+      </c>
+      <c r="Q17">
+        <v>316.39</v>
+      </c>
+      <c r="R17">
+        <v>11075693.3</v>
       </c>
     </row>
     <row r="18">
@@ -1574,21 +1680,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G18">
-        <v>0.018</v>
+        <v>0.055</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1596,10 +1702,10 @@
         </is>
       </c>
       <c r="I18">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J18">
-        <v>0.19</v>
+        <v>0.124</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1608,22 +1714,28 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N18">
-        <v>0.01</v>
+        <v>10246</v>
       </c>
       <c r="O18">
-        <v>0.01</v>
+        <v>60541</v>
       </c>
       <c r="P18">
-        <v>0.019</v>
+        <v>652.27</v>
+      </c>
+      <c r="Q18">
+        <v>411.53</v>
+      </c>
+      <c r="R18">
+        <v>14406319.48</v>
       </c>
     </row>
     <row r="19">
@@ -1644,21 +1756,21 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G19">
-        <v>0.024</v>
+        <v>0.055</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1666,10 +1778,10 @@
         </is>
       </c>
       <c r="I19">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="J19">
-        <v>0.136</v>
+        <v>0.152</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1678,22 +1790,28 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N19">
-        <v>0.018</v>
+        <v>0</v>
       </c>
       <c r="O19">
-        <v>0.01</v>
+        <v>29738</v>
       </c>
       <c r="P19">
-        <v>0.028</v>
+        <v>320.4</v>
+      </c>
+      <c r="Q19">
+        <v>202.15</v>
+      </c>
+      <c r="R19">
+        <v>7076482.54</v>
       </c>
     </row>
     <row r="20">
@@ -1714,21 +1832,21 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G20">
-        <v>0.029</v>
+        <v>0.063</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1736,19 +1854,19 @@
         </is>
       </c>
       <c r="I20">
-        <v>0.032</v>
+        <v>0.013</v>
       </c>
       <c r="J20">
-        <v>0.08599999999999999</v>
+        <v>0.168</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1757,13 +1875,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>0.035</v>
+        <v>44932</v>
       </c>
       <c r="O20">
-        <v>0.026</v>
+        <v>9707</v>
       </c>
       <c r="P20">
-        <v>0.032</v>
+        <v>104.58</v>
+      </c>
+      <c r="Q20">
+        <v>65.98</v>
+      </c>
+      <c r="R20">
+        <v>2309864.7</v>
       </c>
     </row>
     <row r="21">
@@ -1784,21 +1908,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EL42</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Notio Aigaio</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G21">
-        <v>0.061</v>
+        <v>0.064</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1806,10 +1930,10 @@
         </is>
       </c>
       <c r="I21">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="J21">
-        <v>0.537</v>
+        <v>0.169</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1818,22 +1942,28 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N21">
-        <v>0.016</v>
+        <v>44811</v>
       </c>
       <c r="O21">
-        <v>0.016</v>
+        <v>16508</v>
       </c>
       <c r="P21">
-        <v>0.01</v>
+        <v>177.86</v>
+      </c>
+      <c r="Q21">
+        <v>112.22</v>
+      </c>
+      <c r="R21">
+        <v>3928249.4</v>
       </c>
     </row>
     <row r="22">
@@ -1868,42 +1998,48 @@
         </is>
       </c>
       <c r="G22">
-        <v>0.99</v>
+        <v>0.191</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I22">
-        <v>0.99</v>
+        <v>0.028</v>
       </c>
       <c r="J22">
-        <v>0.99</v>
+        <v>0.623</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N22">
-        <v>0.99</v>
+        <v>9259</v>
       </c>
       <c r="O22">
-        <v>0.99</v>
+        <v>269447</v>
       </c>
       <c r="P22">
-        <v>0.99</v>
+        <v>669.5599999999999</v>
+      </c>
+      <c r="Q22">
+        <v>258.56</v>
+      </c>
+      <c r="R22">
+        <v>10262659.39</v>
       </c>
     </row>
     <row r="23">
@@ -1924,12 +2060,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1938,42 +2074,48 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.696</v>
+        <v>0.159</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I23">
-        <v>0.778</v>
+        <v>0.016</v>
       </c>
       <c r="J23">
-        <v>0.624</v>
+        <v>0.782</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N23">
-        <v>0.778</v>
+        <v>0</v>
       </c>
       <c r="O23">
-        <v>0.778</v>
+        <v>88130</v>
       </c>
       <c r="P23">
-        <v>0.778</v>
+        <v>219</v>
+      </c>
+      <c r="Q23">
+        <v>84.56999999999999</v>
+      </c>
+      <c r="R23">
+        <v>3356693.07</v>
       </c>
     </row>
     <row r="24">
@@ -2008,18 +2150,18 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.663</v>
+        <v>0.158</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I24">
-        <v>0.5580000000000001</v>
+        <v>0.019</v>
       </c>
       <c r="J24">
-        <v>0.791</v>
+        <v>0.639</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2028,22 +2170,28 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N24">
-        <v>0.597</v>
+        <v>9287</v>
       </c>
       <c r="O24">
-        <v>0.586</v>
+        <v>131430</v>
       </c>
       <c r="P24">
-        <v>0.49</v>
+        <v>400.99</v>
+      </c>
+      <c r="Q24">
+        <v>152.12</v>
+      </c>
+      <c r="R24">
+        <v>5025326.92</v>
       </c>
     </row>
     <row r="25">
@@ -2064,12 +2212,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2078,42 +2226,48 @@
         </is>
       </c>
       <c r="G25">
-        <v>0.595</v>
+        <v>0.14</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I25">
-        <v>0.606</v>
+        <v>0.014</v>
       </c>
       <c r="J25">
-        <v>0.586</v>
+        <v>0.696</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N25">
-        <v>0.606</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>0.606</v>
+        <v>59009</v>
       </c>
       <c r="P25">
-        <v>0.606</v>
+        <v>146.63</v>
+      </c>
+      <c r="Q25">
+        <v>56.63</v>
+      </c>
+      <c r="R25">
+        <v>2247521.65</v>
       </c>
     </row>
     <row r="26">
@@ -2134,12 +2288,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2148,18 +2302,18 @@
         </is>
       </c>
       <c r="G26">
-        <v>0.512</v>
+        <v>0.139</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I26">
-        <v>0.33</v>
+        <v>0.024</v>
       </c>
       <c r="J26">
-        <v>0.799</v>
+        <v>0.402</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2168,22 +2322,28 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N26">
-        <v>0.33</v>
+        <v>3736</v>
       </c>
       <c r="O26">
-        <v>0.33</v>
+        <v>211234</v>
       </c>
       <c r="P26">
-        <v>0.33</v>
+        <v>524.9</v>
+      </c>
+      <c r="Q26">
+        <v>202.7</v>
+      </c>
+      <c r="R26">
+        <v>8045446.05</v>
       </c>
     </row>
     <row r="27">
@@ -2204,21 +2364,21 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G27">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2226,10 +2386,10 @@
         </is>
       </c>
       <c r="I27">
-        <v>0.016</v>
+        <v>0.011</v>
       </c>
       <c r="J27">
-        <v>0.01</v>
+        <v>0.041</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2238,22 +2398,28 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N27">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>0.016</v>
+        <v>11229</v>
       </c>
       <c r="P27">
-        <v>0.019</v>
+        <v>43.33</v>
+      </c>
+      <c r="Q27">
+        <v>21.94</v>
+      </c>
+      <c r="R27">
+        <v>315459.73</v>
       </c>
     </row>
     <row r="28">
@@ -2274,21 +2440,21 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G28">
-        <v>0.035</v>
+        <v>0.024</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2296,10 +2462,10 @@
         </is>
       </c>
       <c r="I28">
-        <v>0.013</v>
+        <v>0.011</v>
       </c>
       <c r="J28">
-        <v>0.105</v>
+        <v>0.045</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2308,7 +2474,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2317,13 +2483,19 @@
         </is>
       </c>
       <c r="N28">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>0.015</v>
+        <v>14263</v>
       </c>
       <c r="P28">
-        <v>0.012</v>
+        <v>55.04</v>
+      </c>
+      <c r="Q28">
+        <v>27.87</v>
+      </c>
+      <c r="R28">
+        <v>400713.89</v>
       </c>
     </row>
     <row r="29">
@@ -2344,21 +2516,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G29">
-        <v>0.038</v>
+        <v>0.039</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2366,10 +2538,10 @@
         </is>
       </c>
       <c r="I29">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="J29">
-        <v>0.113</v>
+        <v>0.098</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2378,7 +2550,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2387,13 +2559,19 @@
         </is>
       </c>
       <c r="N29">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="O29">
-        <v>0.017</v>
+        <v>7140</v>
       </c>
       <c r="P29">
-        <v>0.013</v>
+        <v>27.55</v>
+      </c>
+      <c r="Q29">
+        <v>13.95</v>
+      </c>
+      <c r="R29">
+        <v>200600.57</v>
       </c>
     </row>
     <row r="30">
@@ -2414,21 +2592,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DK02</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sjælland</t>
+          <t>Noord-Holland</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G30">
-        <v>0.038</v>
+        <v>0.044</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2436,10 +2614,10 @@
         </is>
       </c>
       <c r="I30">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J30">
-        <v>0.139</v>
+        <v>0.114</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2448,22 +2626,28 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N30">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="O30">
-        <v>0.012</v>
+        <v>16709</v>
       </c>
       <c r="P30">
-        <v>0.012</v>
+        <v>13.93</v>
+      </c>
+      <c r="Q30">
+        <v>14.35</v>
+      </c>
+      <c r="R30">
+        <v>237599.38</v>
       </c>
     </row>
     <row r="31">
@@ -2484,21 +2668,21 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G31">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2506,10 +2690,10 @@
         </is>
       </c>
       <c r="I31">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="J31">
-        <v>0.122</v>
+        <v>0.123</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2518,7 +2702,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2527,13 +2711,19 @@
         </is>
       </c>
       <c r="N31">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>0.017</v>
+        <v>6963</v>
       </c>
       <c r="P31">
-        <v>0.012</v>
+        <v>26.87</v>
+      </c>
+      <c r="Q31">
+        <v>13.61</v>
+      </c>
+      <c r="R31">
+        <v>195628.64</v>
       </c>
     </row>
     <row r="32">
@@ -2554,12 +2744,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITI1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Toscana</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2568,42 +2758,48 @@
         </is>
       </c>
       <c r="G32">
-        <v>0.99</v>
+        <v>0.247</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I32">
-        <v>0.99</v>
+        <v>0.064</v>
       </c>
       <c r="J32">
-        <v>0.912</v>
+        <v>0.439</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N32">
-        <v>0.99</v>
+        <v>787177</v>
       </c>
       <c r="O32">
-        <v>0.672</v>
+        <v>73725</v>
       </c>
       <c r="P32">
-        <v>0.99</v>
+        <v>516.6</v>
+      </c>
+      <c r="Q32">
+        <v>205.55</v>
+      </c>
+      <c r="R32">
+        <v>3047222.43</v>
       </c>
     </row>
     <row r="33">
@@ -2638,18 +2834,18 @@
         </is>
       </c>
       <c r="G33">
-        <v>0.748</v>
+        <v>0.211</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I33">
-        <v>0.669</v>
+        <v>0.051</v>
       </c>
       <c r="J33">
-        <v>0.776</v>
+        <v>0.411</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2658,7 +2854,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2667,13 +2863,19 @@
         </is>
       </c>
       <c r="N33">
-        <v>0.67</v>
+        <v>521449</v>
       </c>
       <c r="O33">
-        <v>0.456</v>
+        <v>126035</v>
       </c>
       <c r="P33">
-        <v>0.669</v>
+        <v>883.14</v>
+      </c>
+      <c r="Q33">
+        <v>351.39</v>
+      </c>
+      <c r="R33">
+        <v>5209288.92</v>
       </c>
     </row>
     <row r="34">
@@ -2694,41 +2896,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>ES24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wielkopolskie</t>
+          <t>Aragón</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G34">
-        <v>0.644</v>
+        <v>0.19</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I34">
-        <v>0.661</v>
+        <v>0.066</v>
       </c>
       <c r="J34">
-        <v>0.587</v>
+        <v>0.258</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2737,13 +2939,19 @@
         </is>
       </c>
       <c r="N34">
-        <v>0.251</v>
+        <v>879921</v>
       </c>
       <c r="O34">
-        <v>0.99</v>
+        <v>12334</v>
       </c>
       <c r="P34">
-        <v>0.531</v>
+        <v>159.54</v>
+      </c>
+      <c r="Q34">
+        <v>41.64</v>
+      </c>
+      <c r="R34">
+        <v>729741.4399999999</v>
       </c>
     </row>
     <row r="35">
@@ -2764,56 +2972,62 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G35">
-        <v>0.556</v>
+        <v>0.181</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I35">
-        <v>0.604</v>
+        <v>0.04</v>
       </c>
       <c r="J35">
-        <v>0.48</v>
+        <v>0.388</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N35">
-        <v>0.727</v>
+        <v>290853</v>
       </c>
       <c r="O35">
-        <v>0.327</v>
+        <v>187035</v>
       </c>
       <c r="P35">
-        <v>0.5649999999999999</v>
+        <v>1310.58</v>
+      </c>
+      <c r="Q35">
+        <v>521.46</v>
+      </c>
+      <c r="R35">
+        <v>7730536.47</v>
       </c>
     </row>
     <row r="36">
@@ -2834,32 +3048,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>CZ04</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Severozápad</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G36">
-        <v>0.543</v>
+        <v>0.175</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I36">
-        <v>0.395</v>
+        <v>0.028</v>
       </c>
       <c r="J36">
-        <v>0.702</v>
+        <v>0.518</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -2868,22 +3082,28 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N36">
-        <v>0.395</v>
+        <v>280066</v>
       </c>
       <c r="O36">
-        <v>0.27</v>
+        <v>8573</v>
       </c>
       <c r="P36">
-        <v>0.395</v>
+        <v>45.06</v>
+      </c>
+      <c r="Q36">
+        <v>81.34</v>
+      </c>
+      <c r="R36">
+        <v>425416.92</v>
       </c>
     </row>
     <row r="37">
@@ -2904,17 +3124,17 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G37">
@@ -2926,7 +3146,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>0.044</v>
+        <v>0.017</v>
       </c>
       <c r="J37">
         <v>0.01</v>
@@ -2938,22 +3158,28 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N37">
-        <v>0.017</v>
+        <v>81037</v>
       </c>
       <c r="O37">
-        <v>0.038</v>
+        <v>34084</v>
       </c>
       <c r="P37">
-        <v>0.067</v>
+        <v>341.09</v>
+      </c>
+      <c r="Q37">
+        <v>357.27</v>
+      </c>
+      <c r="R37">
+        <v>1741717.05</v>
       </c>
     </row>
     <row r="38">
@@ -2974,21 +3200,21 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>IE04</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Northern and Western</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G38">
-        <v>0.02</v>
+        <v>0.015</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -2996,10 +3222,10 @@
         </is>
       </c>
       <c r="I38">
-        <v>0.031</v>
+        <v>0.017</v>
       </c>
       <c r="J38">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3008,22 +3234,28 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N38">
-        <v>0.014</v>
+        <v>64748</v>
       </c>
       <c r="O38">
-        <v>0.028</v>
+        <v>43036</v>
       </c>
       <c r="P38">
-        <v>0.047</v>
+        <v>430.69</v>
+      </c>
+      <c r="Q38">
+        <v>451.12</v>
+      </c>
+      <c r="R38">
+        <v>2199224.49</v>
       </c>
     </row>
     <row r="39">
@@ -3044,21 +3276,21 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G39">
-        <v>0.043</v>
+        <v>0.031</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3066,34 +3298,40 @@
         </is>
       </c>
       <c r="I39">
-        <v>0.021</v>
+        <v>0.014</v>
       </c>
       <c r="J39">
-        <v>0.129</v>
+        <v>0.052</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N39">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>0.016</v>
+        <v>59629</v>
       </c>
       <c r="P39">
-        <v>0.03</v>
+        <v>30.94</v>
+      </c>
+      <c r="Q39">
+        <v>60.44</v>
+      </c>
+      <c r="R39">
+        <v>1256929.64</v>
       </c>
     </row>
     <row r="40">
@@ -3114,21 +3352,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G40">
-        <v>0.05</v>
+        <v>0.043</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3139,7 +3377,7 @@
         <v>0.01</v>
       </c>
       <c r="J40">
-        <v>0.344</v>
+        <v>0.115</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3148,22 +3386,28 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N40">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O40">
-        <v>0.01</v>
+        <v>6779</v>
       </c>
       <c r="P40">
-        <v>0.01</v>
+        <v>10.15</v>
+      </c>
+      <c r="Q40">
+        <v>5.94</v>
+      </c>
+      <c r="R40">
+        <v>179503.53</v>
       </c>
     </row>
     <row r="41">
@@ -3184,21 +3428,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>IE05</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G41">
-        <v>0.053</v>
+        <v>0.044</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3206,34 +3450,40 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.022</v>
+        <v>0.012</v>
       </c>
       <c r="J41">
-        <v>0.175</v>
+        <v>0.102</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N41">
-        <v>0.02</v>
+        <v>9390</v>
       </c>
       <c r="O41">
-        <v>0.019</v>
+        <v>22517</v>
       </c>
       <c r="P41">
-        <v>0.025</v>
+        <v>11.68</v>
+      </c>
+      <c r="Q41">
+        <v>22.82</v>
+      </c>
+      <c r="R41">
+        <v>474630.56</v>
       </c>
     </row>
     <row r="42">
@@ -3254,21 +3504,21 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>BE21</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Prov. Antwerpen</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G42">
-        <v>0.99</v>
+        <v>0.989</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3276,34 +3526,40 @@
         </is>
       </c>
       <c r="I42">
-        <v>0.804</v>
+        <v>0.82</v>
       </c>
       <c r="J42">
-        <v>0.905</v>
+        <v>0.517</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N42">
-        <v>0.886</v>
+        <v>11781814</v>
       </c>
       <c r="O42">
-        <v>0.246</v>
+        <v>1095262</v>
       </c>
       <c r="P42">
-        <v>0.9399999999999999</v>
+        <v>6318.37</v>
+      </c>
+      <c r="Q42">
+        <v>875.6799999999999</v>
+      </c>
+      <c r="R42">
+        <v>27504760.9</v>
       </c>
     </row>
     <row r="43">
@@ -3324,12 +3580,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3338,7 +3594,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.98</v>
+        <v>0.84</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3346,34 +3602,40 @@
         </is>
       </c>
       <c r="I43">
-        <v>0.99</v>
+        <v>0.407</v>
       </c>
       <c r="J43">
-        <v>0.72</v>
+        <v>0.753</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N43">
-        <v>0.99</v>
+        <v>5886952</v>
       </c>
       <c r="O43">
-        <v>0.571</v>
+        <v>428034</v>
       </c>
       <c r="P43">
-        <v>0.99</v>
+        <v>1335.55</v>
+      </c>
+      <c r="Q43">
+        <v>161.33</v>
+      </c>
+      <c r="R43">
+        <v>10122087.62</v>
       </c>
     </row>
     <row r="44">
@@ -3394,56 +3656,62 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Mazowiecki regionalny</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G44">
-        <v>0.896</v>
+        <v>0.772</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I44">
-        <v>0.778</v>
+        <v>0.434</v>
       </c>
       <c r="J44">
-        <v>0.767</v>
+        <v>0.597</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N44">
-        <v>0.635</v>
+        <v>6621904</v>
       </c>
       <c r="O44">
-        <v>0.99</v>
+        <v>127493</v>
       </c>
       <c r="P44">
-        <v>0.38</v>
+        <v>876.2</v>
+      </c>
+      <c r="Q44">
+        <v>188.3</v>
+      </c>
+      <c r="R44">
+        <v>3138403.35</v>
       </c>
     </row>
     <row r="45">
@@ -3464,56 +3732,62 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>BE21</t>
+          <t>FRD2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Prov. Antwerpen</t>
+          <t>Haute-Normandie</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G45">
-        <v>0.8100000000000001</v>
+        <v>0.745</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.536</v>
+        <v>0.514</v>
       </c>
       <c r="J45">
-        <v>0.913</v>
+        <v>0.471</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N45">
-        <v>0.617</v>
+        <v>7711156</v>
       </c>
       <c r="O45">
-        <v>0.408</v>
+        <v>305753</v>
       </c>
       <c r="P45">
-        <v>0.358</v>
+        <v>1916.5</v>
+      </c>
+      <c r="Q45">
+        <v>85.91</v>
+      </c>
+      <c r="R45">
+        <v>9497045.289999999</v>
       </c>
     </row>
     <row r="46">
@@ -3534,21 +3808,21 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>DEA1</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G46">
-        <v>0.774</v>
+        <v>0.728</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3556,34 +3830,40 @@
         </is>
       </c>
       <c r="I46">
-        <v>0.767</v>
+        <v>0.378</v>
       </c>
       <c r="J46">
-        <v>0.582</v>
+        <v>0.611</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N46">
-        <v>0.626</v>
+        <v>5677884</v>
       </c>
       <c r="O46">
-        <v>0.977</v>
+        <v>175700</v>
       </c>
       <c r="P46">
-        <v>0.375</v>
+        <v>548.22</v>
+      </c>
+      <c r="Q46">
+        <v>66.22</v>
+      </c>
+      <c r="R46">
+        <v>4154925.1</v>
       </c>
     </row>
     <row r="47">
@@ -3604,21 +3884,21 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DK04</t>
+          <t>DE14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Tübingen</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G47">
-        <v>0.01</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3626,34 +3906,40 @@
         </is>
       </c>
       <c r="I47">
-        <v>0.024</v>
+        <v>0.018</v>
       </c>
       <c r="J47">
-        <v>0.01</v>
+        <v>0.154</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N47">
-        <v>0.023</v>
+        <v>0</v>
       </c>
       <c r="O47">
-        <v>0.02</v>
+        <v>133351</v>
       </c>
       <c r="P47">
-        <v>0.024</v>
+        <v>467.22</v>
+      </c>
+      <c r="Q47">
+        <v>154.6</v>
+      </c>
+      <c r="R47">
+        <v>2094468.62</v>
       </c>
     </row>
     <row r="48">
@@ -3674,12 +3960,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DE14</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tübingen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3688,7 +3974,7 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.027</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3696,10 +3982,10 @@
         </is>
       </c>
       <c r="I48">
-        <v>0.064</v>
+        <v>0.042</v>
       </c>
       <c r="J48">
-        <v>0.014</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3708,7 +3994,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3717,13 +4003,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>0.055</v>
+        <v>0</v>
       </c>
       <c r="O48">
-        <v>0.08</v>
+        <v>503456</v>
       </c>
       <c r="P48">
-        <v>0.036</v>
+        <v>1763.96</v>
+      </c>
+      <c r="Q48">
+        <v>583.6900000000001</v>
+      </c>
+      <c r="R48">
+        <v>7907499.24</v>
       </c>
     </row>
     <row r="49">
@@ -3744,21 +4036,21 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DEB2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Trier</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G49">
-        <v>0.028</v>
+        <v>0.075</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -3766,19 +4058,19 @@
         </is>
       </c>
       <c r="I49">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="J49">
-        <v>0.07099999999999999</v>
+        <v>0.298</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3787,13 +4079,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>0.01</v>
+        <v>5049</v>
       </c>
       <c r="P49">
-        <v>0.015</v>
+        <v>17.69</v>
+      </c>
+      <c r="Q49">
+        <v>5.85</v>
+      </c>
+      <c r="R49">
+        <v>79301.87</v>
       </c>
     </row>
     <row r="50">
@@ -3814,21 +4112,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>DE24</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Nordjylland</t>
+          <t>Oberfranken</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G50">
-        <v>0.029</v>
+        <v>0.075</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -3836,34 +4134,40 @@
         </is>
       </c>
       <c r="I50">
-        <v>0.014</v>
+        <v>0.015</v>
       </c>
       <c r="J50">
-        <v>0.075</v>
+        <v>0.206</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N50">
-        <v>0.013</v>
+        <v>0</v>
       </c>
       <c r="O50">
-        <v>0.013</v>
+        <v>80234</v>
       </c>
       <c r="P50">
-        <v>0.014</v>
+        <v>281.12</v>
+      </c>
+      <c r="Q50">
+        <v>93.02</v>
+      </c>
+      <c r="R50">
+        <v>1260190.55</v>
       </c>
     </row>
     <row r="51">
@@ -3884,21 +4188,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DEB2</t>
+          <t>DK05</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trier</t>
+          <t>Nordjylland</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G51">
-        <v>0.034</v>
+        <v>0.076</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -3906,19 +4210,19 @@
         </is>
       </c>
       <c r="I51">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J51">
-        <v>0.107</v>
+        <v>0.299</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3927,13 +4231,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>0.013</v>
+        <v>8724</v>
       </c>
       <c r="P51">
-        <v>0.011</v>
+        <v>37.34</v>
+      </c>
+      <c r="Q51">
+        <v>5.85</v>
+      </c>
+      <c r="R51">
+        <v>295450.48</v>
       </c>
     </row>
     <row r="52">
@@ -3968,42 +4278,48 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.99</v>
+        <v>0.303</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I52">
-        <v>0.99</v>
+        <v>0.112</v>
       </c>
       <c r="J52">
-        <v>0.8090000000000001</v>
+        <v>0.371</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N52">
-        <v>0.99</v>
+        <v>2160</v>
       </c>
       <c r="O52">
-        <v>0.99</v>
+        <v>1620071</v>
       </c>
       <c r="P52">
-        <v>0.99</v>
+        <v>582.3200000000001</v>
+      </c>
+      <c r="Q52">
+        <v>317.06</v>
+      </c>
+      <c r="R52">
+        <v>18630485.45</v>
       </c>
     </row>
     <row r="53">
@@ -4024,32 +4340,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>IE05</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G53">
-        <v>0.5659999999999999</v>
+        <v>0.295</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I53">
-        <v>0.391</v>
+        <v>0.107</v>
       </c>
       <c r="J53">
-        <v>0.676</v>
+        <v>0.372</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4058,22 +4374,28 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N53">
-        <v>0.224</v>
+        <v>85614</v>
       </c>
       <c r="O53">
-        <v>0.655</v>
+        <v>1449770</v>
       </c>
       <c r="P53">
-        <v>0.294</v>
+        <v>129.9</v>
+      </c>
+      <c r="Q53">
+        <v>33.85</v>
+      </c>
+      <c r="R53">
+        <v>11019168.12</v>
       </c>
     </row>
     <row r="54">
@@ -4094,12 +4416,12 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4108,18 +4430,18 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.5610000000000001</v>
+        <v>0.247</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I54">
-        <v>0.311</v>
+        <v>0.103</v>
       </c>
       <c r="J54">
-        <v>0.834</v>
+        <v>0.273</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4128,22 +4450,28 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N54">
-        <v>0.228</v>
+        <v>63513</v>
       </c>
       <c r="O54">
-        <v>0.115</v>
+        <v>1408724</v>
       </c>
       <c r="P54">
-        <v>0.59</v>
+        <v>126.23</v>
+      </c>
+      <c r="Q54">
+        <v>32.89</v>
+      </c>
+      <c r="R54">
+        <v>10707192.78</v>
       </c>
     </row>
     <row r="55">
@@ -4164,32 +4492,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Śląskie</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G55">
-        <v>0.541</v>
+        <v>0.207</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I55">
-        <v>0.405</v>
+        <v>0.04</v>
       </c>
       <c r="J55">
-        <v>0.595</v>
+        <v>0.502</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4198,22 +4526,28 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N55">
-        <v>0.405</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>0.405</v>
+        <v>475117</v>
       </c>
       <c r="P55">
-        <v>0.405</v>
+        <v>127.48</v>
+      </c>
+      <c r="Q55">
+        <v>208.77</v>
+      </c>
+      <c r="R55">
+        <v>5406529.91</v>
       </c>
     </row>
     <row r="56">
@@ -4234,32 +4568,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G56">
-        <v>0.524</v>
+        <v>0.205</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I56">
-        <v>0.302</v>
+        <v>0.052</v>
       </c>
       <c r="J56">
-        <v>0.748</v>
+        <v>0.378</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4268,22 +4602,28 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N56">
-        <v>0.222</v>
+        <v>17751</v>
       </c>
       <c r="O56">
-        <v>0.112</v>
+        <v>653342</v>
       </c>
       <c r="P56">
-        <v>0.573</v>
+        <v>234.84</v>
+      </c>
+      <c r="Q56">
+        <v>127.86</v>
+      </c>
+      <c r="R56">
+        <v>7513299.44</v>
       </c>
     </row>
     <row r="57">
@@ -4304,21 +4644,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G57">
-        <v>0.01</v>
+        <v>0.038</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4326,10 +4666,10 @@
         </is>
       </c>
       <c r="I57">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="J57">
-        <v>0.01</v>
+        <v>0.092</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4338,22 +4678,28 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N57">
-        <v>0.014</v>
+        <v>0</v>
       </c>
       <c r="O57">
-        <v>0.013</v>
+        <v>11849</v>
       </c>
       <c r="P57">
-        <v>0.026</v>
+        <v>4.75</v>
+      </c>
+      <c r="Q57">
+        <v>3.33</v>
+      </c>
+      <c r="R57">
+        <v>165823.84</v>
       </c>
     </row>
     <row r="58">
@@ -4374,21 +4720,21 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G58">
-        <v>0.022</v>
+        <v>0.043</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4396,10 +4742,10 @@
         </is>
       </c>
       <c r="I58">
-        <v>0.013</v>
+        <v>0.025</v>
       </c>
       <c r="J58">
-        <v>0.044</v>
+        <v>0.048</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4408,22 +4754,28 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N58">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O58">
-        <v>0.011</v>
+        <v>246236</v>
       </c>
       <c r="P58">
-        <v>0.017</v>
+        <v>95.42</v>
+      </c>
+      <c r="Q58">
+        <v>65.58</v>
+      </c>
+      <c r="R58">
+        <v>2510994.84</v>
       </c>
     </row>
     <row r="59">
@@ -4444,21 +4796,21 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>SE31</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Norra Mellansverige</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G59">
-        <v>0.034</v>
+        <v>0.045</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4466,10 +4818,10 @@
         </is>
       </c>
       <c r="I59">
-        <v>0.014</v>
+        <v>0.028</v>
       </c>
       <c r="J59">
-        <v>0.083</v>
+        <v>0.047</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4478,22 +4830,28 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N59">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O59">
-        <v>0.012</v>
+        <v>281503</v>
       </c>
       <c r="P59">
-        <v>0.019</v>
+        <v>109.08</v>
+      </c>
+      <c r="Q59">
+        <v>74.97</v>
+      </c>
+      <c r="R59">
+        <v>2870628.31</v>
       </c>
     </row>
     <row r="60">
@@ -4514,21 +4872,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>NL22</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Nordjylland</t>
+          <t>Gelderland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G60">
-        <v>0.056</v>
+        <v>0.052</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4536,19 +4894,19 @@
         </is>
       </c>
       <c r="I60">
-        <v>0.017</v>
+        <v>0.015</v>
       </c>
       <c r="J60">
-        <v>0.178</v>
+        <v>0.109</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
@@ -4557,13 +4915,19 @@
         </is>
       </c>
       <c r="N60">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="O60">
-        <v>0.013</v>
+        <v>83420</v>
       </c>
       <c r="P60">
-        <v>0.023</v>
+        <v>33.44</v>
+      </c>
+      <c r="Q60">
+        <v>23.42</v>
+      </c>
+      <c r="R60">
+        <v>1167480.69</v>
       </c>
     </row>
     <row r="61">
@@ -4584,21 +4948,21 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DK04</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G61">
-        <v>0.06</v>
+        <v>0.053</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4606,19 +4970,19 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.029</v>
+        <v>0.011</v>
       </c>
       <c r="J61">
-        <v>0.114</v>
+        <v>0.15</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -4627,13 +4991,19 @@
         </is>
       </c>
       <c r="N61">
-        <v>0.024</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>0.018</v>
+        <v>17686</v>
       </c>
       <c r="P61">
-        <v>0.046</v>
+        <v>7.09</v>
+      </c>
+      <c r="Q61">
+        <v>4.96</v>
+      </c>
+      <c r="R61">
+        <v>247519.55</v>
       </c>
     </row>
     <row r="62">
@@ -4654,56 +5024,62 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>ES52</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Świętokrzyskie</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G62">
-        <v>0.99</v>
+        <v>0.655</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I62">
-        <v>0.99</v>
+        <v>0.282</v>
       </c>
       <c r="J62">
-        <v>0.99</v>
+        <v>0.667</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N62">
-        <v>0.99</v>
+        <v>4132364</v>
       </c>
       <c r="O62">
-        <v>0.508</v>
+        <v>188035</v>
       </c>
       <c r="P62">
-        <v>0.99</v>
+        <v>1349.77</v>
+      </c>
+      <c r="Q62">
+        <v>291.48</v>
+      </c>
+      <c r="R62">
+        <v>1829450.55</v>
       </c>
     </row>
     <row r="63">
@@ -4724,21 +5100,21 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ES52</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Comunitat Valenciana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G63">
-        <v>0.773</v>
+        <v>0.6</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -4746,19 +5122,19 @@
         </is>
       </c>
       <c r="I63">
-        <v>0.869</v>
+        <v>0.295</v>
       </c>
       <c r="J63">
-        <v>0.6899999999999999</v>
+        <v>0.537</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
@@ -4767,13 +5143,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>0.677</v>
+        <v>3690134</v>
       </c>
       <c r="O63">
-        <v>0.804</v>
+        <v>839170</v>
       </c>
       <c r="P63">
-        <v>0.705</v>
+        <v>5441</v>
+      </c>
+      <c r="Q63">
+        <v>249.57</v>
+      </c>
+      <c r="R63">
+        <v>6752400.96</v>
       </c>
     </row>
     <row r="64">
@@ -4794,56 +5176,62 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>PL52</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Opolskie</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G64">
-        <v>0.6889999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I64">
-        <v>0.767</v>
+        <v>0.213</v>
       </c>
       <c r="J64">
-        <v>0.622</v>
+        <v>0.573</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N64">
-        <v>0.597</v>
+        <v>3155406</v>
       </c>
       <c r="O64">
-        <v>0.71</v>
+        <v>75010</v>
       </c>
       <c r="P64">
-        <v>0.622</v>
+        <v>538.4400000000001</v>
+      </c>
+      <c r="Q64">
+        <v>116.28</v>
+      </c>
+      <c r="R64">
+        <v>729794.49</v>
       </c>
     </row>
     <row r="65">
@@ -4864,56 +5252,62 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>ES61</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Andalucía</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G65">
-        <v>0.6879999999999999</v>
+        <v>0.518</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I65">
-        <v>0.74</v>
+        <v>0.208</v>
       </c>
       <c r="J65">
-        <v>0.643</v>
+        <v>0.569</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N65">
-        <v>0.418</v>
+        <v>2722191</v>
       </c>
       <c r="O65">
-        <v>0.99</v>
+        <v>429400</v>
       </c>
       <c r="P65">
-        <v>0.455</v>
+        <v>2784.14</v>
+      </c>
+      <c r="Q65">
+        <v>127.71</v>
+      </c>
+      <c r="R65">
+        <v>3455175.59</v>
       </c>
     </row>
     <row r="66">
@@ -4934,32 +5328,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Świętokrzyskie</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G66">
-        <v>0.616</v>
+        <v>0.485</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I66">
-        <v>0.442</v>
+        <v>0.271</v>
       </c>
       <c r="J66">
-        <v>0.867</v>
+        <v>0.384</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -4968,22 +5362,28 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N66">
-        <v>0.252</v>
+        <v>3814216</v>
       </c>
       <c r="O66">
-        <v>0.592</v>
+        <v>341227</v>
       </c>
       <c r="P66">
-        <v>0.272</v>
+        <v>2761.98</v>
+      </c>
+      <c r="Q66">
+        <v>296.49</v>
+      </c>
+      <c r="R66">
+        <v>3575677.42</v>
       </c>
     </row>
     <row r="67">
@@ -5004,21 +5404,21 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DE60</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Noord-Holland</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G67">
-        <v>0.01</v>
+        <v>0.055</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5026,19 +5426,19 @@
         </is>
       </c>
       <c r="I67">
-        <v>0.026</v>
+        <v>0.014</v>
       </c>
       <c r="J67">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5047,13 +5447,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>0.025</v>
+        <v>21420</v>
       </c>
       <c r="O67">
-        <v>0.034</v>
+        <v>48003</v>
       </c>
       <c r="P67">
-        <v>0.017</v>
+        <v>61.65</v>
+      </c>
+      <c r="Q67">
+        <v>16.51</v>
+      </c>
+      <c r="R67">
+        <v>280328.46</v>
       </c>
     </row>
     <row r="68">
@@ -5074,21 +5480,21 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>AT34</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Vorarlberg</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G68">
-        <v>0.023</v>
+        <v>0.057</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5096,19 +5502,19 @@
         </is>
       </c>
       <c r="I68">
-        <v>0.031</v>
+        <v>0.011</v>
       </c>
       <c r="J68">
-        <v>0.028</v>
+        <v>0.175</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5117,13 +5523,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>0.036</v>
+        <v>0</v>
       </c>
       <c r="O68">
-        <v>0.022</v>
+        <v>13056</v>
       </c>
       <c r="P68">
-        <v>0.03</v>
+        <v>181.55</v>
+      </c>
+      <c r="Q68">
+        <v>7.31</v>
+      </c>
+      <c r="R68">
+        <v>151664.14</v>
       </c>
     </row>
     <row r="69">
@@ -5144,21 +5556,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G69">
-        <v>0.027</v>
+        <v>0.06</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5166,34 +5578,40 @@
         </is>
       </c>
       <c r="I69">
-        <v>0.033</v>
+        <v>0.01</v>
       </c>
       <c r="J69">
-        <v>0.034</v>
+        <v>0.202</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N69">
-        <v>0.041</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>0.024</v>
+        <v>7422</v>
       </c>
       <c r="P69">
-        <v>0.028</v>
+        <v>92.06</v>
+      </c>
+      <c r="Q69">
+        <v>12.33</v>
+      </c>
+      <c r="R69">
+        <v>79589.62</v>
       </c>
     </row>
     <row r="70">
@@ -5214,21 +5632,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DE30</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G70">
-        <v>0.032</v>
+        <v>0.061</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5236,19 +5654,19 @@
         </is>
       </c>
       <c r="I70">
-        <v>0.044</v>
+        <v>0.011</v>
       </c>
       <c r="J70">
-        <v>0.032</v>
+        <v>0.195</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
@@ -5257,13 +5675,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>0.039</v>
+        <v>5721</v>
       </c>
       <c r="O70">
-        <v>0.055</v>
+        <v>8989</v>
       </c>
       <c r="P70">
-        <v>0.027</v>
+        <v>11.54</v>
+      </c>
+      <c r="Q70">
+        <v>3.09</v>
+      </c>
+      <c r="R70">
+        <v>52491.98</v>
       </c>
     </row>
     <row r="71">
@@ -5284,21 +5708,21 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G71">
-        <v>0.032</v>
+        <v>0.065</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5306,10 +5730,10 @@
         </is>
       </c>
       <c r="I71">
-        <v>0.016</v>
+        <v>0.043</v>
       </c>
       <c r="J71">
-        <v>0.092</v>
+        <v>0.056</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5318,22 +5742,28 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N71">
-        <v>0.021</v>
+        <v>451284</v>
       </c>
       <c r="O71">
-        <v>0.01</v>
+        <v>76550</v>
       </c>
       <c r="P71">
-        <v>0.019</v>
+        <v>949.49</v>
+      </c>
+      <c r="Q71">
+        <v>127.18</v>
+      </c>
+      <c r="R71">
+        <v>820916.01</v>
       </c>
     </row>
     <row r="72">
@@ -5354,12 +5784,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEA5</t>
+          <t>DEA1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Düsseldorf</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5379,16 +5809,16 @@
         <v>0.99</v>
       </c>
       <c r="J72">
-        <v>0.93</v>
+        <v>0.429</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
@@ -5397,13 +5827,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>0.99</v>
+        <v>13655108</v>
       </c>
       <c r="O72">
-        <v>0.99</v>
+        <v>1927815</v>
       </c>
       <c r="P72">
-        <v>0.608</v>
+        <v>8435.620000000001</v>
+      </c>
+      <c r="Q72">
+        <v>1827.63</v>
+      </c>
+      <c r="R72">
+        <v>22142953.22</v>
       </c>
     </row>
     <row r="73">
@@ -5424,32 +5860,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>SK04</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Východné Slovensko</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G73">
-        <v>0.964</v>
+        <v>0.769</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I73">
-        <v>0.881</v>
+        <v>0.362</v>
       </c>
       <c r="J73">
-        <v>0.99</v>
+        <v>0.711</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5458,22 +5894,28 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N73">
-        <v>0.465</v>
+        <v>5388284</v>
       </c>
       <c r="O73">
-        <v>0.849</v>
+        <v>215473</v>
       </c>
       <c r="P73">
-        <v>0.99</v>
+        <v>2258.03</v>
+      </c>
+      <c r="Q73">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="R73">
+        <v>4826706.62</v>
       </c>
     </row>
     <row r="74">
@@ -5494,56 +5936,62 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DEA1</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G74">
-        <v>0.871</v>
+        <v>0.738</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I74">
-        <v>0.861</v>
+        <v>0.363</v>
       </c>
       <c r="J74">
-        <v>0.829</v>
+        <v>0.653</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N74">
-        <v>0.861</v>
+        <v>4351958</v>
       </c>
       <c r="O74">
-        <v>0.861</v>
+        <v>1267020</v>
       </c>
       <c r="P74">
-        <v>0.529</v>
+        <v>985.3</v>
+      </c>
+      <c r="Q74">
+        <v>393.91</v>
+      </c>
+      <c r="R74">
+        <v>9139782.189999999</v>
       </c>
     </row>
     <row r="75">
@@ -5564,56 +6012,62 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G75">
-        <v>0.556</v>
+        <v>0.706</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I75">
-        <v>0.44</v>
+        <v>0.488</v>
       </c>
       <c r="J75">
-        <v>0.66</v>
+        <v>0.446</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N75">
-        <v>0.216</v>
+        <v>1805137</v>
       </c>
       <c r="O75">
-        <v>0.719</v>
+        <v>5793495</v>
       </c>
       <c r="P75">
-        <v>0.218</v>
+        <v>4505.34</v>
+      </c>
+      <c r="Q75">
+        <v>1801.16</v>
+      </c>
+      <c r="R75">
+        <v>41791998.74</v>
       </c>
     </row>
     <row r="76">
@@ -5634,41 +6088,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>AT31</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Attiki</t>
+          <t>Oberösterreich</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="G76">
-        <v>0.52</v>
+        <v>0.7</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I76">
-        <v>0.276</v>
+        <v>0.591</v>
       </c>
       <c r="J76">
-        <v>0.921</v>
+        <v>0.362</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
@@ -5677,13 +6131,19 @@
         </is>
       </c>
       <c r="N76">
-        <v>0.08699999999999999</v>
+        <v>8752298</v>
       </c>
       <c r="O76">
-        <v>0.522</v>
+        <v>493985</v>
       </c>
       <c r="P76">
-        <v>0.115</v>
+        <v>4424.66</v>
+      </c>
+      <c r="Q76">
+        <v>108.52</v>
+      </c>
+      <c r="R76">
+        <v>8330510.44</v>
       </c>
     </row>
     <row r="77">
@@ -5704,21 +6164,21 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LT01</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sostinės regionas</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G77">
-        <v>0.01</v>
+        <v>0.041</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -5726,10 +6186,10 @@
         </is>
       </c>
       <c r="I77">
-        <v>0.01</v>
+        <v>0.021</v>
       </c>
       <c r="J77">
-        <v>0.01</v>
+        <v>0.052</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -5738,22 +6198,28 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N77">
-        <v>0.01</v>
+        <v>25406</v>
       </c>
       <c r="O77">
-        <v>0.01</v>
+        <v>155611</v>
       </c>
       <c r="P77">
-        <v>0.01</v>
+        <v>680.91</v>
+      </c>
+      <c r="Q77">
+        <v>147.52</v>
+      </c>
+      <c r="R77">
+        <v>1787355.89</v>
       </c>
     </row>
     <row r="78">
@@ -5774,21 +6240,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EE00</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Eesti</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>EE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -5796,34 +6262,40 @@
         </is>
       </c>
       <c r="I78">
-        <v>0.011</v>
+        <v>0.027</v>
       </c>
       <c r="J78">
-        <v>0.187</v>
+        <v>0.06</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N78">
-        <v>0.01</v>
+        <v>15369</v>
       </c>
       <c r="O78">
-        <v>0.011</v>
+        <v>247142</v>
       </c>
       <c r="P78">
-        <v>0.012</v>
+        <v>1081.43</v>
+      </c>
+      <c r="Q78">
+        <v>234.3</v>
+      </c>
+      <c r="R78">
+        <v>2838676.28</v>
       </c>
     </row>
     <row r="79">
@@ -5844,21 +6316,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G79">
-        <v>0.051</v>
+        <v>0.057</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -5866,10 +6338,10 @@
         </is>
       </c>
       <c r="I79">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="J79">
-        <v>0.172</v>
+        <v>0.161</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -5878,7 +6350,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
@@ -5887,13 +6359,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>0.013</v>
+        <v>27783</v>
       </c>
       <c r="P79">
-        <v>0.018</v>
+        <v>317.36</v>
+      </c>
+      <c r="Q79">
+        <v>46.82</v>
+      </c>
+      <c r="R79">
+        <v>563796.62</v>
       </c>
     </row>
     <row r="80">
@@ -5914,21 +6392,21 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LT02</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Vidurio ir vakarų Lietuvos regionas</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.055</v>
+        <v>0.057</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -5936,10 +6414,10 @@
         </is>
       </c>
       <c r="I80">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J80">
-        <v>0.269</v>
+        <v>0.188</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -5948,22 +6426,28 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N80">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O80">
-        <v>0.011</v>
+        <v>4410</v>
       </c>
       <c r="P80">
-        <v>0.011</v>
+        <v>50.38</v>
+      </c>
+      <c r="Q80">
+        <v>7.43</v>
+      </c>
+      <c r="R80">
+        <v>89498.88</v>
       </c>
     </row>
     <row r="81">
@@ -5984,21 +6468,21 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>ES23</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>La Rioja</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G81">
-        <v>0.058</v>
+        <v>0.065</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6009,7 +6493,7 @@
         <v>0.012</v>
       </c>
       <c r="J81">
-        <v>0.276</v>
+        <v>0.204</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6018,22 +6502,28 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N81">
-        <v>0.011</v>
+        <v>21</v>
       </c>
       <c r="O81">
-        <v>0.011</v>
+        <v>28454</v>
       </c>
       <c r="P81">
-        <v>0.012</v>
+        <v>325.03</v>
+      </c>
+      <c r="Q81">
+        <v>47.95</v>
+      </c>
+      <c r="R81">
+        <v>577415.5600000001</v>
       </c>
     </row>
     <row r="82">
@@ -6068,27 +6558,27 @@
         </is>
       </c>
       <c r="G82">
-        <v>0.99</v>
+        <v>0.483</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I82">
-        <v>0.99</v>
+        <v>0.179</v>
       </c>
       <c r="J82">
-        <v>0.99</v>
+        <v>0.576</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
@@ -6097,13 +6587,19 @@
         </is>
       </c>
       <c r="N82">
-        <v>0.99</v>
+        <v>10280</v>
       </c>
       <c r="O82">
-        <v>0.99</v>
+        <v>2681294</v>
       </c>
       <c r="P82">
-        <v>0.99</v>
+        <v>799.1900000000001</v>
+      </c>
+      <c r="Q82">
+        <v>1215.52</v>
+      </c>
+      <c r="R82">
+        <v>42329157.17</v>
       </c>
     </row>
     <row r="83">
@@ -6124,56 +6620,62 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>ITH5</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Emilia-Romagna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G83">
-        <v>0.727</v>
+        <v>0.391</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I83">
-        <v>0.719</v>
+        <v>0.11</v>
       </c>
       <c r="J83">
-        <v>0.74</v>
+        <v>0.621</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N83">
-        <v>0.6879999999999999</v>
+        <v>0</v>
       </c>
       <c r="O83">
-        <v>0.926</v>
+        <v>1586927</v>
       </c>
       <c r="P83">
-        <v>0.544</v>
+        <v>473</v>
+      </c>
+      <c r="Q83">
+        <v>719.41</v>
+      </c>
+      <c r="R83">
+        <v>25052561.22</v>
       </c>
     </row>
     <row r="84">
@@ -6194,12 +6696,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6208,18 +6710,18 @@
         </is>
       </c>
       <c r="G84">
-        <v>0.699</v>
+        <v>0.373</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I84">
-        <v>0.59</v>
+        <v>0.108</v>
       </c>
       <c r="J84">
-        <v>0.834</v>
+        <v>0.579</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6228,22 +6730,28 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N84">
-        <v>0.589</v>
+        <v>0</v>
       </c>
       <c r="O84">
-        <v>0.59</v>
+        <v>1553753</v>
       </c>
       <c r="P84">
-        <v>0.59</v>
+        <v>463.12</v>
+      </c>
+      <c r="Q84">
+        <v>704.37</v>
+      </c>
+      <c r="R84">
+        <v>24528846.55</v>
       </c>
     </row>
     <row r="85">
@@ -6264,12 +6772,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITC1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6278,19 +6786,19 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.665</v>
+        <v>0.302</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I85">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="J85">
         <v>0.577</v>
       </c>
-      <c r="J85">
-        <v>0.773</v>
-      </c>
       <c r="K85" t="inlineStr">
         <is>
           <t>Vulnerability-driven</t>
@@ -6298,7 +6806,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -6307,13 +6815,19 @@
         </is>
       </c>
       <c r="N85">
-        <v>0.577</v>
+        <v>4027</v>
       </c>
       <c r="O85">
-        <v>0.578</v>
+        <v>977352</v>
       </c>
       <c r="P85">
-        <v>0.577</v>
+        <v>291.31</v>
+      </c>
+      <c r="Q85">
+        <v>443.07</v>
+      </c>
+      <c r="R85">
+        <v>15429304.02</v>
       </c>
     </row>
     <row r="86">
@@ -6334,32 +6848,32 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>DEA5</t>
+          <t>ES51</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Arnsberg</t>
+          <t>Cataluña</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G86">
-        <v>0.551</v>
+        <v>0.223</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I86">
-        <v>0.46</v>
+        <v>0.059</v>
       </c>
       <c r="J86">
-        <v>0.667</v>
+        <v>0.392</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6368,22 +6882,28 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N86">
-        <v>0.44</v>
+        <v>0</v>
       </c>
       <c r="O86">
-        <v>0.592</v>
+        <v>781678</v>
       </c>
       <c r="P86">
-        <v>0.349</v>
+        <v>336.04</v>
+      </c>
+      <c r="Q86">
+        <v>143.68</v>
+      </c>
+      <c r="R86">
+        <v>12219131.85</v>
       </c>
     </row>
     <row r="87">
@@ -6404,21 +6924,21 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G87">
-        <v>0.01</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6426,34 +6946,40 @@
         </is>
       </c>
       <c r="I87">
-        <v>0.031</v>
+        <v>0.014</v>
       </c>
       <c r="J87">
-        <v>0.01</v>
+        <v>0.197</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N87">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="O87">
-        <v>0.02</v>
+        <v>67103</v>
       </c>
       <c r="P87">
-        <v>0.04</v>
+        <v>52.99</v>
+      </c>
+      <c r="Q87">
+        <v>108.8</v>
+      </c>
+      <c r="R87">
+        <v>2213528.69</v>
       </c>
     </row>
     <row r="88">
@@ -6474,21 +7000,21 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G88">
-        <v>0.034</v>
+        <v>0.076</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -6496,34 +7022,40 @@
         </is>
       </c>
       <c r="I88">
-        <v>0.031</v>
+        <v>0.015</v>
       </c>
       <c r="J88">
-        <v>0.055</v>
+        <v>0.205</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N88">
-        <v>0.034</v>
+        <v>0</v>
       </c>
       <c r="O88">
-        <v>0.011</v>
+        <v>83332</v>
       </c>
       <c r="P88">
-        <v>0.048</v>
+        <v>21.5</v>
+      </c>
+      <c r="Q88">
+        <v>12.69</v>
+      </c>
+      <c r="R88">
+        <v>1354951.28</v>
       </c>
     </row>
     <row r="89">
@@ -6544,21 +7076,21 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G89">
-        <v>0.04</v>
+        <v>0.076</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -6566,10 +7098,10 @@
         </is>
       </c>
       <c r="I89">
-        <v>0.01</v>
+        <v>0.024</v>
       </c>
       <c r="J89">
-        <v>0.227</v>
+        <v>0.129</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -6578,22 +7110,28 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N89">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O89">
-        <v>0.01</v>
+        <v>229602</v>
       </c>
       <c r="P89">
-        <v>0.01</v>
+        <v>181.31</v>
+      </c>
+      <c r="Q89">
+        <v>372.28</v>
+      </c>
+      <c r="R89">
+        <v>7573866.06</v>
       </c>
     </row>
     <row r="90">
@@ -6628,7 +7166,7 @@
         </is>
       </c>
       <c r="G90">
-        <v>0.042</v>
+        <v>0.077</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -6636,19 +7174,19 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.025</v>
+        <v>0.012</v>
       </c>
       <c r="J90">
-        <v>0.096</v>
+        <v>0.267</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6657,13 +7195,19 @@
         </is>
       </c>
       <c r="N90">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="O90">
-        <v>0.025</v>
+        <v>31831</v>
       </c>
       <c r="P90">
-        <v>0.025</v>
+        <v>14.67</v>
+      </c>
+      <c r="Q90">
+        <v>19.2</v>
+      </c>
+      <c r="R90">
+        <v>713568.3100000001</v>
       </c>
     </row>
     <row r="91">
@@ -6684,21 +7228,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G91">
-        <v>0.043</v>
+        <v>0.077</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -6709,7 +7253,7 @@
         <v>0.016</v>
       </c>
       <c r="J91">
-        <v>0.153</v>
+        <v>0.206</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -6718,7 +7262,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6727,13 +7271,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>0.013</v>
+        <v>90316</v>
       </c>
       <c r="P91">
-        <v>0.017</v>
+        <v>71.31999999999999</v>
+      </c>
+      <c r="Q91">
+        <v>146.44</v>
+      </c>
+      <c r="R91">
+        <v>2979241.95</v>
       </c>
     </row>
     <row r="92">
@@ -6768,42 +7318,48 @@
         </is>
       </c>
       <c r="G92">
-        <v>0.99</v>
+        <v>0.258</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I92">
-        <v>0.99</v>
+        <v>0.083</v>
       </c>
       <c r="J92">
-        <v>0.592</v>
+        <v>0.366</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N92">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="O92">
-        <v>0.99</v>
+        <v>1162570</v>
       </c>
       <c r="P92">
-        <v>0.99</v>
+        <v>358.34</v>
+      </c>
+      <c r="Q92">
+        <v>293.89</v>
+      </c>
+      <c r="R92">
+        <v>15617748.1</v>
       </c>
     </row>
     <row r="93">
@@ -6824,32 +7380,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>PL51</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dolnośląskie</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G93">
-        <v>0.703</v>
+        <v>0.205</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I93">
-        <v>0.397</v>
+        <v>0.051</v>
       </c>
       <c r="J93">
-        <v>0.749</v>
+        <v>0.388</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -6858,22 +7414,28 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N93">
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="O93">
-        <v>0.681</v>
+        <v>644073</v>
       </c>
       <c r="P93">
-        <v>0.39</v>
+        <v>198.52</v>
+      </c>
+      <c r="Q93">
+        <v>162.82</v>
+      </c>
+      <c r="R93">
+        <v>8652353.99</v>
       </c>
     </row>
     <row r="94">
@@ -6894,56 +7456,62 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>HU31</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Észak-Magyarország</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G94">
-        <v>0.673</v>
+        <v>0.202</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I94">
-        <v>0.553</v>
+        <v>0.026</v>
       </c>
       <c r="J94">
-        <v>0.493</v>
+        <v>0.723</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N94">
-        <v>0.553</v>
+        <v>0</v>
       </c>
       <c r="O94">
-        <v>0.553</v>
+        <v>260030</v>
       </c>
       <c r="P94">
-        <v>0.553</v>
+        <v>57.56</v>
+      </c>
+      <c r="Q94">
+        <v>23.9</v>
+      </c>
+      <c r="R94">
+        <v>3625407.71</v>
       </c>
     </row>
     <row r="95">
@@ -6964,32 +7532,32 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G95">
-        <v>0.637</v>
+        <v>0.192</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I95">
-        <v>0.368</v>
+        <v>0.029</v>
       </c>
       <c r="J95">
-        <v>0.664</v>
+        <v>0.592</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -6998,22 +7566,28 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N95">
-        <v>0.112</v>
+        <v>0</v>
       </c>
       <c r="O95">
-        <v>0.631</v>
+        <v>307086</v>
       </c>
       <c r="P95">
-        <v>0.362</v>
+        <v>67.98</v>
+      </c>
+      <c r="Q95">
+        <v>28.23</v>
+      </c>
+      <c r="R95">
+        <v>4281480.81</v>
       </c>
     </row>
     <row r="96">
@@ -7034,56 +7608,62 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>HU12</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Pest</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G96">
-        <v>0.603</v>
+        <v>0.184</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I96">
-        <v>0.463</v>
+        <v>0.027</v>
       </c>
       <c r="J96">
-        <v>0.473</v>
+        <v>0.593</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N96">
-        <v>0.382</v>
+        <v>0</v>
       </c>
       <c r="O96">
-        <v>0.51</v>
+        <v>270480</v>
       </c>
       <c r="P96">
-        <v>0.497</v>
+        <v>59.87</v>
+      </c>
+      <c r="Q96">
+        <v>24.86</v>
+      </c>
+      <c r="R96">
+        <v>3771099.29</v>
       </c>
     </row>
     <row r="97">
@@ -7104,12 +7684,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Västsverige</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7118,7 +7698,7 @@
         </is>
       </c>
       <c r="G97">
-        <v>0.01</v>
+        <v>0.039</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7126,10 +7706,10 @@
         </is>
       </c>
       <c r="I97">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="J97">
-        <v>0.01</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7138,22 +7718,28 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N97">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O97">
-        <v>0.012</v>
+        <v>33026</v>
       </c>
       <c r="P97">
-        <v>0.018</v>
+        <v>6.82</v>
+      </c>
+      <c r="Q97">
+        <v>3.91</v>
+      </c>
+      <c r="R97">
+        <v>1062183.55</v>
       </c>
     </row>
     <row r="98">
@@ -7174,12 +7760,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Noord-Holland</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7188,7 +7774,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.018</v>
+        <v>0.04</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7199,7 +7785,7 @@
         <v>0.012</v>
       </c>
       <c r="J98">
-        <v>0.027</v>
+        <v>0.09</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7208,7 +7794,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -7217,13 +7803,19 @@
         </is>
       </c>
       <c r="N98">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="O98">
-        <v>0.012</v>
+        <v>32117</v>
       </c>
       <c r="P98">
-        <v>0.012</v>
+        <v>27.4</v>
+      </c>
+      <c r="Q98">
+        <v>20.87</v>
+      </c>
+      <c r="R98">
+        <v>880457.37</v>
       </c>
     </row>
     <row r="99">
@@ -7244,12 +7836,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7258,7 +7850,7 @@
         </is>
       </c>
       <c r="G99">
-        <v>0.04</v>
+        <v>0.045</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7266,19 +7858,19 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="J99">
-        <v>0.06900000000000001</v>
+        <v>0.118</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M99" t="inlineStr">
@@ -7287,13 +7879,19 @@
         </is>
       </c>
       <c r="N99">
-        <v>0.019</v>
+        <v>0</v>
       </c>
       <c r="O99">
-        <v>0.018</v>
+        <v>16457</v>
       </c>
       <c r="P99">
-        <v>0.017</v>
+        <v>14.04</v>
+      </c>
+      <c r="Q99">
+        <v>10.69</v>
+      </c>
+      <c r="R99">
+        <v>451148.83</v>
       </c>
     </row>
     <row r="100">
@@ -7314,21 +7912,21 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G100">
-        <v>0.047</v>
+        <v>0.046</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7336,34 +7934,40 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.023</v>
+        <v>0.01</v>
       </c>
       <c r="J100">
-        <v>0.073</v>
+        <v>0.133</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N100">
-        <v>0.017</v>
+        <v>0</v>
       </c>
       <c r="O100">
-        <v>0.015</v>
+        <v>1102</v>
       </c>
       <c r="P100">
-        <v>0.036</v>
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="Q100">
+        <v>0.72</v>
+      </c>
+      <c r="R100">
+        <v>30218.26</v>
       </c>
     </row>
     <row r="101">
@@ -7384,12 +7988,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>NL42</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Limburg (NL)</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -7398,7 +8002,7 @@
         </is>
       </c>
       <c r="G101">
-        <v>0.049</v>
+        <v>0.047</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -7406,19 +8010,19 @@
         </is>
       </c>
       <c r="I101">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="J101">
-        <v>0.09</v>
+        <v>0.127</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -7427,13 +8031,19 @@
         </is>
       </c>
       <c r="N101">
-        <v>0.021</v>
+        <v>0</v>
       </c>
       <c r="O101">
-        <v>0.02</v>
+        <v>11297</v>
       </c>
       <c r="P101">
-        <v>0.018</v>
+        <v>9.640000000000001</v>
+      </c>
+      <c r="Q101">
+        <v>7.34</v>
+      </c>
+      <c r="R101">
+        <v>309695.03</v>
       </c>
     </row>
     <row r="102">
@@ -7454,41 +8064,41 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>ITC1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Piemonte</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G102">
-        <v>0.99</v>
+        <v>0.287</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I102">
-        <v>0.99</v>
+        <v>0.078</v>
       </c>
       <c r="J102">
-        <v>0.827</v>
+        <v>0.482</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -7497,13 +8107,19 @@
         </is>
       </c>
       <c r="N102">
-        <v>0.99</v>
+        <v>31994</v>
       </c>
       <c r="O102">
-        <v>0.99</v>
+        <v>1049029</v>
       </c>
       <c r="P102">
-        <v>0.99</v>
+        <v>289.33</v>
+      </c>
+      <c r="Q102">
+        <v>198.49</v>
+      </c>
+      <c r="R102">
+        <v>14063963.73</v>
       </c>
     </row>
     <row r="103">
@@ -7524,56 +8140,62 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G103">
-        <v>0.85</v>
+        <v>0.253</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I103">
-        <v>0.851</v>
+        <v>0.039</v>
       </c>
       <c r="J103">
-        <v>0.711</v>
+        <v>0.747</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N103">
-        <v>0.851</v>
+        <v>20202</v>
       </c>
       <c r="O103">
-        <v>0.851</v>
+        <v>444867</v>
       </c>
       <c r="P103">
-        <v>0.851</v>
+        <v>122.7</v>
+      </c>
+      <c r="Q103">
+        <v>84.17</v>
+      </c>
+      <c r="R103">
+        <v>5964174.91</v>
       </c>
     </row>
     <row r="104">
@@ -7594,32 +8216,32 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G104">
-        <v>0.72</v>
+        <v>0.209</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I104">
-        <v>0.556</v>
+        <v>0.056</v>
       </c>
       <c r="J104">
-        <v>0.783</v>
+        <v>0.366</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -7628,22 +8250,28 @@
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Diversification</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N104">
-        <v>0.556</v>
+        <v>25976</v>
       </c>
       <c r="O104">
-        <v>0.556</v>
+        <v>698500</v>
       </c>
       <c r="P104">
-        <v>0.556</v>
+        <v>192.65</v>
+      </c>
+      <c r="Q104">
+        <v>132.16</v>
+      </c>
+      <c r="R104">
+        <v>9364551.119999999</v>
       </c>
     </row>
     <row r="105">
@@ -7664,32 +8292,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>CZ02</t>
+          <t>HU22</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Střední Čechy</t>
+          <t>Nyugat-Dunántúl</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G105">
-        <v>0.583</v>
+        <v>0.208</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I105">
-        <v>0.317</v>
+        <v>0.029</v>
       </c>
       <c r="J105">
-        <v>0.905</v>
+        <v>0.707</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -7698,22 +8326,28 @@
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N105">
-        <v>0.098</v>
+        <v>8595</v>
       </c>
       <c r="O105">
-        <v>0.442</v>
+        <v>286998</v>
       </c>
       <c r="P105">
-        <v>0.411</v>
+        <v>73.09</v>
+      </c>
+      <c r="Q105">
+        <v>107.16</v>
+      </c>
+      <c r="R105">
+        <v>7478236.76</v>
       </c>
     </row>
     <row r="106">
@@ -7734,32 +8368,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>RO42</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Vest</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G106">
-        <v>0.581</v>
+        <v>0.201</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I106">
-        <v>0.376</v>
+        <v>0.024</v>
       </c>
       <c r="J106">
-        <v>0.755</v>
+        <v>0.786</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -7768,7 +8402,7 @@
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M106" t="inlineStr">
@@ -7777,13 +8411,19 @@
         </is>
       </c>
       <c r="N106">
-        <v>0.139</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>0.696</v>
+        <v>222851</v>
       </c>
       <c r="P106">
-        <v>0.294</v>
+        <v>39.96</v>
+      </c>
+      <c r="Q106">
+        <v>123</v>
+      </c>
+      <c r="R106">
+        <v>4542371.77</v>
       </c>
     </row>
     <row r="107">
@@ -7804,56 +8444,62 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>FRK1</t>
+          <t>NL31</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Auvergne</t>
+          <t>Utrecht</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G107">
+        <v>0.045</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Very Low</t>
+        </is>
+      </c>
+      <c r="I107">
         <v>0.01</v>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>Very Low</t>
-        </is>
-      </c>
-      <c r="I107">
-        <v>0.022</v>
-      </c>
       <c r="J107">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N107">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="O107">
-        <v>0.014</v>
+        <v>4739</v>
       </c>
       <c r="P107">
-        <v>0.032</v>
+        <v>2.85</v>
+      </c>
+      <c r="Q107">
+        <v>1.87</v>
+      </c>
+      <c r="R107">
+        <v>168892.58</v>
       </c>
     </row>
     <row r="108">
@@ -7874,21 +8520,21 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>FRI2</t>
+          <t>NL32</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Limousin</t>
+          <t>Noord-Holland</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G108">
-        <v>0.015</v>
+        <v>0.046</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -7896,34 +8542,40 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.016</v>
+        <v>0.012</v>
       </c>
       <c r="J108">
-        <v>0.023</v>
+        <v>0.116</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N108">
-        <v>0.015</v>
+        <v>0</v>
       </c>
       <c r="O108">
-        <v>0.012</v>
+        <v>26391</v>
       </c>
       <c r="P108">
-        <v>0.022</v>
+        <v>15.86</v>
+      </c>
+      <c r="Q108">
+        <v>10.4</v>
+      </c>
+      <c r="R108">
+        <v>940556.46</v>
       </c>
     </row>
     <row r="109">
@@ -7958,7 +8610,7 @@
         </is>
       </c>
       <c r="G109">
-        <v>0.018</v>
+        <v>0.048</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -7966,34 +8618,40 @@
         </is>
       </c>
       <c r="I109">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J109">
-        <v>0.044</v>
+        <v>0.141</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N109">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>0.011</v>
+        <v>5033</v>
       </c>
       <c r="P109">
-        <v>0.012</v>
+        <v>1.17</v>
+      </c>
+      <c r="Q109">
+        <v>0.75</v>
+      </c>
+      <c r="R109">
+        <v>71680.19</v>
       </c>
     </row>
     <row r="110">
@@ -8014,21 +8672,21 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>NL11</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Groningen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G110">
-        <v>0.026</v>
+        <v>0.052</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8039,31 +8697,37 @@
         <v>0.01</v>
       </c>
       <c r="J110">
-        <v>0.08599999999999999</v>
+        <v>0.16</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N110">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="O110">
-        <v>0.01</v>
+        <v>1961</v>
       </c>
       <c r="P110">
-        <v>0.01</v>
+        <v>1.18</v>
+      </c>
+      <c r="Q110">
+        <v>0.77</v>
+      </c>
+      <c r="R110">
+        <v>69887.89999999999</v>
       </c>
     </row>
     <row r="111">
@@ -8084,21 +8748,21 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>FRJ1</t>
+          <t>NL22</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Languedoc-Roussillon</t>
+          <t>Gelderland</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G111">
-        <v>0.027</v>
+        <v>0.053</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8106,34 +8770,40 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="J111">
-        <v>0.055</v>
+        <v>0.138</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N111">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="O111">
-        <v>0.012</v>
+        <v>33304</v>
       </c>
       <c r="P111">
-        <v>0.023</v>
+        <v>20.01</v>
+      </c>
+      <c r="Q111">
+        <v>13.13</v>
+      </c>
+      <c r="R111">
+        <v>1186925.56</v>
       </c>
     </row>
     <row r="112">
@@ -8168,42 +8838,48 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.99</v>
+        <v>0.184</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I112">
-        <v>0.913</v>
+        <v>0.037</v>
       </c>
       <c r="J112">
-        <v>0.615</v>
+        <v>0.429</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N112">
-        <v>0.913</v>
+        <v>0</v>
       </c>
       <c r="O112">
-        <v>0.773</v>
+        <v>434257</v>
       </c>
       <c r="P112">
-        <v>0.913</v>
+        <v>186.54</v>
+      </c>
+      <c r="Q112">
+        <v>175.44</v>
+      </c>
+      <c r="R112">
+        <v>7172775.27</v>
       </c>
     </row>
     <row r="113">
@@ -8238,42 +8914,48 @@
         </is>
       </c>
       <c r="G113">
-        <v>0.946</v>
+        <v>0.176</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I113">
-        <v>0.99</v>
+        <v>0.04</v>
       </c>
       <c r="J113">
-        <v>0.519</v>
+        <v>0.37</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N113">
-        <v>0.99</v>
+        <v>0</v>
       </c>
       <c r="O113">
-        <v>0.839</v>
+        <v>471415</v>
       </c>
       <c r="P113">
-        <v>0.99</v>
+        <v>202.51</v>
+      </c>
+      <c r="Q113">
+        <v>190.46</v>
+      </c>
+      <c r="R113">
+        <v>7786521.89</v>
       </c>
     </row>
     <row r="114">
@@ -8294,32 +8976,32 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>PL41</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Wielkopolskie</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G114">
-        <v>0.9360000000000001</v>
+        <v>0.159</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I114">
-        <v>0.596</v>
+        <v>0.017</v>
       </c>
       <c r="J114">
-        <v>0.845</v>
+        <v>0.707</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -8328,22 +9010,28 @@
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>Scope 2</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N114">
-        <v>0.213</v>
+        <v>0</v>
       </c>
       <c r="O114">
-        <v>0.99</v>
+        <v>112924</v>
       </c>
       <c r="P114">
-        <v>0.495</v>
+        <v>48.51</v>
+      </c>
+      <c r="Q114">
+        <v>45.62</v>
+      </c>
+      <c r="R114">
+        <v>1865207.41</v>
       </c>
     </row>
     <row r="115">
@@ -8364,12 +9052,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>IE04</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Northern and Western</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8378,18 +9066,18 @@
         </is>
       </c>
       <c r="G115">
-        <v>0.705</v>
+        <v>0.158</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I115">
-        <v>0.315</v>
+        <v>0.025</v>
       </c>
       <c r="J115">
-        <v>0.919</v>
+        <v>0.472</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -8398,22 +9086,28 @@
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Supply Chain</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N115">
-        <v>0.272</v>
+        <v>19579</v>
       </c>
       <c r="O115">
-        <v>0.174</v>
+        <v>223815</v>
       </c>
       <c r="P115">
-        <v>0.455</v>
+        <v>32.8</v>
+      </c>
+      <c r="Q115">
+        <v>23</v>
+      </c>
+      <c r="R115">
+        <v>2144303.04</v>
       </c>
     </row>
     <row r="116">
@@ -8434,12 +9128,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8448,42 +9142,48 @@
         </is>
       </c>
       <c r="G116">
-        <v>0.611</v>
+        <v>0.154</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I116">
-        <v>0.423</v>
+        <v>0.017</v>
       </c>
       <c r="J116">
-        <v>0.52</v>
+        <v>0.658</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N116">
-        <v>0.424</v>
+        <v>0</v>
       </c>
       <c r="O116">
-        <v>0.359</v>
+        <v>116778</v>
       </c>
       <c r="P116">
-        <v>0.424</v>
+        <v>50.16</v>
+      </c>
+      <c r="Q116">
+        <v>47.18</v>
+      </c>
+      <c r="R116">
+        <v>1928854.55</v>
       </c>
     </row>
     <row r="117">
@@ -8504,21 +9204,21 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>ES41</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Castilla y León</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G117">
-        <v>0.01</v>
+        <v>0.033</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -8526,10 +9226,10 @@
         </is>
       </c>
       <c r="I117">
-        <v>0.06</v>
+        <v>0.013</v>
       </c>
       <c r="J117">
-        <v>0.01</v>
+        <v>0.059</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -8538,22 +9238,28 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N117">
-        <v>0.082</v>
+        <v>0</v>
       </c>
       <c r="O117">
-        <v>0.041</v>
+        <v>50495</v>
       </c>
       <c r="P117">
-        <v>0.054</v>
+        <v>51.82</v>
+      </c>
+      <c r="Q117">
+        <v>90.34</v>
+      </c>
+      <c r="R117">
+        <v>2069213.01</v>
       </c>
     </row>
     <row r="118">
@@ -8574,21 +9280,21 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G118">
-        <v>0.028</v>
+        <v>0.033</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -8596,10 +9302,10 @@
         </is>
       </c>
       <c r="I118">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="J118">
-        <v>0.08</v>
+        <v>0.063</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8608,22 +9314,28 @@
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N118">
-        <v>0.026</v>
+        <v>0</v>
       </c>
       <c r="O118">
-        <v>0.011</v>
+        <v>45096</v>
       </c>
       <c r="P118">
-        <v>0.019</v>
+        <v>46.28</v>
+      </c>
+      <c r="Q118">
+        <v>80.68000000000001</v>
+      </c>
+      <c r="R118">
+        <v>1847995.1</v>
       </c>
     </row>
     <row r="119">
@@ -8644,21 +9356,21 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>AT34</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Vorarlberg</t>
+          <t>Västsverige</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G119">
-        <v>0.036</v>
+        <v>0.046</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -8666,34 +9378,40 @@
         </is>
       </c>
       <c r="I119">
-        <v>0.035</v>
+        <v>0.012</v>
       </c>
       <c r="J119">
-        <v>0.056</v>
+        <v>0.113</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>Scope 3</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N119">
-        <v>0.025</v>
+        <v>0</v>
       </c>
       <c r="O119">
-        <v>0.016</v>
+        <v>27314</v>
       </c>
       <c r="P119">
-        <v>0.063</v>
+        <v>34.5</v>
+      </c>
+      <c r="Q119">
+        <v>5.7</v>
+      </c>
+      <c r="R119">
+        <v>809043.0600000001</v>
       </c>
     </row>
     <row r="120">
@@ -8714,12 +9432,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8728,7 +9446,7 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.037</v>
+        <v>0.05</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -8736,34 +9454,40 @@
         </is>
       </c>
       <c r="I120">
-        <v>0.029</v>
+        <v>0.011</v>
       </c>
       <c r="J120">
-        <v>0.06900000000000001</v>
+        <v>0.142</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N120">
-        <v>0.044</v>
+        <v>0</v>
       </c>
       <c r="O120">
-        <v>0.014</v>
+        <v>15262</v>
       </c>
       <c r="P120">
-        <v>0.03</v>
+        <v>19.28</v>
+      </c>
+      <c r="Q120">
+        <v>3.19</v>
+      </c>
+      <c r="R120">
+        <v>452048.49</v>
       </c>
     </row>
     <row r="121">
@@ -8784,21 +9508,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G121">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -8806,19 +9530,19 @@
         </is>
       </c>
       <c r="I121">
-        <v>0.031</v>
+        <v>0.011</v>
       </c>
       <c r="J121">
-        <v>0.07000000000000001</v>
+        <v>0.146</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>Scope 1</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -8827,13 +9551,19 @@
         </is>
       </c>
       <c r="N121">
-        <v>0.042</v>
+        <v>0</v>
       </c>
       <c r="O121">
-        <v>0.024</v>
+        <v>19792</v>
       </c>
       <c r="P121">
-        <v>0.028</v>
+        <v>20.31</v>
+      </c>
+      <c r="Q121">
+        <v>35.41</v>
+      </c>
+      <c r="R121">
+        <v>811071.84</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -489,7 +489,7 @@
         <v>0.99</v>
       </c>
       <c r="J2">
-        <v>0.452</v>
+        <v>0.445</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.841</v>
+        <v>0.838</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         <v>0.927</v>
       </c>
       <c r="J3">
-        <v>0.355</v>
+        <v>0.348</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.8179999999999999</v>
+        <v>0.823</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
         <v>0.335</v>
       </c>
       <c r="J4">
-        <v>0.9340000000000001</v>
+        <v>0.9330000000000001</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="G5">
-        <v>0.742</v>
+        <v>0.743</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -717,7 +717,7 @@
         <v>0.332</v>
       </c>
       <c r="J5">
-        <v>0.784</v>
+        <v>0.779</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -731,7 +731,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N5">
@@ -768,21 +768,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ES61</t>
+          <t>PL92</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Mazowiecki regionalny</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G6">
-        <v>0.697</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.37</v>
+        <v>0.316</v>
       </c>
       <c r="J6">
-        <v>0.626</v>
+        <v>0.716</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -811,19 +811,19 @@
         </is>
       </c>
       <c r="N6">
-        <v>7072349</v>
+        <v>7072574</v>
       </c>
       <c r="O6">
-        <v>2095649</v>
+        <v>708304</v>
       </c>
       <c r="P6">
-        <v>6842.37</v>
+        <v>2758.57</v>
       </c>
       <c r="Q6">
-        <v>993.76</v>
+        <v>1751.62</v>
       </c>
       <c r="R6">
-        <v>68087363.3</v>
+        <v>25342321.43</v>
       </c>
     </row>
     <row r="7">
@@ -869,7 +869,7 @@
         <v>0.152</v>
       </c>
       <c r="J7">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.028</v>
+        <v>0.02</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -996,21 +996,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>FRM0</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Corse</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G9">
-        <v>0.039</v>
+        <v>0.052</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1018,10 +1018,10 @@
         </is>
       </c>
       <c r="I9">
-        <v>0.02</v>
+        <v>0.011</v>
       </c>
       <c r="J9">
-        <v>0.182</v>
+        <v>0.503</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
@@ -1035,23 +1035,23 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N9">
-        <v>30577</v>
+        <v>0</v>
       </c>
       <c r="O9">
-        <v>224042</v>
+        <v>22340</v>
       </c>
       <c r="P9">
-        <v>849.3200000000001</v>
+        <v>143.28</v>
       </c>
       <c r="Q9">
-        <v>205.62</v>
+        <v>11.63</v>
       </c>
       <c r="R9">
-        <v>7843142.39</v>
+        <v>1239223.42</v>
       </c>
     </row>
     <row r="10">
@@ -1072,21 +1072,21 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G10">
-        <v>0.044</v>
+        <v>0.057</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1094,10 +1094,10 @@
         </is>
       </c>
       <c r="I10">
-        <v>0.033</v>
+        <v>0.043</v>
       </c>
       <c r="J10">
-        <v>0.122</v>
+        <v>0.137</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>15555</v>
+        <v>159553</v>
       </c>
       <c r="O10">
-        <v>580469</v>
+        <v>682156</v>
       </c>
       <c r="P10">
-        <v>2127.72</v>
+        <v>1070.18</v>
       </c>
       <c r="Q10">
-        <v>515.12</v>
+        <v>219.43</v>
       </c>
       <c r="R10">
-        <v>19648656.74</v>
+        <v>18864500.95</v>
       </c>
     </row>
     <row r="11">
@@ -1148,21 +1148,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G11">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="I11">
-        <v>0.011</v>
+        <v>0.02</v>
       </c>
       <c r="J11">
-        <v>0.531</v>
+        <v>0.318</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1187,23 +1187,23 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>30577</v>
       </c>
       <c r="O11">
-        <v>22340</v>
+        <v>224042</v>
       </c>
       <c r="P11">
-        <v>143.28</v>
+        <v>849.3200000000001</v>
       </c>
       <c r="Q11">
-        <v>11.63</v>
+        <v>205.62</v>
       </c>
       <c r="R11">
-        <v>1239223.42</v>
+        <v>7843142.39</v>
       </c>
     </row>
     <row r="12">
@@ -1238,7 +1238,7 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.3</v>
+        <v>0.273</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>0.074</v>
       </c>
       <c r="J12">
-        <v>0.552</v>
+        <v>0.509</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1314,7 +1314,7 @@
         </is>
       </c>
       <c r="G13">
-        <v>0.248</v>
+        <v>0.245</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>0.06</v>
       </c>
       <c r="J13">
-        <v>0.472</v>
+        <v>0.506</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
         </is>
       </c>
       <c r="G14">
-        <v>0.245</v>
+        <v>0.223</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>0.058</v>
       </c>
       <c r="J14">
-        <v>0.481</v>
+        <v>0.442</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1452,21 +1452,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRF2</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Champagne-Ardenne</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G15">
-        <v>0.244</v>
+        <v>0.215</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         </is>
       </c>
       <c r="I15">
-        <v>0.051</v>
+        <v>0.028</v>
       </c>
       <c r="J15">
-        <v>0.543</v>
+        <v>0.852</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1486,28 +1486,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N15">
-        <v>602936</v>
+        <v>55969</v>
       </c>
       <c r="O15">
-        <v>41664</v>
+        <v>227355</v>
       </c>
       <c r="P15">
-        <v>207.95</v>
+        <v>592.99</v>
       </c>
       <c r="Q15">
-        <v>35.74</v>
+        <v>307.42</v>
       </c>
       <c r="R15">
-        <v>6021671.25</v>
+        <v>15931427.45</v>
       </c>
     </row>
     <row r="16">
@@ -1528,21 +1528,21 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Champagne-Ardenne</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G16">
-        <v>0.219</v>
+        <v>0.212</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1550,10 +1550,10 @@
         </is>
       </c>
       <c r="I16">
-        <v>0.028</v>
+        <v>0.051</v>
       </c>
       <c r="J16">
-        <v>0.801</v>
+        <v>0.455</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1562,28 +1562,28 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N16">
-        <v>55969</v>
+        <v>602936</v>
       </c>
       <c r="O16">
-        <v>227355</v>
+        <v>41664</v>
       </c>
       <c r="P16">
-        <v>592.99</v>
+        <v>207.95</v>
       </c>
       <c r="Q16">
-        <v>307.42</v>
+        <v>35.74</v>
       </c>
       <c r="R16">
-        <v>15931427.45</v>
+        <v>6021671.25</v>
       </c>
     </row>
     <row r="17">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.043</v>
+        <v>0.044</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>0.013</v>
       </c>
       <c r="J17">
-        <v>0.093</v>
+        <v>0.104</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.055</v>
+        <v>0.047</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1705,11 +1705,11 @@
         <v>0.014</v>
       </c>
       <c r="J18">
-        <v>0.124</v>
+        <v>0.103</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1781,7 +1781,7 @@
         <v>0.012</v>
       </c>
       <c r="J19">
-        <v>0.152</v>
+        <v>0.164</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1832,12 +1832,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="I20">
-        <v>0.013</v>
+        <v>0.014</v>
       </c>
       <c r="J20">
-        <v>0.168</v>
+        <v>0.175</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>44932</v>
+        <v>44811</v>
       </c>
       <c r="O20">
-        <v>9707</v>
+        <v>16508</v>
       </c>
       <c r="P20">
-        <v>104.58</v>
+        <v>177.86</v>
       </c>
       <c r="Q20">
-        <v>65.98</v>
+        <v>112.22</v>
       </c>
       <c r="R20">
-        <v>2309864.7</v>
+        <v>3928249.4</v>
       </c>
     </row>
     <row r="21">
@@ -1908,21 +1908,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G21">
-        <v>0.064</v>
+        <v>0.063</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="I21">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J21">
-        <v>0.169</v>
+        <v>0.222</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>44811</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>16508</v>
+        <v>15665</v>
       </c>
       <c r="P21">
-        <v>177.86</v>
+        <v>97.91</v>
       </c>
       <c r="Q21">
-        <v>112.22</v>
+        <v>34.72</v>
       </c>
       <c r="R21">
-        <v>3928249.4</v>
+        <v>4365634.41</v>
       </c>
     </row>
     <row r="22">
@@ -1998,7 +1998,7 @@
         </is>
       </c>
       <c r="G22">
-        <v>0.191</v>
+        <v>0.167</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>0.028</v>
       </c>
       <c r="J22">
-        <v>0.623</v>
+        <v>0.529</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2074,7 +2074,7 @@
         </is>
       </c>
       <c r="G23">
-        <v>0.159</v>
+        <v>0.158</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         <v>0.016</v>
       </c>
       <c r="J23">
-        <v>0.782</v>
+        <v>0.845</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2136,21 +2136,21 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G24">
-        <v>0.158</v>
+        <v>0.14</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="I24">
-        <v>0.019</v>
+        <v>0.024</v>
       </c>
       <c r="J24">
-        <v>0.639</v>
+        <v>0.448</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2175,23 +2175,23 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N24">
-        <v>9287</v>
+        <v>3736</v>
       </c>
       <c r="O24">
-        <v>131430</v>
+        <v>211234</v>
       </c>
       <c r="P24">
-        <v>400.99</v>
+        <v>524.9</v>
       </c>
       <c r="Q24">
-        <v>152.12</v>
+        <v>202.7</v>
       </c>
       <c r="R24">
-        <v>5025326.92</v>
+        <v>8045446.05</v>
       </c>
     </row>
     <row r="25">
@@ -2237,7 +2237,7 @@
         <v>0.014</v>
       </c>
       <c r="J25">
-        <v>0.696</v>
+        <v>0.76</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N25">
@@ -2288,21 +2288,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>PT11</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PT</t>
         </is>
       </c>
       <c r="G26">
-        <v>0.139</v>
+        <v>0.137</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="I26">
-        <v>0.024</v>
+        <v>0.019</v>
       </c>
       <c r="J26">
-        <v>0.402</v>
+        <v>0.537</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2327,23 +2327,23 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N26">
-        <v>3736</v>
+        <v>9287</v>
       </c>
       <c r="O26">
-        <v>211234</v>
+        <v>131430</v>
       </c>
       <c r="P26">
-        <v>524.9</v>
+        <v>400.99</v>
       </c>
       <c r="Q26">
-        <v>202.7</v>
+        <v>152.12</v>
       </c>
       <c r="R26">
-        <v>8045446.05</v>
+        <v>5025326.92</v>
       </c>
     </row>
     <row r="27">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.022</v>
+        <v>0.033</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2389,7 +2389,7 @@
         <v>0.011</v>
       </c>
       <c r="J27">
-        <v>0.041</v>
+        <v>0.077</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.024</v>
+        <v>0.035</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>0.011</v>
       </c>
       <c r="J28">
-        <v>0.045</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0.039</v>
+        <v>0.049</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2541,11 +2541,11 @@
         <v>0.01</v>
       </c>
       <c r="J29">
-        <v>0.098</v>
+        <v>0.151</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2592,21 +2592,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Noord-Holland</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G30">
-        <v>0.044</v>
+        <v>0.052</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="I30">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J30">
-        <v>0.114</v>
+        <v>0.167</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>16709</v>
+        <v>6963</v>
       </c>
       <c r="P30">
-        <v>13.93</v>
+        <v>26.87</v>
       </c>
       <c r="Q30">
-        <v>14.35</v>
+        <v>13.61</v>
       </c>
       <c r="R30">
-        <v>237599.38</v>
+        <v>195628.64</v>
       </c>
     </row>
     <row r="31">
@@ -2668,21 +2668,21 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G31">
-        <v>0.045</v>
+        <v>0.056</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>0.01</v>
       </c>
       <c r="J31">
-        <v>0.123</v>
+        <v>0.193</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2714,16 +2714,16 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>6963</v>
+        <v>3900</v>
       </c>
       <c r="P31">
-        <v>26.87</v>
+        <v>1.72</v>
       </c>
       <c r="Q31">
-        <v>13.61</v>
+        <v>1.65</v>
       </c>
       <c r="R31">
-        <v>195628.64</v>
+        <v>102071.15</v>
       </c>
     </row>
     <row r="32">
@@ -2758,7 +2758,7 @@
         </is>
       </c>
       <c r="G32">
-        <v>0.247</v>
+        <v>0.254</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2769,7 +2769,7 @@
         <v>0.064</v>
       </c>
       <c r="J32">
-        <v>0.439</v>
+        <v>0.507</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2834,7 +2834,7 @@
         </is>
       </c>
       <c r="G33">
-        <v>0.211</v>
+        <v>0.219</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>0.051</v>
       </c>
       <c r="J33">
-        <v>0.411</v>
+        <v>0.481</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ES24</t>
+          <t>ITC4</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aragón</t>
+          <t>Lombardia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G34">
-        <v>0.19</v>
+        <v>0.188</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="I34">
-        <v>0.066</v>
+        <v>0.04</v>
       </c>
       <c r="J34">
-        <v>0.258</v>
+        <v>0.458</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2935,23 +2935,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N34">
-        <v>879921</v>
+        <v>290853</v>
       </c>
       <c r="O34">
-        <v>12334</v>
+        <v>187035</v>
       </c>
       <c r="P34">
-        <v>159.54</v>
+        <v>1310.58</v>
       </c>
       <c r="Q34">
-        <v>41.64</v>
+        <v>521.46</v>
       </c>
       <c r="R34">
-        <v>729741.4399999999</v>
+        <v>7730536.47</v>
       </c>
     </row>
     <row r="35">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G35">
-        <v>0.181</v>
+        <v>0.187</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="I35">
-        <v>0.04</v>
+        <v>0.029</v>
       </c>
       <c r="J35">
-        <v>0.388</v>
+        <v>0.612</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3011,23 +3011,23 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N35">
-        <v>290853</v>
+        <v>295376</v>
       </c>
       <c r="O35">
-        <v>187035</v>
+        <v>13765</v>
       </c>
       <c r="P35">
-        <v>1310.58</v>
+        <v>64.03</v>
       </c>
       <c r="Q35">
-        <v>521.46</v>
+        <v>32.02</v>
       </c>
       <c r="R35">
-        <v>7730536.47</v>
+        <v>353560.97</v>
       </c>
     </row>
     <row r="36">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.175</v>
+        <v>0.183</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
         <v>0.028</v>
       </c>
       <c r="J36">
-        <v>0.518</v>
+        <v>0.618</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N36">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.015</v>
+        <v>0.02</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>0.017</v>
       </c>
       <c r="J38">
-        <v>0.017</v>
+        <v>0.023</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G39">
-        <v>0.031</v>
+        <v>0.032</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3298,10 +3298,10 @@
         </is>
       </c>
       <c r="I39">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J39">
-        <v>0.052</v>
+        <v>0.074</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>5173</v>
       </c>
       <c r="O39">
-        <v>59629</v>
+        <v>3246</v>
       </c>
       <c r="P39">
-        <v>30.94</v>
+        <v>12.02</v>
       </c>
       <c r="Q39">
-        <v>60.44</v>
+        <v>3.82</v>
       </c>
       <c r="R39">
-        <v>1256929.64</v>
+        <v>203126.32</v>
       </c>
     </row>
     <row r="40">
@@ -3352,21 +3352,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G40">
-        <v>0.043</v>
+        <v>0.041</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3374,14 +3374,14 @@
         </is>
       </c>
       <c r="I40">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J40">
-        <v>0.115</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -3391,23 +3391,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N40">
         <v>0</v>
       </c>
       <c r="O40">
-        <v>6779</v>
+        <v>59629</v>
       </c>
       <c r="P40">
-        <v>10.15</v>
+        <v>30.94</v>
       </c>
       <c r="Q40">
-        <v>5.94</v>
+        <v>60.44</v>
       </c>
       <c r="R40">
-        <v>179503.53</v>
+        <v>1256929.64</v>
       </c>
     </row>
     <row r="41">
@@ -3428,21 +3428,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G41">
-        <v>0.044</v>
+        <v>0.046</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3450,14 +3450,14 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="J41">
-        <v>0.102</v>
+        <v>0.137</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3467,23 +3467,23 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N41">
-        <v>9390</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>22517</v>
+        <v>6779</v>
       </c>
       <c r="P41">
-        <v>11.68</v>
+        <v>10.15</v>
       </c>
       <c r="Q41">
-        <v>22.82</v>
+        <v>5.94</v>
       </c>
       <c r="R41">
-        <v>474630.56</v>
+        <v>179503.53</v>
       </c>
     </row>
     <row r="42">
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="G42">
-        <v>0.989</v>
+        <v>0.9370000000000001</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>0.82</v>
       </c>
       <c r="J42">
-        <v>0.517</v>
+        <v>0.514</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.84</v>
+        <v>0.875</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>0.407</v>
       </c>
       <c r="J43">
-        <v>0.753</v>
+        <v>0.903</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3670,18 +3670,18 @@
         </is>
       </c>
       <c r="G44">
-        <v>0.772</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I44">
         <v>0.434</v>
       </c>
       <c r="J44">
-        <v>0.597</v>
+        <v>0.734</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3732,36 +3732,36 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FRD2</t>
+          <t>NL33</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Haute-Normandie</t>
+          <t>Zuid-Holland</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G45">
-        <v>0.745</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.514</v>
+        <v>0.642</v>
       </c>
       <c r="J45">
-        <v>0.471</v>
+        <v>0.491</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N45">
-        <v>7711156</v>
+        <v>8076779</v>
       </c>
       <c r="O45">
-        <v>305753</v>
+        <v>1967937</v>
       </c>
       <c r="P45">
-        <v>1916.5</v>
+        <v>7418.85</v>
       </c>
       <c r="Q45">
-        <v>85.91</v>
+        <v>995.72</v>
       </c>
       <c r="R45">
-        <v>9497045.289999999</v>
+        <v>41477161.69</v>
       </c>
     </row>
     <row r="46">
@@ -3822,7 +3822,7 @@
         </is>
       </c>
       <c r="G46">
-        <v>0.728</v>
+        <v>0.74</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3833,7 +3833,7 @@
         <v>0.378</v>
       </c>
       <c r="J46">
-        <v>0.611</v>
+        <v>0.699</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3847,7 +3847,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N46">
@@ -3884,21 +3884,21 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>DE14</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tübingen</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G47">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="I47">
-        <v>0.018</v>
+        <v>0.011</v>
       </c>
       <c r="J47">
-        <v>0.154</v>
+        <v>0.344</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3923,23 +3923,23 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47">
-        <v>133351</v>
+        <v>15994</v>
       </c>
       <c r="P47">
-        <v>467.22</v>
+        <v>58.89</v>
       </c>
       <c r="Q47">
-        <v>154.6</v>
+        <v>0.5</v>
       </c>
       <c r="R47">
-        <v>2094468.62</v>
+        <v>405895.45</v>
       </c>
     </row>
     <row r="48">
@@ -3960,21 +3960,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DK05</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Nordjylland</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G48">
-        <v>0.07199999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3982,14 +3982,14 @@
         </is>
       </c>
       <c r="I48">
-        <v>0.042</v>
+        <v>0.011</v>
       </c>
       <c r="J48">
-        <v>0.07000000000000001</v>
+        <v>0.364</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -3999,23 +3999,23 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N48">
         <v>0</v>
       </c>
       <c r="O48">
-        <v>503456</v>
+        <v>8724</v>
       </c>
       <c r="P48">
-        <v>1763.96</v>
+        <v>37.34</v>
       </c>
       <c r="Q48">
-        <v>583.6900000000001</v>
+        <v>5.85</v>
       </c>
       <c r="R48">
-        <v>7907499.24</v>
+        <v>295450.48</v>
       </c>
     </row>
     <row r="49">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.075</v>
+        <v>0.081</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
         <v>0.01</v>
       </c>
       <c r="J49">
-        <v>0.298</v>
+        <v>0.372</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4112,12 +4112,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DE24</t>
+          <t>DE14</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Oberfranken</t>
+          <t>Tübingen</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -4126,7 +4126,7 @@
         </is>
       </c>
       <c r="G50">
-        <v>0.075</v>
+        <v>0.082</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="I50">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="J50">
-        <v>0.206</v>
+        <v>0.212</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4158,16 +4158,16 @@
         <v>0</v>
       </c>
       <c r="O50">
-        <v>80234</v>
+        <v>133351</v>
       </c>
       <c r="P50">
-        <v>281.12</v>
+        <v>467.22</v>
       </c>
       <c r="Q50">
-        <v>93.02</v>
+        <v>154.6</v>
       </c>
       <c r="R50">
-        <v>1260190.55</v>
+        <v>2094468.62</v>
       </c>
     </row>
     <row r="51">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>DK04</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nordjylland</t>
+          <t>Midtjylland</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4202,7 +4202,7 @@
         </is>
       </c>
       <c r="G51">
-        <v>0.076</v>
+        <v>0.083</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="I51">
-        <v>0.011</v>
+        <v>0.014</v>
       </c>
       <c r="J51">
-        <v>0.299</v>
+        <v>0.292</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4227,23 +4227,23 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>26250</v>
       </c>
       <c r="O51">
-        <v>8724</v>
+        <v>33023</v>
       </c>
       <c r="P51">
-        <v>37.34</v>
+        <v>141.36</v>
       </c>
       <c r="Q51">
-        <v>5.85</v>
+        <v>22.15</v>
       </c>
       <c r="R51">
-        <v>295450.48</v>
+        <v>1118387.01</v>
       </c>
     </row>
     <row r="52">
@@ -4278,7 +4278,7 @@
         </is>
       </c>
       <c r="G52">
-        <v>0.303</v>
+        <v>0.302</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
         <v>0.112</v>
       </c>
       <c r="J52">
-        <v>0.371</v>
+        <v>0.407</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.295</v>
+        <v>0.274</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>0.107</v>
       </c>
       <c r="J53">
-        <v>0.372</v>
+        <v>0.355</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         </is>
       </c>
       <c r="G54">
-        <v>0.247</v>
+        <v>0.239</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4441,7 +4441,7 @@
         <v>0.103</v>
       </c>
       <c r="J54">
-        <v>0.273</v>
+        <v>0.283</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4492,21 +4492,21 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>ITH3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Veneto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G55">
-        <v>0.207</v>
+        <v>0.211</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4514,10 +4514,10 @@
         </is>
       </c>
       <c r="I55">
-        <v>0.04</v>
+        <v>0.052</v>
       </c>
       <c r="J55">
-        <v>0.502</v>
+        <v>0.439</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4535,19 +4535,19 @@
         </is>
       </c>
       <c r="N55">
-        <v>0</v>
+        <v>17751</v>
       </c>
       <c r="O55">
-        <v>475117</v>
+        <v>653342</v>
       </c>
       <c r="P55">
-        <v>127.48</v>
+        <v>234.84</v>
       </c>
       <c r="Q55">
-        <v>208.77</v>
+        <v>127.86</v>
       </c>
       <c r="R55">
-        <v>5406529.91</v>
+        <v>7513299.44</v>
       </c>
     </row>
     <row r="56">
@@ -4568,21 +4568,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>PL22</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Śląskie</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G56">
-        <v>0.205</v>
+        <v>0.21</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4590,10 +4590,10 @@
         </is>
       </c>
       <c r="I56">
-        <v>0.052</v>
+        <v>0.04</v>
       </c>
       <c r="J56">
-        <v>0.378</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4611,19 +4611,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>17751</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>653342</v>
+        <v>475117</v>
       </c>
       <c r="P56">
-        <v>234.84</v>
+        <v>127.48</v>
       </c>
       <c r="Q56">
-        <v>127.86</v>
+        <v>208.77</v>
       </c>
       <c r="R56">
-        <v>7513299.44</v>
+        <v>5406529.91</v>
       </c>
     </row>
     <row r="57">
@@ -4644,21 +4644,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Västsverige</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G57">
-        <v>0.038</v>
+        <v>0.045</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="I57">
-        <v>0.011</v>
+        <v>0.019</v>
       </c>
       <c r="J57">
-        <v>0.092</v>
+        <v>0.074</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4683,23 +4683,23 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57">
-        <v>11849</v>
+        <v>137837</v>
       </c>
       <c r="P57">
-        <v>4.75</v>
+        <v>12.42</v>
       </c>
       <c r="Q57">
-        <v>3.33</v>
+        <v>4.7</v>
       </c>
       <c r="R57">
-        <v>165823.84</v>
+        <v>1640297.31</v>
       </c>
     </row>
     <row r="58">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>0.025</v>
       </c>
       <c r="J58">
-        <v>0.048</v>
+        <v>0.058</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>0.045</v>
+        <v>0.053</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4821,7 +4821,7 @@
         <v>0.028</v>
       </c>
       <c r="J59">
-        <v>0.047</v>
+        <v>0.066</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4872,21 +4872,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NL22</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Gelderland</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G60">
-        <v>0.052</v>
+        <v>0.057</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4894,14 +4894,14 @@
         </is>
       </c>
       <c r="I60">
-        <v>0.015</v>
+        <v>0.012</v>
       </c>
       <c r="J60">
-        <v>0.109</v>
+        <v>0.178</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4911,23 +4911,23 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>83420</v>
+        <v>25829</v>
       </c>
       <c r="P60">
-        <v>33.44</v>
+        <v>2.33</v>
       </c>
       <c r="Q60">
-        <v>23.42</v>
+        <v>0.88</v>
       </c>
       <c r="R60">
-        <v>1167480.69</v>
+        <v>307377.02</v>
       </c>
     </row>
     <row r="61">
@@ -4948,21 +4948,21 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G61">
-        <v>0.053</v>
+        <v>0.061</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="J61">
-        <v>0.15</v>
+        <v>0.124</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4987,23 +4987,23 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N61">
-        <v>0</v>
+        <v>4331</v>
       </c>
       <c r="O61">
-        <v>17686</v>
+        <v>129489</v>
       </c>
       <c r="P61">
-        <v>7.09</v>
+        <v>11.67</v>
       </c>
       <c r="Q61">
-        <v>4.96</v>
+        <v>4.42</v>
       </c>
       <c r="R61">
-        <v>247519.55</v>
+        <v>1540953.23</v>
       </c>
     </row>
     <row r="62">
@@ -5038,7 +5038,7 @@
         </is>
       </c>
       <c r="G62">
-        <v>0.655</v>
+        <v>0.656</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>0.282</v>
       </c>
       <c r="J62">
-        <v>0.667</v>
+        <v>0.738</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5114,18 +5114,18 @@
         </is>
       </c>
       <c r="G63">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I63">
         <v>0.295</v>
       </c>
       <c r="J63">
-        <v>0.537</v>
+        <v>0.586</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="G64">
-        <v>0.527</v>
+        <v>0.544</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5201,7 +5201,7 @@
         <v>0.213</v>
       </c>
       <c r="J64">
-        <v>0.573</v>
+        <v>0.676</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="G65">
-        <v>0.518</v>
+        <v>0.525</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5277,7 +5277,7 @@
         <v>0.208</v>
       </c>
       <c r="J65">
-        <v>0.569</v>
+        <v>0.646</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N65">
@@ -5342,7 +5342,7 @@
         </is>
       </c>
       <c r="G66">
-        <v>0.485</v>
+        <v>0.518</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>0.271</v>
       </c>
       <c r="J66">
-        <v>0.384</v>
+        <v>0.481</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5404,21 +5404,21 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Noord-Holland</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G67">
-        <v>0.055</v>
+        <v>0.063</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="I67">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J67">
-        <v>0.126</v>
+        <v>0.226</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5447,19 +5447,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>21420</v>
+        <v>0</v>
       </c>
       <c r="O67">
-        <v>48003</v>
+        <v>13056</v>
       </c>
       <c r="P67">
-        <v>61.65</v>
+        <v>181.55</v>
       </c>
       <c r="Q67">
-        <v>16.51</v>
+        <v>7.31</v>
       </c>
       <c r="R67">
-        <v>280328.46</v>
+        <v>151664.14</v>
       </c>
     </row>
     <row r="68">
@@ -5480,21 +5480,21 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G68">
-        <v>0.057</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5502,10 +5502,10 @@
         </is>
       </c>
       <c r="I68">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J68">
-        <v>0.175</v>
+        <v>0.274</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -5526,16 +5526,16 @@
         <v>0</v>
       </c>
       <c r="O68">
-        <v>13056</v>
+        <v>7422</v>
       </c>
       <c r="P68">
-        <v>181.55</v>
+        <v>92.06</v>
       </c>
       <c r="Q68">
-        <v>7.31</v>
+        <v>12.33</v>
       </c>
       <c r="R68">
-        <v>151664.14</v>
+        <v>79589.62</v>
       </c>
     </row>
     <row r="69">
@@ -5556,21 +5556,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DE60</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G69">
-        <v>0.06</v>
+        <v>0.076</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="I69">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J69">
-        <v>0.202</v>
+        <v>0.282</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5602,16 +5602,16 @@
         <v>0</v>
       </c>
       <c r="O69">
-        <v>7422</v>
+        <v>34833</v>
       </c>
       <c r="P69">
-        <v>92.06</v>
+        <v>251.63</v>
       </c>
       <c r="Q69">
-        <v>12.33</v>
+        <v>0.7</v>
       </c>
       <c r="R69">
-        <v>79589.62</v>
+        <v>319388.36</v>
       </c>
     </row>
     <row r="70">
@@ -5632,21 +5632,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DE30</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Berlin</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G70">
-        <v>0.061</v>
+        <v>0.078</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>0.011</v>
       </c>
       <c r="J70">
-        <v>0.195</v>
+        <v>0.327</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5675,19 +5675,19 @@
         </is>
       </c>
       <c r="N70">
-        <v>5721</v>
+        <v>0</v>
       </c>
       <c r="O70">
-        <v>8989</v>
+        <v>13747</v>
       </c>
       <c r="P70">
-        <v>11.54</v>
+        <v>170.51</v>
       </c>
       <c r="Q70">
-        <v>3.09</v>
+        <v>22.84</v>
       </c>
       <c r="R70">
-        <v>52491.98</v>
+        <v>147424.69</v>
       </c>
     </row>
     <row r="71">
@@ -5708,21 +5708,21 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>NL23</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Flevoland</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G71">
-        <v>0.065</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5730,19 +5730,19 @@
         </is>
       </c>
       <c r="I71">
-        <v>0.043</v>
+        <v>0.011</v>
       </c>
       <c r="J71">
-        <v>0.056</v>
+        <v>0.384</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5751,19 +5751,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>451284</v>
+        <v>5721</v>
       </c>
       <c r="O71">
-        <v>76550</v>
+        <v>8989</v>
       </c>
       <c r="P71">
-        <v>949.49</v>
+        <v>11.54</v>
       </c>
       <c r="Q71">
-        <v>127.18</v>
+        <v>3.09</v>
       </c>
       <c r="R71">
-        <v>820916.01</v>
+        <v>52491.98</v>
       </c>
     </row>
     <row r="72">
@@ -5809,7 +5809,7 @@
         <v>0.99</v>
       </c>
       <c r="J72">
-        <v>0.429</v>
+        <v>0.474</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         </is>
       </c>
       <c r="G73">
-        <v>0.769</v>
+        <v>0.797</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5885,7 +5885,7 @@
         <v>0.362</v>
       </c>
       <c r="J73">
-        <v>0.711</v>
+        <v>0.843</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5950,7 +5950,7 @@
         </is>
       </c>
       <c r="G74">
-        <v>0.738</v>
+        <v>0.768</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>0.363</v>
       </c>
       <c r="J74">
-        <v>0.653</v>
+        <v>0.782</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5975,7 +5975,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N74">
@@ -6026,7 +6026,7 @@
         </is>
       </c>
       <c r="G75">
-        <v>0.706</v>
+        <v>0.744</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -6037,7 +6037,7 @@
         <v>0.488</v>
       </c>
       <c r="J75">
-        <v>0.446</v>
+        <v>0.546</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         </is>
       </c>
       <c r="G76">
-        <v>0.7</v>
+        <v>0.722</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
         <v>0.591</v>
       </c>
       <c r="J76">
-        <v>0.362</v>
+        <v>0.425</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="G77">
-        <v>0.041</v>
+        <v>0.057</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>0.021</v>
       </c>
       <c r="J77">
-        <v>0.052</v>
+        <v>0.095</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6240,21 +6240,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.051</v>
+        <v>0.063</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6262,14 +6262,14 @@
         </is>
       </c>
       <c r="I78">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="J78">
-        <v>0.06</v>
+        <v>0.201</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6283,19 +6283,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>15369</v>
+        <v>0</v>
       </c>
       <c r="O78">
-        <v>247142</v>
+        <v>35098</v>
       </c>
       <c r="P78">
-        <v>1081.43</v>
+        <v>306.53</v>
       </c>
       <c r="Q78">
-        <v>234.3</v>
+        <v>19.57</v>
       </c>
       <c r="R78">
-        <v>2838676.28</v>
+        <v>587231.1800000001</v>
       </c>
     </row>
     <row r="79">
@@ -6316,21 +6316,21 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G79">
-        <v>0.057</v>
+        <v>0.068</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6338,14 +6338,14 @@
         </is>
       </c>
       <c r="I79">
-        <v>0.012</v>
+        <v>0.027</v>
       </c>
       <c r="J79">
-        <v>0.161</v>
+        <v>0.107</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6359,19 +6359,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>0</v>
+        <v>15369</v>
       </c>
       <c r="O79">
-        <v>27783</v>
+        <v>247142</v>
       </c>
       <c r="P79">
-        <v>317.36</v>
+        <v>1081.43</v>
       </c>
       <c r="Q79">
-        <v>46.82</v>
+        <v>234.3</v>
       </c>
       <c r="R79">
-        <v>563796.62</v>
+        <v>2838676.28</v>
       </c>
     </row>
     <row r="80">
@@ -6392,21 +6392,21 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>FRH0</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Bretagne</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.057</v>
+        <v>0.076</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="I80">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J80">
-        <v>0.188</v>
+        <v>0.292</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6431,23 +6431,23 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80">
-        <v>4410</v>
+        <v>24663</v>
       </c>
       <c r="P80">
-        <v>50.38</v>
+        <v>215.4</v>
       </c>
       <c r="Q80">
-        <v>7.43</v>
+        <v>13.75</v>
       </c>
       <c r="R80">
-        <v>89498.88</v>
+        <v>412654.25</v>
       </c>
     </row>
     <row r="81">
@@ -6468,21 +6468,21 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>DE24</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Oberfranken</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G81">
-        <v>0.065</v>
+        <v>0.078</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6490,10 +6490,10 @@
         </is>
       </c>
       <c r="I81">
-        <v>0.012</v>
+        <v>0.013</v>
       </c>
       <c r="J81">
-        <v>0.204</v>
+        <v>0.277</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6511,19 +6511,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="O81">
-        <v>28454</v>
+        <v>47210</v>
       </c>
       <c r="P81">
-        <v>325.03</v>
+        <v>206.58</v>
       </c>
       <c r="Q81">
-        <v>47.95</v>
+        <v>44.76</v>
       </c>
       <c r="R81">
-        <v>577415.5600000001</v>
+        <v>542256.03</v>
       </c>
     </row>
     <row r="82">
@@ -6558,7 +6558,7 @@
         </is>
       </c>
       <c r="G82">
-        <v>0.483</v>
+        <v>0.421</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>0.179</v>
       </c>
       <c r="J82">
-        <v>0.576</v>
+        <v>0.486</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         </is>
       </c>
       <c r="G83">
-        <v>0.391</v>
+        <v>0.335</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>0.11</v>
       </c>
       <c r="J83">
-        <v>0.621</v>
+        <v>0.508</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6710,7 +6710,7 @@
         </is>
       </c>
       <c r="G84">
-        <v>0.373</v>
+        <v>0.329</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6721,7 +6721,7 @@
         <v>0.108</v>
       </c>
       <c r="J84">
-        <v>0.579</v>
+        <v>0.499</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         </is>
       </c>
       <c r="G85">
-        <v>0.302</v>
+        <v>0.267</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6797,7 +6797,7 @@
         <v>0.07199999999999999</v>
       </c>
       <c r="J85">
-        <v>0.577</v>
+        <v>0.499</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6848,21 +6848,21 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ES51</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Cataluña</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G86">
-        <v>0.223</v>
+        <v>0.217</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6870,10 +6870,10 @@
         </is>
       </c>
       <c r="I86">
-        <v>0.059</v>
+        <v>0.029</v>
       </c>
       <c r="J86">
-        <v>0.392</v>
+        <v>0.838</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6887,23 +6887,23 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N86">
         <v>0</v>
       </c>
       <c r="O86">
-        <v>781678</v>
+        <v>296403</v>
       </c>
       <c r="P86">
-        <v>336.04</v>
+        <v>88.34999999999999</v>
       </c>
       <c r="Q86">
-        <v>143.68</v>
+        <v>134.37</v>
       </c>
       <c r="R86">
-        <v>12219131.85</v>
+        <v>4679270.88</v>
       </c>
     </row>
     <row r="87">
@@ -6924,12 +6924,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>0.07099999999999999</v>
+        <v>0.052</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6946,14 +6946,14 @@
         </is>
       </c>
       <c r="I87">
-        <v>0.014</v>
+        <v>0.024</v>
       </c>
       <c r="J87">
-        <v>0.197</v>
+        <v>0.073</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -6970,16 +6970,16 @@
         <v>0</v>
       </c>
       <c r="O87">
-        <v>67103</v>
+        <v>229602</v>
       </c>
       <c r="P87">
-        <v>52.99</v>
+        <v>181.31</v>
       </c>
       <c r="Q87">
-        <v>108.8</v>
+        <v>372.28</v>
       </c>
       <c r="R87">
-        <v>2213528.69</v>
+        <v>7573866.06</v>
       </c>
     </row>
     <row r="88">
@@ -7000,21 +7000,21 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G88">
-        <v>0.076</v>
+        <v>0.063</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7022,10 +7022,10 @@
         </is>
       </c>
       <c r="I88">
-        <v>0.015</v>
+        <v>0.016</v>
       </c>
       <c r="J88">
-        <v>0.205</v>
+        <v>0.156</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7046,16 +7046,16 @@
         <v>0</v>
       </c>
       <c r="O88">
-        <v>83332</v>
+        <v>90316</v>
       </c>
       <c r="P88">
-        <v>21.5</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="Q88">
-        <v>12.69</v>
+        <v>146.44</v>
       </c>
       <c r="R88">
-        <v>1354951.28</v>
+        <v>2979241.95</v>
       </c>
     </row>
     <row r="89">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="G89">
-        <v>0.076</v>
+        <v>0.065</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="I89">
-        <v>0.024</v>
+        <v>0.014</v>
       </c>
       <c r="J89">
-        <v>0.129</v>
+        <v>0.184</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7122,16 +7122,16 @@
         <v>0</v>
       </c>
       <c r="O89">
-        <v>229602</v>
+        <v>67103</v>
       </c>
       <c r="P89">
-        <v>181.31</v>
+        <v>52.99</v>
       </c>
       <c r="Q89">
-        <v>372.28</v>
+        <v>108.8</v>
       </c>
       <c r="R89">
-        <v>7573866.06</v>
+        <v>2213528.69</v>
       </c>
     </row>
     <row r="90">
@@ -7152,21 +7152,21 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G90">
-        <v>0.077</v>
+        <v>0.068</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.012</v>
+        <v>0.015</v>
       </c>
       <c r="J90">
-        <v>0.267</v>
+        <v>0.185</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7198,16 +7198,16 @@
         <v>0</v>
       </c>
       <c r="O90">
-        <v>31831</v>
+        <v>83332</v>
       </c>
       <c r="P90">
-        <v>14.67</v>
+        <v>21.5</v>
       </c>
       <c r="Q90">
-        <v>19.2</v>
+        <v>12.69</v>
       </c>
       <c r="R90">
-        <v>713568.3100000001</v>
+        <v>1354951.28</v>
       </c>
     </row>
     <row r="91">
@@ -7228,21 +7228,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G91">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="I91">
-        <v>0.016</v>
+        <v>0.017</v>
       </c>
       <c r="J91">
-        <v>0.206</v>
+        <v>0.197</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7271,19 +7271,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>0</v>
+        <v>15491</v>
       </c>
       <c r="O91">
-        <v>90316</v>
+        <v>100385</v>
       </c>
       <c r="P91">
-        <v>71.31999999999999</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="Q91">
-        <v>146.44</v>
+        <v>26.72</v>
       </c>
       <c r="R91">
-        <v>2979241.95</v>
+        <v>2076421.49</v>
       </c>
     </row>
     <row r="92">
@@ -7318,7 +7318,7 @@
         </is>
       </c>
       <c r="G92">
-        <v>0.258</v>
+        <v>0.259</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>0.083</v>
       </c>
       <c r="J92">
-        <v>0.366</v>
+        <v>0.406</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="G93">
-        <v>0.205</v>
+        <v>0.208</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>0.051</v>
       </c>
       <c r="J93">
-        <v>0.388</v>
+        <v>0.44</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>0.026</v>
       </c>
       <c r="J94">
-        <v>0.723</v>
+        <v>0.799</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N94">
@@ -7532,21 +7532,21 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>EL30</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Közép-Dunántúl</t>
+          <t>Attiki</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G95">
-        <v>0.192</v>
+        <v>0.195</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="I95">
-        <v>0.029</v>
+        <v>0.032</v>
       </c>
       <c r="J95">
-        <v>0.592</v>
+        <v>0.625</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7571,23 +7571,23 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N95">
         <v>0</v>
       </c>
       <c r="O95">
-        <v>307086</v>
+        <v>342018</v>
       </c>
       <c r="P95">
-        <v>67.98</v>
+        <v>63.64</v>
       </c>
       <c r="Q95">
-        <v>28.23</v>
+        <v>61.28</v>
       </c>
       <c r="R95">
-        <v>4281480.81</v>
+        <v>2053165.64</v>
       </c>
     </row>
     <row r="96">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>HU12</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Pest</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7622,7 +7622,7 @@
         </is>
       </c>
       <c r="G96">
-        <v>0.184</v>
+        <v>0.194</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="I96">
-        <v>0.027</v>
+        <v>0.029</v>
       </c>
       <c r="J96">
-        <v>0.593</v>
+        <v>0.662</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7647,23 +7647,23 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N96">
         <v>0</v>
       </c>
       <c r="O96">
-        <v>270480</v>
+        <v>307086</v>
       </c>
       <c r="P96">
-        <v>59.87</v>
+        <v>67.98</v>
       </c>
       <c r="Q96">
-        <v>24.86</v>
+        <v>28.23</v>
       </c>
       <c r="R96">
-        <v>3771099.29</v>
+        <v>4281480.81</v>
       </c>
     </row>
     <row r="97">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="G97">
-        <v>0.039</v>
+        <v>0.033</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7709,7 +7709,7 @@
         <v>0.012</v>
       </c>
       <c r="J97">
-        <v>0.08699999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N97">
@@ -7760,21 +7760,21 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Noord-Holland</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G98">
-        <v>0.04</v>
+        <v>0.043</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="I98">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="J98">
-        <v>0.09</v>
+        <v>0.061</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O98">
-        <v>32117</v>
+        <v>171192</v>
       </c>
       <c r="P98">
-        <v>27.4</v>
+        <v>126.02</v>
       </c>
       <c r="Q98">
-        <v>20.87</v>
+        <v>139.07</v>
       </c>
       <c r="R98">
-        <v>880457.37</v>
+        <v>7194730.05</v>
       </c>
     </row>
     <row r="99">
@@ -7836,21 +7836,21 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G99">
-        <v>0.045</v>
+        <v>0.046</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7858,10 +7858,10 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="J99">
-        <v>0.118</v>
+        <v>0.119</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
@@ -7875,23 +7875,23 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N99">
         <v>0</v>
       </c>
       <c r="O99">
-        <v>16457</v>
+        <v>30645</v>
       </c>
       <c r="P99">
-        <v>14.04</v>
+        <v>6.32</v>
       </c>
       <c r="Q99">
-        <v>10.69</v>
+        <v>3.62</v>
       </c>
       <c r="R99">
-        <v>451148.83</v>
+        <v>985589.2</v>
       </c>
     </row>
     <row r="100">
@@ -7912,21 +7912,21 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G100">
-        <v>0.046</v>
+        <v>0.047</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7934,14 +7934,14 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.01</v>
+        <v>0.022</v>
       </c>
       <c r="J100">
-        <v>0.133</v>
+        <v>0.068</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>0</v>
       </c>
       <c r="O100">
-        <v>1102</v>
+        <v>184643</v>
       </c>
       <c r="P100">
-        <v>0.9399999999999999</v>
+        <v>135.92</v>
       </c>
       <c r="Q100">
-        <v>0.72</v>
+        <v>150</v>
       </c>
       <c r="R100">
-        <v>30218.26</v>
+        <v>7760059.23</v>
       </c>
     </row>
     <row r="101">
@@ -7988,21 +7988,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NL42</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Limburg (NL)</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G101">
-        <v>0.047</v>
+        <v>0.051</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>0.011</v>
       </c>
       <c r="J101">
-        <v>0.127</v>
+        <v>0.147</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8034,16 +8034,16 @@
         <v>0</v>
       </c>
       <c r="O101">
-        <v>11297</v>
+        <v>23767</v>
       </c>
       <c r="P101">
-        <v>9.640000000000001</v>
+        <v>17.5</v>
       </c>
       <c r="Q101">
-        <v>7.34</v>
+        <v>19.31</v>
       </c>
       <c r="R101">
-        <v>309695.03</v>
+        <v>998863.6899999999</v>
       </c>
     </row>
     <row r="102">
@@ -8078,7 +8078,7 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.287</v>
+        <v>0.277</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
@@ -8089,7 +8089,7 @@
         <v>0.078</v>
       </c>
       <c r="J102">
-        <v>0.482</v>
+        <v>0.495</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.253</v>
+        <v>0.256</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
@@ -8165,7 +8165,7 @@
         <v>0.039</v>
       </c>
       <c r="J103">
-        <v>0.747</v>
+        <v>0.842</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8230,7 +8230,7 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.209</v>
+        <v>0.219</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>0.056</v>
       </c>
       <c r="J104">
-        <v>0.366</v>
+        <v>0.44</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8306,18 +8306,18 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.208</v>
+        <v>0.196</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I105">
         <v>0.029</v>
       </c>
       <c r="J105">
-        <v>0.707</v>
+        <v>0.694</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N105">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RO42</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Vest</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G106">
-        <v>0.201</v>
+        <v>0.193</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I106">
-        <v>0.024</v>
+        <v>0.029</v>
       </c>
       <c r="J106">
-        <v>0.786</v>
+        <v>0.668</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8407,23 +8407,23 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N106">
-        <v>0</v>
+        <v>13704</v>
       </c>
       <c r="O106">
-        <v>222851</v>
+        <v>283291</v>
       </c>
       <c r="P106">
-        <v>39.96</v>
+        <v>72.14</v>
       </c>
       <c r="Q106">
-        <v>123</v>
+        <v>105.78</v>
       </c>
       <c r="R106">
-        <v>4542371.77</v>
+        <v>7381652.83</v>
       </c>
     </row>
     <row r="107">
@@ -8444,21 +8444,21 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NL31</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Utrecht</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G107">
-        <v>0.045</v>
+        <v>0.055</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>0.01</v>
       </c>
       <c r="J107">
-        <v>0.126</v>
+        <v>0.187</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
@@ -8490,16 +8490,16 @@
         <v>0</v>
       </c>
       <c r="O107">
-        <v>4739</v>
+        <v>5033</v>
       </c>
       <c r="P107">
-        <v>2.85</v>
+        <v>1.17</v>
       </c>
       <c r="Q107">
-        <v>1.87</v>
+        <v>0.75</v>
       </c>
       <c r="R107">
-        <v>168892.58</v>
+        <v>71680.19</v>
       </c>
     </row>
     <row r="108">
@@ -8520,21 +8520,21 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NL32</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Noord-Holland</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G108">
-        <v>0.046</v>
+        <v>0.064</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8542,10 +8542,10 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="J108">
-        <v>0.116</v>
+        <v>0.252</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
@@ -8566,16 +8566,16 @@
         <v>0</v>
       </c>
       <c r="O108">
-        <v>26391</v>
+        <v>2049</v>
       </c>
       <c r="P108">
-        <v>15.86</v>
+        <v>0.99</v>
       </c>
       <c r="Q108">
-        <v>10.4</v>
+        <v>0.38</v>
       </c>
       <c r="R108">
-        <v>940556.46</v>
+        <v>100966.09</v>
       </c>
     </row>
     <row r="109">
@@ -8596,21 +8596,21 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>FRK1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Auvergne</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G109">
-        <v>0.048</v>
+        <v>0.066</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="I109">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="J109">
-        <v>0.141</v>
+        <v>0.244</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8635,23 +8635,23 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N109">
         <v>0</v>
       </c>
       <c r="O109">
-        <v>5033</v>
+        <v>12016</v>
       </c>
       <c r="P109">
-        <v>1.17</v>
+        <v>8.42</v>
       </c>
       <c r="Q109">
-        <v>0.75</v>
+        <v>2.76</v>
       </c>
       <c r="R109">
-        <v>71680.19</v>
+        <v>734820.3</v>
       </c>
     </row>
     <row r="110">
@@ -8672,21 +8672,21 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NL11</t>
+          <t>DE72</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Groningen</t>
+          <t>Gießen</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G110">
-        <v>0.052</v>
+        <v>0.068</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="I110">
-        <v>0.01</v>
+        <v>0.011</v>
       </c>
       <c r="J110">
-        <v>0.16</v>
+        <v>0.258</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8718,16 +8718,16 @@
         <v>0</v>
       </c>
       <c r="O110">
-        <v>1961</v>
+        <v>14100</v>
       </c>
       <c r="P110">
-        <v>1.18</v>
+        <v>12.78</v>
       </c>
       <c r="Q110">
-        <v>0.77</v>
+        <v>11.55</v>
       </c>
       <c r="R110">
-        <v>69887.89999999999</v>
+        <v>509379.55</v>
       </c>
     </row>
     <row r="111">
@@ -8748,21 +8748,21 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NL22</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Gelderland</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G111">
-        <v>0.053</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.012</v>
+        <v>0.018</v>
       </c>
       <c r="J111">
-        <v>0.138</v>
+        <v>0.159</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8791,19 +8791,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>0</v>
+        <v>15455</v>
       </c>
       <c r="O111">
-        <v>33304</v>
+        <v>112913</v>
       </c>
       <c r="P111">
-        <v>20.01</v>
+        <v>102.31</v>
       </c>
       <c r="Q111">
-        <v>13.13</v>
+        <v>92.53</v>
       </c>
       <c r="R111">
-        <v>1186925.56</v>
+        <v>4079202</v>
       </c>
     </row>
     <row r="112">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.184</v>
+        <v>0.178</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8849,7 +8849,7 @@
         <v>0.037</v>
       </c>
       <c r="J112">
-        <v>0.429</v>
+        <v>0.44</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         </is>
       </c>
       <c r="G113">
-        <v>0.176</v>
+        <v>0.175</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>0.04</v>
       </c>
       <c r="J113">
-        <v>0.37</v>
+        <v>0.402</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="G114">
-        <v>0.159</v>
+        <v>0.162</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>0.017</v>
       </c>
       <c r="J114">
-        <v>0.707</v>
+        <v>0.803</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -9052,21 +9052,21 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>IE04</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Northern and Western</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G115">
-        <v>0.158</v>
+        <v>0.154</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="I115">
-        <v>0.025</v>
+        <v>0.015</v>
       </c>
       <c r="J115">
-        <v>0.472</v>
+        <v>0.856</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -9091,23 +9091,23 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N115">
-        <v>19579</v>
+        <v>0</v>
       </c>
       <c r="O115">
-        <v>223815</v>
+        <v>74477</v>
       </c>
       <c r="P115">
-        <v>32.8</v>
+        <v>31.99</v>
       </c>
       <c r="Q115">
-        <v>23</v>
+        <v>30.09</v>
       </c>
       <c r="R115">
-        <v>2144303.04</v>
+        <v>1230156.3</v>
       </c>
     </row>
     <row r="116">
@@ -9153,7 +9153,7 @@
         <v>0.017</v>
       </c>
       <c r="J116">
-        <v>0.658</v>
+        <v>0.72</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -9167,7 +9167,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N116">
@@ -9204,12 +9204,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="G117">
-        <v>0.033</v>
+        <v>0.031</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9250,16 +9250,16 @@
         <v>0</v>
       </c>
       <c r="O117">
-        <v>50495</v>
+        <v>45096</v>
       </c>
       <c r="P117">
-        <v>51.82</v>
+        <v>46.28</v>
       </c>
       <c r="Q117">
-        <v>90.34</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="R117">
-        <v>2069213.01</v>
+        <v>1847995.1</v>
       </c>
     </row>
     <row r="118">
@@ -9280,12 +9280,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="G118">
-        <v>0.033</v>
+        <v>0.034</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>0.013</v>
       </c>
       <c r="J118">
-        <v>0.063</v>
+        <v>0.066</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -9326,16 +9326,16 @@
         <v>0</v>
       </c>
       <c r="O118">
-        <v>45096</v>
+        <v>50495</v>
       </c>
       <c r="P118">
-        <v>46.28</v>
+        <v>51.82</v>
       </c>
       <c r="Q118">
-        <v>80.68000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="R118">
-        <v>1847995.1</v>
+        <v>2069213.01</v>
       </c>
     </row>
     <row r="119">
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="G119">
-        <v>0.046</v>
+        <v>0.036</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9381,11 +9381,11 @@
         <v>0.012</v>
       </c>
       <c r="J119">
-        <v>0.113</v>
+        <v>0.081</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9395,7 +9395,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N119">
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.05</v>
+        <v>0.043</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>0.011</v>
       </c>
       <c r="J120">
-        <v>0.142</v>
+        <v>0.116</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9471,7 +9471,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N120">
@@ -9522,7 +9522,7 @@
         </is>
       </c>
       <c r="G121">
-        <v>0.052</v>
+        <v>0.05</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9533,7 +9533,7 @@
         <v>0.011</v>
       </c>
       <c r="J121">
-        <v>0.146</v>
+        <v>0.147</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>

--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,40 +486,40 @@
         </is>
       </c>
       <c r="I2">
-        <v>0.99</v>
+        <v>0.495</v>
       </c>
       <c r="J2">
-        <v>0.445</v>
+        <v>0.711</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N2">
-        <v>8100289</v>
+        <v>6177767</v>
       </c>
       <c r="O2">
-        <v>16842417</v>
+        <v>558559</v>
       </c>
       <c r="P2">
-        <v>20064.08</v>
+        <v>748.6900000000001</v>
       </c>
       <c r="Q2">
-        <v>6273.26</v>
+        <v>234.08</v>
       </c>
       <c r="R2">
-        <v>231574624.05</v>
+        <v>8641139.41</v>
       </c>
     </row>
     <row r="3">
@@ -540,21 +540,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DEA1</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Zeeland</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G3">
-        <v>0.838</v>
+        <v>0.988</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -562,10 +562,10 @@
         </is>
       </c>
       <c r="I3">
-        <v>0.927</v>
+        <v>0.99</v>
       </c>
       <c r="J3">
-        <v>0.348</v>
+        <v>0.354</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -583,19 +583,19 @@
         </is>
       </c>
       <c r="N3">
-        <v>18692467</v>
+        <v>7771088</v>
       </c>
       <c r="O3">
-        <v>4658267</v>
+        <v>888957</v>
       </c>
       <c r="P3">
-        <v>8051.72</v>
+        <v>1161.22</v>
       </c>
       <c r="Q3">
-        <v>3345.81</v>
+        <v>281.13</v>
       </c>
       <c r="R3">
-        <v>61837247.36</v>
+        <v>10723428.75</v>
       </c>
     </row>
     <row r="4">
@@ -616,21 +616,21 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G4">
-        <v>0.823</v>
+        <v>0.966</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="I4">
-        <v>0.335</v>
+        <v>0.441</v>
       </c>
       <c r="J4">
-        <v>0.9330000000000001</v>
+        <v>0.761</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -655,23 +655,23 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N4">
-        <v>6876932</v>
+        <v>3330456</v>
       </c>
       <c r="O4">
-        <v>1386007</v>
+        <v>257727</v>
       </c>
       <c r="P4">
-        <v>2180.71</v>
+        <v>860.8099999999999</v>
       </c>
       <c r="Q4">
-        <v>681.8200000000001</v>
+        <v>209.63</v>
       </c>
       <c r="R4">
-        <v>25169243.03</v>
+        <v>4930103.2</v>
       </c>
     </row>
     <row r="5">
@@ -692,32 +692,32 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Peloponnisos</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G5">
-        <v>0.743</v>
+        <v>0.871</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I5">
-        <v>0.332</v>
+        <v>0.359</v>
       </c>
       <c r="J5">
-        <v>0.779</v>
+        <v>0.766</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -731,23 +731,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N5">
-        <v>5651291</v>
+        <v>2060741</v>
       </c>
       <c r="O5">
-        <v>2546310</v>
+        <v>115141</v>
       </c>
       <c r="P5">
-        <v>3305.04</v>
+        <v>645.95</v>
       </c>
       <c r="Q5">
-        <v>1033.36</v>
+        <v>157.3</v>
       </c>
       <c r="R5">
-        <v>38145944.94</v>
+        <v>3699531.08</v>
       </c>
     </row>
     <row r="6">
@@ -768,21 +768,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mazowiecki regionalny</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G6">
-        <v>0.6909999999999999</v>
+        <v>0.74</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="I6">
-        <v>0.316</v>
+        <v>0.214</v>
       </c>
       <c r="J6">
-        <v>0.716</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N6">
-        <v>7072574</v>
+        <v>6876932</v>
       </c>
       <c r="O6">
-        <v>708304</v>
+        <v>1386007</v>
       </c>
       <c r="P6">
-        <v>2758.57</v>
+        <v>2180.71</v>
       </c>
       <c r="Q6">
-        <v>1751.62</v>
+        <v>681.8200000000001</v>
       </c>
       <c r="R6">
-        <v>25342321.43</v>
+        <v>25169243.03</v>
       </c>
     </row>
     <row r="7">
@@ -866,14 +866,14 @@
         </is>
       </c>
       <c r="I7">
-        <v>0.152</v>
+        <v>0.025</v>
       </c>
       <c r="J7">
-        <v>0.015</v>
+        <v>0.018</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.02</v>
+        <v>0.012</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -942,14 +942,14 @@
         </is>
       </c>
       <c r="I8">
-        <v>0.286</v>
+        <v>0.048</v>
       </c>
       <c r="J8">
         <v>0.01</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -996,21 +996,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FRM0</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Corse</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G9">
-        <v>0.052</v>
+        <v>0.097</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1018,40 +1018,40 @@
         </is>
       </c>
       <c r="I9">
-        <v>0.011</v>
+        <v>0.055</v>
       </c>
       <c r="J9">
-        <v>0.503</v>
+        <v>0.094</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>3595112</v>
       </c>
       <c r="O9">
-        <v>22340</v>
+        <v>2077073</v>
       </c>
       <c r="P9">
-        <v>143.28</v>
+        <v>7117.16</v>
       </c>
       <c r="Q9">
-        <v>11.63</v>
+        <v>2957.46</v>
       </c>
       <c r="R9">
-        <v>1239223.42</v>
+        <v>54659830.74</v>
       </c>
     </row>
     <row r="10">
@@ -1072,21 +1072,21 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G10">
-        <v>0.057</v>
+        <v>0.099</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1094,14 +1094,14 @@
         </is>
       </c>
       <c r="I10">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="J10">
-        <v>0.137</v>
+        <v>0.156</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>159553</v>
+        <v>683183</v>
       </c>
       <c r="O10">
-        <v>682156</v>
+        <v>690041</v>
       </c>
       <c r="P10">
-        <v>1070.18</v>
+        <v>3328.96</v>
       </c>
       <c r="Q10">
-        <v>219.43</v>
+        <v>270.27</v>
       </c>
       <c r="R10">
-        <v>18864500.95</v>
+        <v>28792983.21</v>
       </c>
     </row>
     <row r="11">
@@ -1148,21 +1148,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G11">
-        <v>0.062</v>
+        <v>0.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1170,10 +1170,10 @@
         </is>
       </c>
       <c r="I11">
-        <v>0.02</v>
+        <v>0.036</v>
       </c>
       <c r="J11">
-        <v>0.318</v>
+        <v>0.15</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>30577</v>
+        <v>159553</v>
       </c>
       <c r="O11">
-        <v>224042</v>
+        <v>682156</v>
       </c>
       <c r="P11">
-        <v>849.3200000000001</v>
+        <v>1070.18</v>
       </c>
       <c r="Q11">
-        <v>205.62</v>
+        <v>219.43</v>
       </c>
       <c r="R11">
-        <v>7843142.39</v>
+        <v>18864500.95</v>
       </c>
     </row>
     <row r="12">
@@ -1224,32 +1224,32 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FRE1</t>
+          <t>BE32</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nord-Pas de Calais</t>
+          <t>Prov. Hainaut</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G12">
-        <v>0.273</v>
+        <v>0.173</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I12">
-        <v>0.074</v>
+        <v>0.031</v>
       </c>
       <c r="J12">
-        <v>0.509</v>
+        <v>0.522</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1263,23 +1263,23 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N12">
-        <v>923749</v>
+        <v>316072</v>
       </c>
       <c r="O12">
-        <v>89646</v>
+        <v>60514</v>
       </c>
       <c r="P12">
-        <v>447.42</v>
+        <v>256.58</v>
       </c>
       <c r="Q12">
-        <v>76.89</v>
+        <v>86.61</v>
       </c>
       <c r="R12">
-        <v>12956355.85</v>
+        <v>6667441.9</v>
       </c>
     </row>
     <row r="13">
@@ -1300,32 +1300,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ES43</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Extremadura</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G13">
-        <v>0.245</v>
+        <v>0.168</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I13">
-        <v>0.06</v>
+        <v>0.026</v>
       </c>
       <c r="J13">
-        <v>0.506</v>
+        <v>0.597</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1339,23 +1339,23 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N13">
-        <v>415071</v>
+        <v>137081</v>
       </c>
       <c r="O13">
-        <v>380381</v>
+        <v>27085</v>
       </c>
       <c r="P13">
-        <v>992.11</v>
+        <v>123.27</v>
       </c>
       <c r="Q13">
-        <v>514.33</v>
+        <v>40.4</v>
       </c>
       <c r="R13">
-        <v>26654450.7</v>
+        <v>4629062.5</v>
       </c>
     </row>
     <row r="14">
@@ -1376,32 +1376,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FRE2</t>
+          <t>BE34</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Picardie</t>
+          <t>Prov. Luxembourg (BE)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G14">
-        <v>0.223</v>
+        <v>0.166</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I14">
-        <v>0.058</v>
+        <v>0.032</v>
       </c>
       <c r="J14">
-        <v>0.442</v>
+        <v>0.471</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1415,23 +1415,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N14">
-        <v>716827</v>
+        <v>62764</v>
       </c>
       <c r="O14">
-        <v>38545</v>
+        <v>18402</v>
       </c>
       <c r="P14">
-        <v>192.38</v>
+        <v>78.03</v>
       </c>
       <c r="Q14">
-        <v>33.06</v>
+        <v>26.34</v>
       </c>
       <c r="R14">
-        <v>5570802.09</v>
+        <v>2027563.68</v>
       </c>
     </row>
     <row r="15">
@@ -1452,32 +1452,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>FRF2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Champagne-Ardenne</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G15">
-        <v>0.215</v>
+        <v>0.165</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I15">
-        <v>0.028</v>
+        <v>0.034</v>
       </c>
       <c r="J15">
-        <v>0.852</v>
+        <v>0.441</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1486,28 +1486,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N15">
-        <v>55969</v>
+        <v>602936</v>
       </c>
       <c r="O15">
-        <v>227355</v>
+        <v>41664</v>
       </c>
       <c r="P15">
-        <v>592.99</v>
+        <v>207.95</v>
       </c>
       <c r="Q15">
-        <v>307.42</v>
+        <v>35.74</v>
       </c>
       <c r="R15">
-        <v>15931427.45</v>
+        <v>6021671.25</v>
       </c>
     </row>
     <row r="16">
@@ -1528,32 +1528,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FRF2</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Champagne-Ardenne</t>
+          <t>Zeeland</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G16">
-        <v>0.212</v>
+        <v>0.164</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I16">
-        <v>0.051</v>
+        <v>0.039</v>
       </c>
       <c r="J16">
-        <v>0.455</v>
+        <v>0.38</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1567,23 +1567,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N16">
-        <v>602936</v>
+        <v>222706</v>
       </c>
       <c r="O16">
-        <v>41664</v>
+        <v>18443</v>
       </c>
       <c r="P16">
-        <v>207.95</v>
+        <v>120.32</v>
       </c>
       <c r="Q16">
-        <v>35.74</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="R16">
-        <v>6021671.25</v>
+        <v>3940161.78</v>
       </c>
     </row>
     <row r="17">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.044</v>
+        <v>0.038</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="I17">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="J17">
-        <v>0.104</v>
+        <v>0.09</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>10246</v>
       </c>
       <c r="O17">
-        <v>46545</v>
+        <v>60541</v>
       </c>
       <c r="P17">
-        <v>501.47</v>
+        <v>652.27</v>
       </c>
       <c r="Q17">
-        <v>316.39</v>
+        <v>411.53</v>
       </c>
       <c r="R17">
-        <v>11075693.3</v>
+        <v>14406319.48</v>
       </c>
     </row>
     <row r="18">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.047</v>
+        <v>0.039</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="I18">
-        <v>0.014</v>
+        <v>0.01</v>
       </c>
       <c r="J18">
-        <v>0.103</v>
+        <v>0.097</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>10246</v>
+        <v>0</v>
       </c>
       <c r="O18">
-        <v>60541</v>
+        <v>46545</v>
       </c>
       <c r="P18">
-        <v>652.27</v>
+        <v>501.47</v>
       </c>
       <c r="Q18">
-        <v>411.53</v>
+        <v>316.39</v>
       </c>
       <c r="R18">
-        <v>14406319.48</v>
+        <v>11075693.3</v>
       </c>
     </row>
     <row r="19">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1778,10 +1778,10 @@
         </is>
       </c>
       <c r="I19">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="J19">
-        <v>0.164</v>
+        <v>0.161</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.063</v>
+        <v>0.057</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="I20">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J20">
-        <v>0.175</v>
+        <v>0.176</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1908,21 +1908,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G21">
-        <v>0.063</v>
+        <v>0.061</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1933,7 +1933,7 @@
         <v>0.011</v>
       </c>
       <c r="J21">
-        <v>0.222</v>
+        <v>0.205</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>44932</v>
       </c>
       <c r="O21">
-        <v>15665</v>
+        <v>9707</v>
       </c>
       <c r="P21">
-        <v>97.91</v>
+        <v>104.58</v>
       </c>
       <c r="Q21">
-        <v>34.72</v>
+        <v>65.98</v>
       </c>
       <c r="R21">
-        <v>4365634.41</v>
+        <v>2309864.7</v>
       </c>
     </row>
     <row r="22">
@@ -1984,21 +1984,21 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G22">
-        <v>0.167</v>
+        <v>0.131</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2006,10 +2006,10 @@
         </is>
       </c>
       <c r="I22">
-        <v>0.028</v>
+        <v>0.01</v>
       </c>
       <c r="J22">
-        <v>0.529</v>
+        <v>0.921</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2023,23 +2023,23 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N22">
-        <v>9259</v>
+        <v>0</v>
       </c>
       <c r="O22">
-        <v>269447</v>
+        <v>9584</v>
       </c>
       <c r="P22">
-        <v>669.5599999999999</v>
+        <v>24.26</v>
       </c>
       <c r="Q22">
-        <v>258.56</v>
+        <v>10.58</v>
       </c>
       <c r="R22">
-        <v>10262659.39</v>
+        <v>274912.77</v>
       </c>
     </row>
     <row r="23">
@@ -2060,21 +2060,21 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Severozapaden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G23">
-        <v>0.158</v>
+        <v>0.13</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2082,10 +2082,10 @@
         </is>
       </c>
       <c r="I23">
-        <v>0.016</v>
+        <v>0.01</v>
       </c>
       <c r="J23">
-        <v>0.845</v>
+        <v>0.919</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2099,23 +2099,23 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N23">
         <v>0</v>
       </c>
       <c r="O23">
-        <v>88130</v>
+        <v>4087</v>
       </c>
       <c r="P23">
-        <v>219</v>
+        <v>10.93</v>
       </c>
       <c r="Q23">
-        <v>84.56999999999999</v>
+        <v>12.2</v>
       </c>
       <c r="R23">
-        <v>3356693.07</v>
+        <v>174920.82</v>
       </c>
     </row>
     <row r="24">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2150,7 +2150,7 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.14</v>
+        <v>0.128</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="I24">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="J24">
-        <v>0.448</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2175,23 +2175,23 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N24">
-        <v>3736</v>
+        <v>0</v>
       </c>
       <c r="O24">
-        <v>211234</v>
+        <v>88130</v>
       </c>
       <c r="P24">
-        <v>524.9</v>
+        <v>219</v>
       </c>
       <c r="Q24">
-        <v>202.7</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="R24">
-        <v>8045446.05</v>
+        <v>3356693.07</v>
       </c>
     </row>
     <row r="25">
@@ -2212,21 +2212,21 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Dytiki Makedonia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G25">
-        <v>0.14</v>
+        <v>0.127</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2234,10 +2234,10 @@
         </is>
       </c>
       <c r="I25">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J25">
-        <v>0.76</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2258,16 +2258,16 @@
         <v>0</v>
       </c>
       <c r="O25">
-        <v>59009</v>
+        <v>3106</v>
       </c>
       <c r="P25">
-        <v>146.63</v>
+        <v>0.8</v>
       </c>
       <c r="Q25">
-        <v>56.63</v>
+        <v>10.99</v>
       </c>
       <c r="R25">
-        <v>2247521.65</v>
+        <v>53485.11</v>
       </c>
     </row>
     <row r="26">
@@ -2288,21 +2288,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PT11</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Norte</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G26">
-        <v>0.137</v>
+        <v>0.126</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         </is>
       </c>
       <c r="I26">
-        <v>0.019</v>
+        <v>0.01</v>
       </c>
       <c r="J26">
-        <v>0.537</v>
+        <v>0.866</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2327,23 +2327,23 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N26">
-        <v>9287</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>131430</v>
+        <v>6794</v>
       </c>
       <c r="P26">
-        <v>400.99</v>
+        <v>16.88</v>
       </c>
       <c r="Q26">
-        <v>152.12</v>
+        <v>6.52</v>
       </c>
       <c r="R26">
-        <v>5025326.92</v>
+        <v>258750.19</v>
       </c>
     </row>
     <row r="27">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.033</v>
+        <v>0.036</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2386,10 +2386,10 @@
         </is>
       </c>
       <c r="I27">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J27">
-        <v>0.077</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K27" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.035</v>
+        <v>0.038</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2462,10 +2462,10 @@
         </is>
       </c>
       <c r="I28">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J28">
-        <v>0.08400000000000001</v>
+        <v>0.091</v>
       </c>
       <c r="K28" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         </is>
       </c>
       <c r="G29">
-        <v>0.049</v>
+        <v>0.051</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2541,7 +2541,7 @@
         <v>0.01</v>
       </c>
       <c r="J29">
-        <v>0.151</v>
+        <v>0.155</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         </is>
       </c>
       <c r="G30">
-        <v>0.052</v>
+        <v>0.053</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>0.01</v>
       </c>
       <c r="J30">
-        <v>0.167</v>
+        <v>0.171</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="G31">
-        <v>0.056</v>
+        <v>0.057</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2693,7 +2693,7 @@
         <v>0.01</v>
       </c>
       <c r="J31">
-        <v>0.193</v>
+        <v>0.195</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -2744,32 +2744,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>ITI1</t>
+          <t>BE34</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Toscana</t>
+          <t>Prov. Luxembourg (BE)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G32">
-        <v>0.254</v>
+        <v>0.161</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I32">
-        <v>0.064</v>
+        <v>0.042</v>
       </c>
       <c r="J32">
-        <v>0.507</v>
+        <v>0.337</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2783,23 +2783,23 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N32">
-        <v>787177</v>
+        <v>112095</v>
       </c>
       <c r="O32">
-        <v>73725</v>
+        <v>6875</v>
       </c>
       <c r="P32">
-        <v>516.6</v>
+        <v>38.3</v>
       </c>
       <c r="Q32">
-        <v>205.55</v>
+        <v>18.54</v>
       </c>
       <c r="R32">
-        <v>3047222.43</v>
+        <v>327698.66</v>
       </c>
     </row>
     <row r="33">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>SE32</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Mellersta Norrland</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G33">
-        <v>0.219</v>
+        <v>0.16</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I33">
-        <v>0.051</v>
+        <v>0.037</v>
       </c>
       <c r="J33">
-        <v>0.481</v>
+        <v>0.38</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2859,23 +2859,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N33">
-        <v>521449</v>
+        <v>179232</v>
       </c>
       <c r="O33">
-        <v>126035</v>
+        <v>33515</v>
       </c>
       <c r="P33">
-        <v>883.14</v>
+        <v>123.85</v>
       </c>
       <c r="Q33">
-        <v>351.39</v>
+        <v>12.77</v>
       </c>
       <c r="R33">
-        <v>5209288.92</v>
+        <v>1443154.7</v>
       </c>
     </row>
     <row r="34">
@@ -2896,21 +2896,21 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G34">
-        <v>0.188</v>
+        <v>0.14</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2918,10 +2918,10 @@
         </is>
       </c>
       <c r="I34">
-        <v>0.04</v>
+        <v>0.016</v>
       </c>
       <c r="J34">
-        <v>0.458</v>
+        <v>0.67</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -2935,23 +2935,23 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N34">
-        <v>290853</v>
+        <v>46724</v>
       </c>
       <c r="O34">
-        <v>187035</v>
+        <v>1516</v>
       </c>
       <c r="P34">
-        <v>1310.58</v>
+        <v>9.1</v>
       </c>
       <c r="Q34">
-        <v>521.46</v>
+        <v>13.84</v>
       </c>
       <c r="R34">
-        <v>7730536.47</v>
+        <v>96858.27</v>
       </c>
     </row>
     <row r="35">
@@ -2972,21 +2972,21 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>ITH2</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Közép-Dunántúl</t>
+          <t>Provincia Autonoma di Trento</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G35">
-        <v>0.187</v>
+        <v>0.137</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -2994,10 +2994,10 @@
         </is>
       </c>
       <c r="I35">
-        <v>0.029</v>
+        <v>0.027</v>
       </c>
       <c r="J35">
-        <v>0.612</v>
+        <v>0.378</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3011,23 +3011,23 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N35">
-        <v>295376</v>
+        <v>217643</v>
       </c>
       <c r="O35">
-        <v>13765</v>
+        <v>19593</v>
       </c>
       <c r="P35">
-        <v>64.03</v>
+        <v>137.29</v>
       </c>
       <c r="Q35">
-        <v>32.02</v>
+        <v>54.63</v>
       </c>
       <c r="R35">
-        <v>353560.97</v>
+        <v>809829.72</v>
       </c>
     </row>
     <row r="36">
@@ -3062,7 +3062,7 @@
         </is>
       </c>
       <c r="G36">
-        <v>0.183</v>
+        <v>0.136</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3070,10 +3070,10 @@
         </is>
       </c>
       <c r="I36">
-        <v>0.028</v>
+        <v>0.017</v>
       </c>
       <c r="J36">
-        <v>0.618</v>
+        <v>0.601</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3146,7 +3146,7 @@
         </is>
       </c>
       <c r="I37">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="J37">
         <v>0.01</v>
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.02</v>
+        <v>0.014</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         </is>
       </c>
       <c r="I38">
+        <v>0.01</v>
+      </c>
+      <c r="J38">
         <v>0.017</v>
-      </c>
-      <c r="J38">
-        <v>0.023</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -3276,21 +3276,21 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LU00</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G39">
-        <v>0.032</v>
+        <v>0.04</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3301,7 +3301,7 @@
         <v>0.011</v>
       </c>
       <c r="J39">
-        <v>0.074</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -3310,28 +3310,28 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N39">
-        <v>5173</v>
+        <v>0</v>
       </c>
       <c r="O39">
-        <v>3246</v>
+        <v>59629</v>
       </c>
       <c r="P39">
-        <v>12.02</v>
+        <v>30.94</v>
       </c>
       <c r="Q39">
-        <v>3.82</v>
+        <v>60.44</v>
       </c>
       <c r="R39">
-        <v>203126.32</v>
+        <v>1256929.64</v>
       </c>
     </row>
     <row r="40">
@@ -3352,21 +3352,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G40">
-        <v>0.041</v>
+        <v>0.043</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3377,7 +3377,7 @@
         <v>0.014</v>
       </c>
       <c r="J40">
-        <v>0.08799999999999999</v>
+        <v>0.081</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3386,28 +3386,28 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>471622</v>
       </c>
       <c r="O40">
-        <v>59629</v>
+        <v>26427</v>
       </c>
       <c r="P40">
-        <v>30.94</v>
+        <v>264.47</v>
       </c>
       <c r="Q40">
-        <v>60.44</v>
+        <v>277.01</v>
       </c>
       <c r="R40">
-        <v>1256929.64</v>
+        <v>1350468.02</v>
       </c>
     </row>
     <row r="41">
@@ -3428,21 +3428,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G41">
-        <v>0.046</v>
+        <v>0.043</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3450,40 +3450,40 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J41">
-        <v>0.137</v>
+        <v>0.097</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>123605</v>
       </c>
       <c r="O41">
-        <v>6779</v>
+        <v>12625</v>
       </c>
       <c r="P41">
-        <v>10.15</v>
+        <v>126.34</v>
       </c>
       <c r="Q41">
-        <v>5.94</v>
+        <v>132.33</v>
       </c>
       <c r="R41">
-        <v>179503.53</v>
+        <v>645130.8199999999</v>
       </c>
     </row>
     <row r="42">
@@ -3504,21 +3504,21 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>BE21</t>
+          <t>NL34</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Prov. Antwerpen</t>
+          <t>Zeeland</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="G42">
-        <v>0.9370000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="I42">
-        <v>0.82</v>
+        <v>0.99</v>
       </c>
       <c r="J42">
-        <v>0.514</v>
+        <v>0.518</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3547,19 +3547,19 @@
         </is>
       </c>
       <c r="N42">
-        <v>11781814</v>
+        <v>7484706</v>
       </c>
       <c r="O42">
-        <v>1095262</v>
+        <v>767408</v>
       </c>
       <c r="P42">
-        <v>6318.37</v>
+        <v>2893.03</v>
       </c>
       <c r="Q42">
-        <v>875.6799999999999</v>
+        <v>388.29</v>
       </c>
       <c r="R42">
-        <v>27504760.9</v>
+        <v>16174264.14</v>
       </c>
     </row>
     <row r="43">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3594,18 +3594,18 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.875</v>
+        <v>0.776</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I43">
-        <v>0.407</v>
+        <v>0.452</v>
       </c>
       <c r="J43">
-        <v>0.903</v>
+        <v>0.699</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3623,19 +3623,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>5886952</v>
+        <v>5677884</v>
       </c>
       <c r="O43">
-        <v>428034</v>
+        <v>175700</v>
       </c>
       <c r="P43">
-        <v>1335.55</v>
+        <v>548.22</v>
       </c>
       <c r="Q43">
-        <v>161.33</v>
+        <v>66.22</v>
       </c>
       <c r="R43">
-        <v>10122087.62</v>
+        <v>4154925.1</v>
       </c>
     </row>
     <row r="44">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PL92</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mazowiecki regionalny</t>
+          <t>Peloponnisos</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G44">
-        <v>0.8139999999999999</v>
+        <v>0.719</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I44">
-        <v>0.434</v>
+        <v>0.355</v>
       </c>
       <c r="J44">
-        <v>0.734</v>
+        <v>0.765</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3699,19 +3699,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>6621904</v>
+        <v>2047197</v>
       </c>
       <c r="O44">
-        <v>127493</v>
+        <v>2995</v>
       </c>
       <c r="P44">
-        <v>876.2</v>
+        <v>40.63</v>
       </c>
       <c r="Q44">
-        <v>188.3</v>
+        <v>1.03</v>
       </c>
       <c r="R44">
-        <v>3138403.35</v>
+        <v>332084.95</v>
       </c>
     </row>
     <row r="45">
@@ -3732,36 +3732,36 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NL33</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Zuid-Holland</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G45">
-        <v>0.8090000000000001</v>
+        <v>0.541</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.642</v>
+        <v>0.174</v>
       </c>
       <c r="J45">
-        <v>0.491</v>
+        <v>0.888</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -3771,23 +3771,23 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N45">
-        <v>8076779</v>
+        <v>5886952</v>
       </c>
       <c r="O45">
-        <v>1967937</v>
+        <v>428034</v>
       </c>
       <c r="P45">
-        <v>7418.85</v>
+        <v>1335.55</v>
       </c>
       <c r="Q45">
-        <v>995.72</v>
+        <v>161.33</v>
       </c>
       <c r="R45">
-        <v>41477161.69</v>
+        <v>10122087.62</v>
       </c>
     </row>
     <row r="46">
@@ -3808,32 +3808,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>BE21</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Prov. Antwerpen</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G46">
-        <v>0.74</v>
+        <v>0.523</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I46">
-        <v>0.378</v>
+        <v>0.306</v>
       </c>
       <c r="J46">
-        <v>0.699</v>
+        <v>0.471</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3847,23 +3847,23 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N46">
-        <v>5677884</v>
+        <v>11781814</v>
       </c>
       <c r="O46">
-        <v>175700</v>
+        <v>1095262</v>
       </c>
       <c r="P46">
-        <v>548.22</v>
+        <v>6318.37</v>
       </c>
       <c r="Q46">
-        <v>66.22</v>
+        <v>875.6799999999999</v>
       </c>
       <c r="R46">
-        <v>4154925.1</v>
+        <v>27504760.9</v>
       </c>
     </row>
     <row r="47">
@@ -3884,21 +3884,21 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G47">
-        <v>0.081</v>
+        <v>0.049</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3906,10 +3906,10 @@
         </is>
       </c>
       <c r="I47">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="J47">
-        <v>0.344</v>
+        <v>0.12</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -3923,23 +3923,23 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N47">
         <v>0</v>
       </c>
       <c r="O47">
-        <v>15994</v>
+        <v>503456</v>
       </c>
       <c r="P47">
-        <v>58.89</v>
+        <v>1763.96</v>
       </c>
       <c r="Q47">
-        <v>0.5</v>
+        <v>583.6900000000001</v>
       </c>
       <c r="R47">
-        <v>405895.45</v>
+        <v>7907499.24</v>
       </c>
     </row>
     <row r="48">
@@ -3960,21 +3960,21 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DK05</t>
+          <t>DE14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nordjylland</t>
+          <t>Tübingen</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G48">
-        <v>0.081</v>
+        <v>0.067</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>0.011</v>
       </c>
       <c r="J48">
-        <v>0.364</v>
+        <v>0.238</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -3999,23 +3999,23 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N48">
         <v>0</v>
       </c>
       <c r="O48">
-        <v>8724</v>
+        <v>133351</v>
       </c>
       <c r="P48">
-        <v>37.34</v>
+        <v>467.22</v>
       </c>
       <c r="Q48">
-        <v>5.85</v>
+        <v>154.6</v>
       </c>
       <c r="R48">
-        <v>295450.48</v>
+        <v>2094468.62</v>
       </c>
     </row>
     <row r="49">
@@ -4036,12 +4036,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DEB2</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Trier</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -4050,7 +4050,7 @@
         </is>
       </c>
       <c r="G49">
-        <v>0.081</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4058,10 +4058,10 @@
         </is>
       </c>
       <c r="I49">
-        <v>0.01</v>
+        <v>0.012</v>
       </c>
       <c r="J49">
-        <v>0.372</v>
+        <v>0.228</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4075,23 +4075,23 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N49">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="O49">
-        <v>5049</v>
+        <v>176182</v>
       </c>
       <c r="P49">
-        <v>17.69</v>
+        <v>617.29</v>
       </c>
       <c r="Q49">
-        <v>5.85</v>
+        <v>204.26</v>
       </c>
       <c r="R49">
-        <v>79301.87</v>
+        <v>2767186.65</v>
       </c>
     </row>
     <row r="50">
@@ -4112,21 +4112,21 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>DE14</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tübingen</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G50">
-        <v>0.082</v>
+        <v>0.076</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4134,10 +4134,10 @@
         </is>
       </c>
       <c r="I50">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="J50">
-        <v>0.212</v>
+        <v>0.258</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -4155,19 +4155,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>0</v>
+        <v>40160</v>
       </c>
       <c r="O50">
-        <v>133351</v>
+        <v>116404</v>
       </c>
       <c r="P50">
-        <v>467.22</v>
+        <v>729.64</v>
       </c>
       <c r="Q50">
-        <v>154.6</v>
+        <v>32.71</v>
       </c>
       <c r="R50">
-        <v>2094468.62</v>
+        <v>3615655.6</v>
       </c>
     </row>
     <row r="51">
@@ -4188,21 +4188,21 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DK04</t>
+          <t>DE24</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Midtjylland</t>
+          <t>Oberfranken</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G51">
-        <v>0.083</v>
+        <v>0.076</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4210,10 +4210,10 @@
         </is>
       </c>
       <c r="I51">
-        <v>0.014</v>
+        <v>0.011</v>
       </c>
       <c r="J51">
-        <v>0.292</v>
+        <v>0.294</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -4231,19 +4231,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>26250</v>
+        <v>0</v>
       </c>
       <c r="O51">
-        <v>33023</v>
+        <v>80234</v>
       </c>
       <c r="P51">
-        <v>141.36</v>
+        <v>281.12</v>
       </c>
       <c r="Q51">
-        <v>22.15</v>
+        <v>93.02</v>
       </c>
       <c r="R51">
-        <v>1118387.01</v>
+        <v>1260190.55</v>
       </c>
     </row>
     <row r="52">
@@ -4264,32 +4264,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>IE05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Southern</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G52">
-        <v>0.302</v>
+        <v>0.177</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I52">
-        <v>0.112</v>
+        <v>0.049</v>
       </c>
       <c r="J52">
-        <v>0.407</v>
+        <v>0.347</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4307,19 +4307,19 @@
         </is>
       </c>
       <c r="N52">
-        <v>2160</v>
+        <v>85614</v>
       </c>
       <c r="O52">
-        <v>1620071</v>
+        <v>1449770</v>
       </c>
       <c r="P52">
-        <v>582.3200000000001</v>
+        <v>129.9</v>
       </c>
       <c r="Q52">
-        <v>317.06</v>
+        <v>33.85</v>
       </c>
       <c r="R52">
-        <v>18630485.45</v>
+        <v>11019168.12</v>
       </c>
     </row>
     <row r="53">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>IE04</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Northern and Western</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -4354,18 +4354,18 @@
         </is>
       </c>
       <c r="G53">
-        <v>0.274</v>
+        <v>0.167</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I53">
-        <v>0.107</v>
+        <v>0.042</v>
       </c>
       <c r="J53">
-        <v>0.355</v>
+        <v>0.358</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4383,19 +4383,19 @@
         </is>
       </c>
       <c r="N53">
-        <v>85614</v>
+        <v>9343</v>
       </c>
       <c r="O53">
-        <v>1449770</v>
+        <v>648920</v>
       </c>
       <c r="P53">
-        <v>129.9</v>
+        <v>58.15</v>
       </c>
       <c r="Q53">
-        <v>33.85</v>
+        <v>15.15</v>
       </c>
       <c r="R53">
-        <v>11019168.12</v>
+        <v>4932204.25</v>
       </c>
     </row>
     <row r="54">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>BE31</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Prov. Brabant Wallon</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G54">
-        <v>0.239</v>
+        <v>0.167</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I54">
-        <v>0.103</v>
+        <v>0.036</v>
       </c>
       <c r="J54">
-        <v>0.283</v>
+        <v>0.419</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4459,19 +4459,19 @@
         </is>
       </c>
       <c r="N54">
-        <v>63513</v>
+        <v>42339</v>
       </c>
       <c r="O54">
-        <v>1408724</v>
+        <v>183751</v>
       </c>
       <c r="P54">
-        <v>126.23</v>
+        <v>81.45</v>
       </c>
       <c r="Q54">
-        <v>32.89</v>
+        <v>16.2</v>
       </c>
       <c r="R54">
-        <v>10707192.78</v>
+        <v>3218848.98</v>
       </c>
     </row>
     <row r="55">
@@ -4492,32 +4492,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>IE06</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Eastern and Midland</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="G55">
-        <v>0.211</v>
+        <v>0.147</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I55">
-        <v>0.052</v>
+        <v>0.042</v>
       </c>
       <c r="J55">
-        <v>0.439</v>
+        <v>0.28</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4531,23 +4531,23 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N55">
-        <v>17751</v>
+        <v>63513</v>
       </c>
       <c r="O55">
-        <v>653342</v>
+        <v>1408724</v>
       </c>
       <c r="P55">
-        <v>234.84</v>
+        <v>126.23</v>
       </c>
       <c r="Q55">
-        <v>127.86</v>
+        <v>32.89</v>
       </c>
       <c r="R55">
-        <v>7513299.44</v>
+        <v>10707192.78</v>
       </c>
     </row>
     <row r="56">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PL22</t>
+          <t>HU32</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Śląskie</t>
+          <t>Észak-Alföld</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G56">
-        <v>0.21</v>
+        <v>0.139</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I56">
-        <v>0.04</v>
+        <v>0.014</v>
       </c>
       <c r="J56">
-        <v>0.5679999999999999</v>
+        <v>0.757</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4607,23 +4607,23 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N56">
-        <v>0</v>
+        <v>36185</v>
       </c>
       <c r="O56">
-        <v>475117</v>
+        <v>130160</v>
       </c>
       <c r="P56">
-        <v>127.48</v>
+        <v>101.51</v>
       </c>
       <c r="Q56">
-        <v>208.77</v>
+        <v>28.13</v>
       </c>
       <c r="R56">
-        <v>5406529.91</v>
+        <v>1496348.22</v>
       </c>
     </row>
     <row r="57">
@@ -4644,21 +4644,21 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Västsverige</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G57">
-        <v>0.045</v>
+        <v>0.033</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="I57">
-        <v>0.019</v>
+        <v>0.011</v>
       </c>
       <c r="J57">
-        <v>0.074</v>
+        <v>0.063</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -4683,23 +4683,23 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N57">
         <v>0</v>
       </c>
       <c r="O57">
-        <v>137837</v>
+        <v>246236</v>
       </c>
       <c r="P57">
-        <v>12.42</v>
+        <v>95.42</v>
       </c>
       <c r="Q57">
-        <v>4.7</v>
+        <v>65.58</v>
       </c>
       <c r="R57">
-        <v>1640297.31</v>
+        <v>2510994.84</v>
       </c>
     </row>
     <row r="58">
@@ -4720,12 +4720,12 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>0.047</v>
+        <v>0.034</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4742,10 +4742,10 @@
         </is>
       </c>
       <c r="I58">
-        <v>0.025</v>
+        <v>0.011</v>
       </c>
       <c r="J58">
-        <v>0.058</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -4766,16 +4766,16 @@
         <v>0</v>
       </c>
       <c r="O58">
-        <v>246236</v>
+        <v>281503</v>
       </c>
       <c r="P58">
-        <v>95.42</v>
+        <v>109.08</v>
       </c>
       <c r="Q58">
-        <v>65.58</v>
+        <v>74.97</v>
       </c>
       <c r="R58">
-        <v>2510994.84</v>
+        <v>2870628.31</v>
       </c>
     </row>
     <row r="59">
@@ -4796,21 +4796,21 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Västsverige</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G59">
-        <v>0.053</v>
+        <v>0.044</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4818,10 +4818,10 @@
         </is>
       </c>
       <c r="I59">
-        <v>0.028</v>
+        <v>0.012</v>
       </c>
       <c r="J59">
-        <v>0.066</v>
+        <v>0.096</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -4835,23 +4835,23 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N59">
         <v>0</v>
       </c>
       <c r="O59">
-        <v>281503</v>
+        <v>137837</v>
       </c>
       <c r="P59">
-        <v>109.08</v>
+        <v>12.42</v>
       </c>
       <c r="Q59">
-        <v>74.97</v>
+        <v>4.7</v>
       </c>
       <c r="R59">
-        <v>2870628.31</v>
+        <v>1640297.31</v>
       </c>
     </row>
     <row r="60">
@@ -4872,21 +4872,21 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G60">
-        <v>0.057</v>
+        <v>0.052</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
         <v>0.012</v>
       </c>
       <c r="J60">
-        <v>0.178</v>
+        <v>0.134</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -4911,23 +4911,23 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N60">
         <v>0</v>
       </c>
       <c r="O60">
-        <v>25829</v>
+        <v>282203</v>
       </c>
       <c r="P60">
-        <v>2.33</v>
+        <v>109.36</v>
       </c>
       <c r="Q60">
-        <v>0.88</v>
+        <v>75.16</v>
       </c>
       <c r="R60">
-        <v>307377.02</v>
+        <v>2877772.27</v>
       </c>
     </row>
     <row r="61">
@@ -4948,21 +4948,21 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G61">
-        <v>0.061</v>
+        <v>0.058</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.018</v>
+        <v>0.013</v>
       </c>
       <c r="J61">
-        <v>0.124</v>
+        <v>0.149</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -4987,23 +4987,23 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N61">
-        <v>4331</v>
+        <v>0</v>
       </c>
       <c r="O61">
-        <v>129489</v>
+        <v>217564</v>
       </c>
       <c r="P61">
-        <v>11.67</v>
+        <v>84.31</v>
       </c>
       <c r="Q61">
-        <v>4.42</v>
+        <v>57.94</v>
       </c>
       <c r="R61">
-        <v>1540953.23</v>
+        <v>2218614.82</v>
       </c>
     </row>
     <row r="62">
@@ -5024,21 +5024,21 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Świętokrzyskie</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G62">
-        <v>0.656</v>
+        <v>0.636</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5046,10 +5046,10 @@
         </is>
       </c>
       <c r="I62">
-        <v>0.282</v>
+        <v>0.278</v>
       </c>
       <c r="J62">
-        <v>0.738</v>
+        <v>0.764</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5067,19 +5067,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>4132364</v>
+        <v>2111231</v>
       </c>
       <c r="O62">
-        <v>188035</v>
+        <v>14420</v>
       </c>
       <c r="P62">
-        <v>1349.77</v>
+        <v>320.34</v>
       </c>
       <c r="Q62">
-        <v>291.48</v>
+        <v>24.07</v>
       </c>
       <c r="R62">
-        <v>1829450.55</v>
+        <v>115430.42</v>
       </c>
     </row>
     <row r="63">
@@ -5100,21 +5100,21 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>ES52</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Comunitat Valenciana</t>
+          <t>Dytiki Elláda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G63">
-        <v>0.597</v>
+        <v>0.5</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="I63">
-        <v>0.295</v>
+        <v>0.158</v>
       </c>
       <c r="J63">
-        <v>0.586</v>
+        <v>0.832</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5139,23 +5139,23 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N63">
-        <v>3690134</v>
+        <v>745326</v>
       </c>
       <c r="O63">
-        <v>839170</v>
+        <v>6176</v>
       </c>
       <c r="P63">
-        <v>5441</v>
+        <v>137.2</v>
       </c>
       <c r="Q63">
-        <v>249.57</v>
+        <v>10.31</v>
       </c>
       <c r="R63">
-        <v>6752400.96</v>
+        <v>49438.11</v>
       </c>
     </row>
     <row r="64">
@@ -5176,21 +5176,21 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>PL52</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Opolskie</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G64">
-        <v>0.544</v>
+        <v>0.494</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5198,10 +5198,10 @@
         </is>
       </c>
       <c r="I64">
-        <v>0.213</v>
+        <v>0.172</v>
       </c>
       <c r="J64">
-        <v>0.676</v>
+        <v>0.751</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="N64">
-        <v>3155406</v>
+        <v>746142</v>
       </c>
       <c r="O64">
-        <v>75010</v>
+        <v>14072</v>
       </c>
       <c r="P64">
-        <v>538.4400000000001</v>
+        <v>113.9</v>
       </c>
       <c r="Q64">
-        <v>116.28</v>
+        <v>12.23</v>
       </c>
       <c r="R64">
-        <v>729794.49</v>
+        <v>147454.31</v>
       </c>
     </row>
     <row r="65">
@@ -5252,21 +5252,21 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ES61</t>
+          <t>PL72</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Andalucía</t>
+          <t>Świętokrzyskie</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="G65">
-        <v>0.525</v>
+        <v>0.473</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5274,10 +5274,10 @@
         </is>
       </c>
       <c r="I65">
-        <v>0.208</v>
+        <v>0.163</v>
       </c>
       <c r="J65">
-        <v>0.646</v>
+        <v>0.722</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5291,23 +5291,23 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N65">
-        <v>2722191</v>
+        <v>4132364</v>
       </c>
       <c r="O65">
-        <v>429400</v>
+        <v>188035</v>
       </c>
       <c r="P65">
-        <v>2784.14</v>
+        <v>1349.77</v>
       </c>
       <c r="Q65">
-        <v>127.71</v>
+        <v>291.48</v>
       </c>
       <c r="R65">
-        <v>3455175.59</v>
+        <v>1829450.55</v>
       </c>
     </row>
     <row r="66">
@@ -5328,21 +5328,21 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>BE35</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Prov. Namur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G66">
-        <v>0.518</v>
+        <v>0.461</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5350,10 +5350,10 @@
         </is>
       </c>
       <c r="I66">
-        <v>0.271</v>
+        <v>0.217</v>
       </c>
       <c r="J66">
-        <v>0.481</v>
+        <v>0.517</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5371,19 +5371,19 @@
         </is>
       </c>
       <c r="N66">
-        <v>3814216</v>
+        <v>781112</v>
       </c>
       <c r="O66">
-        <v>341227</v>
+        <v>31562</v>
       </c>
       <c r="P66">
-        <v>2761.98</v>
+        <v>353.9</v>
       </c>
       <c r="Q66">
-        <v>296.49</v>
+        <v>16.37</v>
       </c>
       <c r="R66">
-        <v>3575677.42</v>
+        <v>343951.23</v>
       </c>
     </row>
     <row r="67">
@@ -5404,21 +5404,21 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G67">
-        <v>0.063</v>
+        <v>0.047</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5426,10 +5426,10 @@
         </is>
       </c>
       <c r="I67">
-        <v>0.011</v>
+        <v>0.012</v>
       </c>
       <c r="J67">
-        <v>0.226</v>
+        <v>0.113</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
@@ -5447,19 +5447,19 @@
         </is>
       </c>
       <c r="N67">
-        <v>0</v>
+        <v>451284</v>
       </c>
       <c r="O67">
-        <v>13056</v>
+        <v>76550</v>
       </c>
       <c r="P67">
-        <v>181.55</v>
+        <v>949.49</v>
       </c>
       <c r="Q67">
-        <v>7.31</v>
+        <v>127.18</v>
       </c>
       <c r="R67">
-        <v>151664.14</v>
+        <v>820916.01</v>
       </c>
     </row>
     <row r="68">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>DE60</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5494,7 +5494,7 @@
         </is>
       </c>
       <c r="G68">
-        <v>0.06900000000000001</v>
+        <v>0.051</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5502,19 +5502,19 @@
         </is>
       </c>
       <c r="I68">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J68">
-        <v>0.274</v>
+        <v>0.107</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
@@ -5523,19 +5523,19 @@
         </is>
       </c>
       <c r="N68">
-        <v>0</v>
+        <v>826658</v>
       </c>
       <c r="O68">
-        <v>7422</v>
+        <v>76088</v>
       </c>
       <c r="P68">
-        <v>92.06</v>
+        <v>943.76</v>
       </c>
       <c r="Q68">
-        <v>12.33</v>
+        <v>126.41</v>
       </c>
       <c r="R68">
-        <v>79589.62</v>
+        <v>815962.74</v>
       </c>
     </row>
     <row r="69">
@@ -5556,21 +5556,21 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G69">
-        <v>0.076</v>
+        <v>0.066</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5578,10 +5578,10 @@
         </is>
       </c>
       <c r="I69">
-        <v>0.012</v>
+        <v>0.014</v>
       </c>
       <c r="J69">
-        <v>0.282</v>
+        <v>0.178</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5599,19 +5599,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>0</v>
+        <v>454253</v>
       </c>
       <c r="O69">
-        <v>34833</v>
+        <v>67320</v>
       </c>
       <c r="P69">
-        <v>251.63</v>
+        <v>835</v>
       </c>
       <c r="Q69">
-        <v>0.7</v>
+        <v>111.84</v>
       </c>
       <c r="R69">
-        <v>319388.36</v>
+        <v>721931.23</v>
       </c>
     </row>
     <row r="70">
@@ -5632,21 +5632,21 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DE30</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Berlin</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G70">
-        <v>0.078</v>
+        <v>0.067</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5654,10 +5654,10 @@
         </is>
       </c>
       <c r="I70">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J70">
-        <v>0.327</v>
+        <v>0.255</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -5678,16 +5678,16 @@
         <v>0</v>
       </c>
       <c r="O70">
-        <v>13747</v>
+        <v>13056</v>
       </c>
       <c r="P70">
-        <v>170.51</v>
+        <v>181.55</v>
       </c>
       <c r="Q70">
-        <v>22.84</v>
+        <v>7.31</v>
       </c>
       <c r="R70">
-        <v>147424.69</v>
+        <v>151664.14</v>
       </c>
     </row>
     <row r="71">
@@ -5708,21 +5708,21 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NL23</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Flevoland</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G71">
-        <v>0.08500000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="I71">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J71">
-        <v>0.384</v>
+        <v>0.295</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -5751,19 +5751,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>5721</v>
+        <v>0</v>
       </c>
       <c r="O71">
-        <v>8989</v>
+        <v>7422</v>
       </c>
       <c r="P71">
-        <v>11.54</v>
+        <v>92.06</v>
       </c>
       <c r="Q71">
-        <v>3.09</v>
+        <v>12.33</v>
       </c>
       <c r="R71">
-        <v>52491.98</v>
+        <v>79589.62</v>
       </c>
     </row>
     <row r="72">
@@ -5784,36 +5784,36 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>DEA1</t>
+          <t>SE33</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Düsseldorf</t>
+          <t>Övre Norrland</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G72">
-        <v>0.99</v>
+        <v>0.544</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Very High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I72">
-        <v>0.99</v>
+        <v>0.349</v>
       </c>
       <c r="J72">
-        <v>0.474</v>
+        <v>0.446</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>13655108</v>
+        <v>4030911</v>
       </c>
       <c r="O72">
-        <v>1927815</v>
+        <v>190114</v>
       </c>
       <c r="P72">
-        <v>8435.620000000001</v>
+        <v>672.28</v>
       </c>
       <c r="Q72">
-        <v>1827.63</v>
+        <v>0</v>
       </c>
       <c r="R72">
-        <v>22142953.22</v>
+        <v>2232388.82</v>
       </c>
     </row>
     <row r="73">
@@ -5860,32 +5860,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>SK04</t>
+          <t>ES12</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Východné Slovensko</t>
+          <t>Principado de Asturias</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="G73">
-        <v>0.797</v>
+        <v>0.517</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I73">
-        <v>0.362</v>
+        <v>0.294</v>
       </c>
       <c r="J73">
-        <v>0.843</v>
+        <v>0.479</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5903,19 +5903,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>5388284</v>
+        <v>4131636</v>
       </c>
       <c r="O73">
-        <v>215473</v>
+        <v>608545</v>
       </c>
       <c r="P73">
-        <v>2258.03</v>
+        <v>1081.7</v>
       </c>
       <c r="Q73">
-        <v>97.59999999999999</v>
+        <v>248.89</v>
       </c>
       <c r="R73">
-        <v>4826706.62</v>
+        <v>7061995.92</v>
       </c>
     </row>
     <row r="74">
@@ -5936,32 +5936,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G74">
-        <v>0.768</v>
+        <v>0.507</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I74">
-        <v>0.363</v>
+        <v>0.172</v>
       </c>
       <c r="J74">
-        <v>0.782</v>
+        <v>0.789</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5975,23 +5975,23 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N74">
-        <v>4351958</v>
+        <v>1163945</v>
       </c>
       <c r="O74">
-        <v>1267020</v>
+        <v>119413</v>
       </c>
       <c r="P74">
-        <v>985.3</v>
+        <v>95.86</v>
       </c>
       <c r="Q74">
-        <v>393.91</v>
+        <v>138.1</v>
       </c>
       <c r="R74">
-        <v>9139782.189999999</v>
+        <v>560640.63</v>
       </c>
     </row>
     <row r="75">
@@ -6012,62 +6012,62 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>SK04</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Východné Slovensko</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G75">
-        <v>0.744</v>
+        <v>0.487</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I75">
-        <v>0.488</v>
+        <v>0.151</v>
       </c>
       <c r="J75">
-        <v>0.546</v>
+        <v>0.829</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N75">
-        <v>1805137</v>
+        <v>5388284</v>
       </c>
       <c r="O75">
-        <v>5793495</v>
+        <v>215473</v>
       </c>
       <c r="P75">
-        <v>4505.34</v>
+        <v>2258.03</v>
       </c>
       <c r="Q75">
-        <v>1801.16</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R75">
-        <v>41791998.74</v>
+        <v>4826706.62</v>
       </c>
     </row>
     <row r="76">
@@ -6088,62 +6088,62 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>AT31</t>
+          <t>ITC2</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oberösterreich</t>
+          <t>Valle d’Aosta/Vallée d’Aoste</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G76">
-        <v>0.722</v>
+        <v>0.41</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I76">
-        <v>0.591</v>
+        <v>0.156</v>
       </c>
       <c r="J76">
-        <v>0.425</v>
+        <v>0.572</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N76">
-        <v>8752298</v>
+        <v>87962</v>
       </c>
       <c r="O76">
-        <v>493985</v>
+        <v>172712</v>
       </c>
       <c r="P76">
-        <v>4424.66</v>
+        <v>134.31</v>
       </c>
       <c r="Q76">
-        <v>108.52</v>
+        <v>53.69</v>
       </c>
       <c r="R76">
-        <v>8330510.44</v>
+        <v>1245873.15</v>
       </c>
     </row>
     <row r="77">
@@ -6178,7 +6178,7 @@
         </is>
       </c>
       <c r="G77">
-        <v>0.057</v>
+        <v>0.048</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6186,14 +6186,14 @@
         </is>
       </c>
       <c r="I77">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="J77">
-        <v>0.095</v>
+        <v>0.127</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6240,21 +6240,21 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Midi-Pyrénées</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G78">
-        <v>0.063</v>
+        <v>0.049</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6262,10 +6262,10 @@
         </is>
       </c>
       <c r="I78">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J78">
-        <v>0.201</v>
+        <v>0.133</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6283,19 +6283,19 @@
         </is>
       </c>
       <c r="N78">
-        <v>0</v>
+        <v>15369</v>
       </c>
       <c r="O78">
-        <v>35098</v>
+        <v>247142</v>
       </c>
       <c r="P78">
-        <v>306.53</v>
+        <v>1081.43</v>
       </c>
       <c r="Q78">
-        <v>19.57</v>
+        <v>234.3</v>
       </c>
       <c r="R78">
-        <v>587231.1800000001</v>
+        <v>2838676.28</v>
       </c>
     </row>
     <row r="79">
@@ -6316,12 +6316,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6330,7 +6330,7 @@
         </is>
       </c>
       <c r="G79">
-        <v>0.068</v>
+        <v>0.062</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6338,14 +6338,14 @@
         </is>
       </c>
       <c r="I79">
-        <v>0.027</v>
+        <v>0.012</v>
       </c>
       <c r="J79">
-        <v>0.107</v>
+        <v>0.198</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6359,19 +6359,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>15369</v>
+        <v>21411</v>
       </c>
       <c r="O79">
-        <v>247142</v>
+        <v>173122</v>
       </c>
       <c r="P79">
-        <v>1081.43</v>
+        <v>757.54</v>
       </c>
       <c r="Q79">
-        <v>234.3</v>
+        <v>164.12</v>
       </c>
       <c r="R79">
-        <v>2838676.28</v>
+        <v>1988480.52</v>
       </c>
     </row>
     <row r="80">
@@ -6392,12 +6392,12 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FRH0</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bretagne</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6406,7 +6406,7 @@
         </is>
       </c>
       <c r="G80">
-        <v>0.076</v>
+        <v>0.064</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -6414,10 +6414,10 @@
         </is>
       </c>
       <c r="I80">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J80">
-        <v>0.292</v>
+        <v>0.227</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6431,23 +6431,23 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80">
-        <v>24663</v>
+        <v>35098</v>
       </c>
       <c r="P80">
-        <v>215.4</v>
+        <v>306.53</v>
       </c>
       <c r="Q80">
-        <v>13.75</v>
+        <v>19.57</v>
       </c>
       <c r="R80">
-        <v>412654.25</v>
+        <v>587231.1800000001</v>
       </c>
     </row>
     <row r="81">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DE24</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Oberfranken</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6482,7 +6482,7 @@
         </is>
       </c>
       <c r="G81">
-        <v>0.078</v>
+        <v>0.067</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6493,7 +6493,7 @@
         <v>0.013</v>
       </c>
       <c r="J81">
-        <v>0.277</v>
+        <v>0.213</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6511,19 +6511,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>0</v>
+        <v>37878</v>
       </c>
       <c r="O81">
-        <v>47210</v>
+        <v>128381</v>
       </c>
       <c r="P81">
-        <v>206.58</v>
+        <v>561.76</v>
       </c>
       <c r="Q81">
-        <v>44.76</v>
+        <v>121.71</v>
       </c>
       <c r="R81">
-        <v>542256.03</v>
+        <v>1474591.88</v>
       </c>
     </row>
     <row r="82">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6558,18 +6558,18 @@
         </is>
       </c>
       <c r="G82">
-        <v>0.421</v>
+        <v>0.147</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I82">
-        <v>0.179</v>
+        <v>0.014</v>
       </c>
       <c r="J82">
-        <v>0.486</v>
+        <v>0.858</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6583,23 +6583,23 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N82">
-        <v>10280</v>
+        <v>0</v>
       </c>
       <c r="O82">
-        <v>2681294</v>
+        <v>144473</v>
       </c>
       <c r="P82">
-        <v>799.1900000000001</v>
+        <v>43.06</v>
       </c>
       <c r="Q82">
-        <v>1215.52</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="R82">
-        <v>42329157.17</v>
+        <v>2280771.98</v>
       </c>
     </row>
     <row r="83">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ITH5</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Emilia-Romagna</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6634,18 +6634,18 @@
         </is>
       </c>
       <c r="G83">
-        <v>0.335</v>
+        <v>0.146</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I83">
-        <v>0.11</v>
+        <v>0.015</v>
       </c>
       <c r="J83">
-        <v>0.508</v>
+        <v>0.794</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6659,23 +6659,23 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N83">
         <v>0</v>
       </c>
       <c r="O83">
-        <v>1586927</v>
+        <v>52080</v>
       </c>
       <c r="P83">
-        <v>473</v>
+        <v>15.52</v>
       </c>
       <c r="Q83">
-        <v>719.41</v>
+        <v>23.61</v>
       </c>
       <c r="R83">
-        <v>25052561.22</v>
+        <v>822183.05</v>
       </c>
     </row>
     <row r="84">
@@ -6696,32 +6696,32 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G84">
-        <v>0.329</v>
+        <v>0.143</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I84">
-        <v>0.108</v>
+        <v>0.016</v>
       </c>
       <c r="J84">
-        <v>0.499</v>
+        <v>0.708</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6735,23 +6735,23 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N84">
         <v>0</v>
       </c>
       <c r="O84">
-        <v>1553753</v>
+        <v>46816</v>
       </c>
       <c r="P84">
-        <v>463.12</v>
+        <v>32.93</v>
       </c>
       <c r="Q84">
-        <v>704.37</v>
+        <v>15.67</v>
       </c>
       <c r="R84">
-        <v>24528846.55</v>
+        <v>303671.29</v>
       </c>
     </row>
     <row r="85">
@@ -6772,32 +6772,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Yugoiztochen</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G85">
-        <v>0.267</v>
+        <v>0.143</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I85">
-        <v>0.07199999999999999</v>
+        <v>0.015</v>
       </c>
       <c r="J85">
-        <v>0.499</v>
+        <v>0.771</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6811,23 +6811,23 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N85">
-        <v>4027</v>
+        <v>0</v>
       </c>
       <c r="O85">
-        <v>977352</v>
+        <v>123396</v>
       </c>
       <c r="P85">
-        <v>291.31</v>
+        <v>35.44</v>
       </c>
       <c r="Q85">
-        <v>443.07</v>
+        <v>92.62</v>
       </c>
       <c r="R85">
-        <v>15429304.02</v>
+        <v>1371390</v>
       </c>
     </row>
     <row r="86">
@@ -6862,18 +6862,18 @@
         </is>
       </c>
       <c r="G86">
-        <v>0.217</v>
+        <v>0.143</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I86">
-        <v>0.029</v>
+        <v>0.014</v>
       </c>
       <c r="J86">
-        <v>0.838</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>0.052</v>
+        <v>0.034</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6946,10 +6946,10 @@
         </is>
       </c>
       <c r="I87">
-        <v>0.024</v>
+        <v>0.011</v>
       </c>
       <c r="J87">
-        <v>0.073</v>
+        <v>0.068</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G88">
-        <v>0.063</v>
+        <v>0.039</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7022,14 +7022,14 @@
         </is>
       </c>
       <c r="I88">
-        <v>0.016</v>
+        <v>0.013</v>
       </c>
       <c r="J88">
-        <v>0.156</v>
+        <v>0.075</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7046,16 +7046,16 @@
         <v>0</v>
       </c>
       <c r="O88">
-        <v>90316</v>
+        <v>700466</v>
       </c>
       <c r="P88">
-        <v>71.31999999999999</v>
+        <v>553.14</v>
       </c>
       <c r="Q88">
-        <v>146.44</v>
+        <v>1135.74</v>
       </c>
       <c r="R88">
-        <v>2979241.95</v>
+        <v>23106234.76</v>
       </c>
     </row>
     <row r="89">
@@ -7076,12 +7076,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="G89">
-        <v>0.065</v>
+        <v>0.053</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7098,10 +7098,10 @@
         </is>
       </c>
       <c r="I89">
-        <v>0.014</v>
+        <v>0.012</v>
       </c>
       <c r="J89">
-        <v>0.184</v>
+        <v>0.14</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7119,19 +7119,19 @@
         </is>
       </c>
       <c r="N89">
-        <v>0</v>
+        <v>1633</v>
       </c>
       <c r="O89">
-        <v>67103</v>
+        <v>283584</v>
       </c>
       <c r="P89">
-        <v>52.99</v>
+        <v>223.94</v>
       </c>
       <c r="Q89">
-        <v>108.8</v>
+        <v>459.81</v>
       </c>
       <c r="R89">
-        <v>2213528.69</v>
+        <v>9354575.140000001</v>
       </c>
     </row>
     <row r="90">
@@ -7152,21 +7152,21 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G90">
-        <v>0.068</v>
+        <v>0.054</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7174,10 +7174,10 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="J90">
-        <v>0.185</v>
+        <v>0.155</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7198,16 +7198,16 @@
         <v>0</v>
       </c>
       <c r="O90">
-        <v>83332</v>
+        <v>90316</v>
       </c>
       <c r="P90">
-        <v>21.5</v>
+        <v>71.31999999999999</v>
       </c>
       <c r="Q90">
-        <v>12.69</v>
+        <v>146.44</v>
       </c>
       <c r="R90">
-        <v>1354951.28</v>
+        <v>2979241.95</v>
       </c>
     </row>
     <row r="91">
@@ -7228,21 +7228,21 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Midi-Pyrénées</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G91">
-        <v>0.076</v>
+        <v>0.058</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7250,10 +7250,10 @@
         </is>
       </c>
       <c r="I91">
-        <v>0.017</v>
+        <v>0.011</v>
       </c>
       <c r="J91">
-        <v>0.197</v>
+        <v>0.183</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7271,19 +7271,19 @@
         </is>
       </c>
       <c r="N91">
-        <v>15491</v>
+        <v>0</v>
       </c>
       <c r="O91">
-        <v>100385</v>
+        <v>67103</v>
       </c>
       <c r="P91">
-        <v>68.70999999999999</v>
+        <v>52.99</v>
       </c>
       <c r="Q91">
-        <v>26.72</v>
+        <v>108.8</v>
       </c>
       <c r="R91">
-        <v>2076421.49</v>
+        <v>2213528.69</v>
       </c>
     </row>
     <row r="92">
@@ -7304,32 +7304,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>HU31</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Észak-Magyarország</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G92">
-        <v>0.259</v>
+        <v>0.157</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I92">
-        <v>0.083</v>
+        <v>0.017</v>
       </c>
       <c r="J92">
-        <v>0.406</v>
+        <v>0.773</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7343,23 +7343,23 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N92">
         <v>0</v>
       </c>
       <c r="O92">
-        <v>1162570</v>
+        <v>260030</v>
       </c>
       <c r="P92">
-        <v>358.34</v>
+        <v>57.56</v>
       </c>
       <c r="Q92">
-        <v>293.89</v>
+        <v>23.9</v>
       </c>
       <c r="R92">
-        <v>15617748.1</v>
+        <v>3625407.71</v>
       </c>
     </row>
     <row r="93">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>HU23</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Dél-Dunántúl</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G93">
-        <v>0.208</v>
+        <v>0.152</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I93">
-        <v>0.051</v>
+        <v>0.017</v>
       </c>
       <c r="J93">
-        <v>0.44</v>
+        <v>0.745</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7426,16 +7426,16 @@
         <v>0</v>
       </c>
       <c r="O93">
-        <v>644073</v>
+        <v>153517</v>
       </c>
       <c r="P93">
-        <v>198.52</v>
+        <v>33.98</v>
       </c>
       <c r="Q93">
-        <v>162.82</v>
+        <v>14.11</v>
       </c>
       <c r="R93">
-        <v>8652353.99</v>
+        <v>2140375.24</v>
       </c>
     </row>
     <row r="94">
@@ -7456,32 +7456,32 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>HU31</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Észak-Magyarország</t>
+          <t>Peloponnisos</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G94">
-        <v>0.202</v>
+        <v>0.147</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I94">
-        <v>0.026</v>
+        <v>0.017</v>
       </c>
       <c r="J94">
-        <v>0.799</v>
+        <v>0.7</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7495,23 +7495,23 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N94">
         <v>0</v>
       </c>
       <c r="O94">
-        <v>260030</v>
+        <v>41080</v>
       </c>
       <c r="P94">
-        <v>57.56</v>
+        <v>7.64</v>
       </c>
       <c r="Q94">
-        <v>23.9</v>
+        <v>7.36</v>
       </c>
       <c r="R94">
-        <v>3625407.71</v>
+        <v>246608.06</v>
       </c>
     </row>
     <row r="95">
@@ -7532,21 +7532,21 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>EL30</t>
+          <t>HU12</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Attiki</t>
+          <t>Pest</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G95">
-        <v>0.195</v>
+        <v>0.141</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="I95">
-        <v>0.032</v>
+        <v>0.018</v>
       </c>
       <c r="J95">
-        <v>0.625</v>
+        <v>0.624</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7578,16 +7578,16 @@
         <v>0</v>
       </c>
       <c r="O95">
-        <v>342018</v>
+        <v>270480</v>
       </c>
       <c r="P95">
-        <v>63.64</v>
+        <v>59.87</v>
       </c>
       <c r="Q95">
-        <v>61.28</v>
+        <v>24.86</v>
       </c>
       <c r="R95">
-        <v>2053165.64</v>
+        <v>3771099.29</v>
       </c>
     </row>
     <row r="96">
@@ -7608,21 +7608,21 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Közép-Dunántúl</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G96">
-        <v>0.194</v>
+        <v>0.141</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         </is>
       </c>
       <c r="I96">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="J96">
-        <v>0.662</v>
+        <v>0.828</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7647,23 +7647,23 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N96">
         <v>0</v>
       </c>
       <c r="O96">
-        <v>307086</v>
+        <v>122138</v>
       </c>
       <c r="P96">
-        <v>67.98</v>
+        <v>37.65</v>
       </c>
       <c r="Q96">
-        <v>28.23</v>
+        <v>30.88</v>
       </c>
       <c r="R96">
-        <v>4281480.81</v>
+        <v>1640775.09</v>
       </c>
     </row>
     <row r="97">
@@ -7684,21 +7684,21 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>SE23</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Västsverige</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G97">
-        <v>0.033</v>
+        <v>0.032</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7706,10 +7706,10 @@
         </is>
       </c>
       <c r="I97">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J97">
-        <v>0.06900000000000001</v>
+        <v>0.062</v>
       </c>
       <c r="K97" t="inlineStr">
         <is>
@@ -7723,23 +7723,23 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N97">
         <v>0</v>
       </c>
       <c r="O97">
-        <v>33026</v>
+        <v>171192</v>
       </c>
       <c r="P97">
-        <v>6.82</v>
+        <v>126.02</v>
       </c>
       <c r="Q97">
-        <v>3.91</v>
+        <v>139.07</v>
       </c>
       <c r="R97">
-        <v>1062183.55</v>
+        <v>7194730.05</v>
       </c>
     </row>
     <row r="98">
@@ -7760,12 +7760,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.043</v>
+        <v>0.034</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7782,10 +7782,10 @@
         </is>
       </c>
       <c r="I98">
-        <v>0.021</v>
+        <v>0.011</v>
       </c>
       <c r="J98">
-        <v>0.061</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K98" t="inlineStr">
         <is>
@@ -7806,16 +7806,16 @@
         <v>0</v>
       </c>
       <c r="O98">
-        <v>171192</v>
+        <v>184643</v>
       </c>
       <c r="P98">
-        <v>126.02</v>
+        <v>135.92</v>
       </c>
       <c r="Q98">
-        <v>139.07</v>
+        <v>150</v>
       </c>
       <c r="R98">
-        <v>7194730.05</v>
+        <v>7760059.23</v>
       </c>
     </row>
     <row r="99">
@@ -7836,12 +7836,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>SE23</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Västsverige</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="G99">
-        <v>0.046</v>
+        <v>0.038</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7858,14 +7858,14 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="J99">
-        <v>0.119</v>
+        <v>0.089</v>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7882,16 +7882,16 @@
         <v>0</v>
       </c>
       <c r="O99">
-        <v>30645</v>
+        <v>33026</v>
       </c>
       <c r="P99">
-        <v>6.32</v>
+        <v>6.82</v>
       </c>
       <c r="Q99">
-        <v>3.62</v>
+        <v>3.91</v>
       </c>
       <c r="R99">
-        <v>985589.2</v>
+        <v>1062183.55</v>
       </c>
     </row>
     <row r="100">
@@ -7912,12 +7912,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="G100">
-        <v>0.047</v>
+        <v>0.049</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7934,14 +7934,14 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.022</v>
+        <v>0.011</v>
       </c>
       <c r="J100">
-        <v>0.068</v>
+        <v>0.134</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7958,16 +7958,16 @@
         <v>0</v>
       </c>
       <c r="O100">
-        <v>184643</v>
+        <v>117259</v>
       </c>
       <c r="P100">
-        <v>135.92</v>
+        <v>86.31999999999999</v>
       </c>
       <c r="Q100">
-        <v>150</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="R100">
-        <v>7760059.23</v>
+        <v>4928060.29</v>
       </c>
     </row>
     <row r="101">
@@ -7988,21 +7988,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G101">
-        <v>0.051</v>
+        <v>0.05</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8013,7 +8013,7 @@
         <v>0.011</v>
       </c>
       <c r="J101">
-        <v>0.147</v>
+        <v>0.139</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
@@ -8027,23 +8027,23 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N101">
         <v>0</v>
       </c>
       <c r="O101">
-        <v>23767</v>
+        <v>30645</v>
       </c>
       <c r="P101">
-        <v>17.5</v>
+        <v>6.32</v>
       </c>
       <c r="Q101">
-        <v>19.31</v>
+        <v>3.62</v>
       </c>
       <c r="R101">
-        <v>998863.6899999999</v>
+        <v>985589.2</v>
       </c>
     </row>
     <row r="102">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ITC1</t>
+          <t>ITF5</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Piemonte</t>
+          <t>Basilicata</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8078,18 +8078,18 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.277</v>
+        <v>0.175</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I102">
-        <v>0.078</v>
+        <v>0.025</v>
       </c>
       <c r="J102">
-        <v>0.495</v>
+        <v>0.676</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8103,23 +8103,23 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N102">
-        <v>31994</v>
+        <v>0</v>
       </c>
       <c r="O102">
-        <v>1049029</v>
+        <v>143902</v>
       </c>
       <c r="P102">
-        <v>289.33</v>
+        <v>39.69</v>
       </c>
       <c r="Q102">
-        <v>198.49</v>
+        <v>27.23</v>
       </c>
       <c r="R102">
-        <v>14063963.73</v>
+        <v>1929245.25</v>
       </c>
     </row>
     <row r="103">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8154,18 +8154,18 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.256</v>
+        <v>0.167</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I103">
-        <v>0.039</v>
+        <v>0.021</v>
       </c>
       <c r="J103">
-        <v>0.842</v>
+        <v>0.718</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8179,23 +8179,23 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N103">
-        <v>20202</v>
+        <v>0</v>
       </c>
       <c r="O103">
-        <v>444867</v>
+        <v>52120</v>
       </c>
       <c r="P103">
-        <v>122.7</v>
+        <v>14.37</v>
       </c>
       <c r="Q103">
-        <v>84.17</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R103">
-        <v>5964174.91</v>
+        <v>698757.04</v>
       </c>
     </row>
     <row r="104">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8230,18 +8230,18 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.219</v>
+        <v>0.154</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Very Low</t>
         </is>
       </c>
       <c r="I104">
-        <v>0.056</v>
+        <v>0.016</v>
       </c>
       <c r="J104">
-        <v>0.44</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8255,23 +8255,23 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N104">
-        <v>25976</v>
+        <v>20202</v>
       </c>
       <c r="O104">
-        <v>698500</v>
+        <v>444867</v>
       </c>
       <c r="P104">
-        <v>192.65</v>
+        <v>122.7</v>
       </c>
       <c r="Q104">
-        <v>132.16</v>
+        <v>84.17</v>
       </c>
       <c r="R104">
-        <v>9364551.119999999</v>
+        <v>5964174.91</v>
       </c>
     </row>
     <row r="105">
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="G105">
-        <v>0.196</v>
+        <v>0.144</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
@@ -8314,10 +8314,10 @@
         </is>
       </c>
       <c r="I105">
-        <v>0.029</v>
+        <v>0.017</v>
       </c>
       <c r="J105">
-        <v>0.694</v>
+        <v>0.67</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8368,21 +8368,21 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>HU21</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Közép-Dunántúl</t>
+          <t>Sud-Muntenia</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G106">
-        <v>0.193</v>
+        <v>0.142</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="I106">
-        <v>0.029</v>
+        <v>0.013</v>
       </c>
       <c r="J106">
-        <v>0.668</v>
+        <v>0.854</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8407,23 +8407,23 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N106">
-        <v>13704</v>
+        <v>50567</v>
       </c>
       <c r="O106">
-        <v>283291</v>
+        <v>123303</v>
       </c>
       <c r="P106">
-        <v>72.14</v>
+        <v>22.11</v>
       </c>
       <c r="Q106">
-        <v>105.78</v>
+        <v>68.05</v>
       </c>
       <c r="R106">
-        <v>7381652.83</v>
+        <v>2513284.1</v>
       </c>
     </row>
     <row r="107">
@@ -8444,21 +8444,21 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G107">
-        <v>0.055</v>
+        <v>0.041</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8466,14 +8466,14 @@
         </is>
       </c>
       <c r="I107">
-        <v>0.01</v>
+        <v>0.015</v>
       </c>
       <c r="J107">
-        <v>0.187</v>
+        <v>0.073</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8487,19 +8487,19 @@
         </is>
       </c>
       <c r="N107">
-        <v>0</v>
+        <v>64206</v>
       </c>
       <c r="O107">
-        <v>5033</v>
+        <v>791924</v>
       </c>
       <c r="P107">
-        <v>1.17</v>
+        <v>717.54</v>
       </c>
       <c r="Q107">
-        <v>0.75</v>
+        <v>648.95</v>
       </c>
       <c r="R107">
-        <v>71680.19</v>
+        <v>28609895.88</v>
       </c>
     </row>
     <row r="108">
@@ -8520,21 +8520,21 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LU00</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>LU</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G108">
-        <v>0.064</v>
+        <v>0.042</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8542,14 +8542,14 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.01</v>
+        <v>0.014</v>
       </c>
       <c r="J108">
-        <v>0.252</v>
+        <v>0.08</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8566,16 +8566,16 @@
         <v>0</v>
       </c>
       <c r="O108">
-        <v>2049</v>
+        <v>923297</v>
       </c>
       <c r="P108">
-        <v>0.99</v>
+        <v>836.5700000000001</v>
       </c>
       <c r="Q108">
-        <v>0.38</v>
+        <v>756.6</v>
       </c>
       <c r="R108">
-        <v>100966.09</v>
+        <v>33356003.01</v>
       </c>
     </row>
     <row r="109">
@@ -8596,21 +8596,21 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>FRK1</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Auvergne</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G109">
-        <v>0.066</v>
+        <v>0.055</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="I109">
-        <v>0.011</v>
+        <v>0.013</v>
       </c>
       <c r="J109">
-        <v>0.244</v>
+        <v>0.145</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8635,23 +8635,23 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N109">
-        <v>0</v>
+        <v>45701</v>
       </c>
       <c r="O109">
-        <v>12016</v>
+        <v>256023</v>
       </c>
       <c r="P109">
-        <v>8.42</v>
+        <v>231.98</v>
       </c>
       <c r="Q109">
-        <v>2.76</v>
+        <v>209.8</v>
       </c>
       <c r="R109">
-        <v>734820.3</v>
+        <v>9249367.83</v>
       </c>
     </row>
     <row r="110">
@@ -8672,21 +8672,21 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DE72</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Gießen</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G110">
-        <v>0.068</v>
+        <v>0.056</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8694,10 +8694,10 @@
         </is>
       </c>
       <c r="I110">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J110">
-        <v>0.258</v>
+        <v>0.187</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8718,16 +8718,16 @@
         <v>0</v>
       </c>
       <c r="O110">
-        <v>14100</v>
+        <v>5033</v>
       </c>
       <c r="P110">
-        <v>12.78</v>
+        <v>1.17</v>
       </c>
       <c r="Q110">
-        <v>11.55</v>
+        <v>0.75</v>
       </c>
       <c r="R110">
-        <v>509379.55</v>
+        <v>71680.19</v>
       </c>
     </row>
     <row r="111">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="G111">
-        <v>0.06900000000000001</v>
+        <v>0.056</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8770,10 +8770,10 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.018</v>
+        <v>0.012</v>
       </c>
       <c r="J111">
-        <v>0.159</v>
+        <v>0.16</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
@@ -8824,12 +8824,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>ITH3</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Veneto</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -8838,7 +8838,7 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.178</v>
+        <v>0.134</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
@@ -8846,10 +8846,10 @@
         </is>
       </c>
       <c r="I112">
-        <v>0.037</v>
+        <v>0.012</v>
       </c>
       <c r="J112">
-        <v>0.44</v>
+        <v>0.827</v>
       </c>
       <c r="K112" t="inlineStr">
         <is>
@@ -8863,23 +8863,23 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N112">
         <v>0</v>
       </c>
       <c r="O112">
-        <v>434257</v>
+        <v>74477</v>
       </c>
       <c r="P112">
-        <v>186.54</v>
+        <v>31.99</v>
       </c>
       <c r="Q112">
-        <v>175.44</v>
+        <v>30.09</v>
       </c>
       <c r="R112">
-        <v>7172775.27</v>
+        <v>1230156.3</v>
       </c>
     </row>
     <row r="113">
@@ -8900,21 +8900,21 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>ITC4</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Lombardia</t>
+          <t>Severozapaden</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G113">
-        <v>0.175</v>
+        <v>0.13</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
@@ -8922,10 +8922,10 @@
         </is>
       </c>
       <c r="I113">
-        <v>0.04</v>
+        <v>0.011</v>
       </c>
       <c r="J113">
-        <v>0.402</v>
+        <v>0.89</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N113">
         <v>0</v>
       </c>
       <c r="O113">
-        <v>471415</v>
+        <v>9006</v>
       </c>
       <c r="P113">
-        <v>202.51</v>
+        <v>4.94</v>
       </c>
       <c r="Q113">
-        <v>190.46</v>
+        <v>9.67</v>
       </c>
       <c r="R113">
-        <v>7786521.89</v>
+        <v>154843.1</v>
       </c>
     </row>
     <row r="114">
@@ -8976,12 +8976,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8990,7 +8990,7 @@
         </is>
       </c>
       <c r="G114">
-        <v>0.162</v>
+        <v>0.127</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
@@ -8998,10 +8998,10 @@
         </is>
       </c>
       <c r="I114">
-        <v>0.017</v>
+        <v>0.012</v>
       </c>
       <c r="J114">
-        <v>0.803</v>
+        <v>0.763</v>
       </c>
       <c r="K114" t="inlineStr">
         <is>
@@ -9022,16 +9022,16 @@
         <v>0</v>
       </c>
       <c r="O114">
-        <v>112924</v>
+        <v>19347</v>
       </c>
       <c r="P114">
-        <v>48.51</v>
+        <v>8.31</v>
       </c>
       <c r="Q114">
-        <v>45.62</v>
+        <v>7.82</v>
       </c>
       <c r="R114">
-        <v>1865207.41</v>
+        <v>319567.23</v>
       </c>
     </row>
     <row r="115">
@@ -9052,12 +9052,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9066,7 +9066,7 @@
         </is>
       </c>
       <c r="G115">
-        <v>0.154</v>
+        <v>0.127</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
@@ -9074,10 +9074,10 @@
         </is>
       </c>
       <c r="I115">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="J115">
-        <v>0.856</v>
+        <v>0.776</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -9098,16 +9098,16 @@
         <v>0</v>
       </c>
       <c r="O115">
-        <v>74477</v>
+        <v>112924</v>
       </c>
       <c r="P115">
-        <v>31.99</v>
+        <v>48.51</v>
       </c>
       <c r="Q115">
-        <v>30.09</v>
+        <v>45.62</v>
       </c>
       <c r="R115">
-        <v>1230156.3</v>
+        <v>1865207.41</v>
       </c>
     </row>
     <row r="116">
@@ -9128,21 +9128,21 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>ITF4</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Puglia</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G116">
-        <v>0.154</v>
+        <v>0.126</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
@@ -9150,10 +9150,10 @@
         </is>
       </c>
       <c r="I116">
-        <v>0.017</v>
+        <v>0.01</v>
       </c>
       <c r="J116">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -9167,23 +9167,23 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N116">
         <v>0</v>
       </c>
       <c r="O116">
-        <v>116778</v>
+        <v>10497</v>
       </c>
       <c r="P116">
-        <v>50.16</v>
+        <v>15.96</v>
       </c>
       <c r="Q116">
-        <v>47.18</v>
+        <v>1.75</v>
       </c>
       <c r="R116">
-        <v>1928854.55</v>
+        <v>270621.74</v>
       </c>
     </row>
     <row r="117">
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="I117">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="J117">
-        <v>0.059</v>
+        <v>0.063</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="G118">
-        <v>0.034</v>
+        <v>0.033</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9302,10 +9302,10 @@
         </is>
       </c>
       <c r="I118">
-        <v>0.013</v>
+        <v>0.01</v>
       </c>
       <c r="J118">
-        <v>0.066</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="G119">
-        <v>0.036</v>
+        <v>0.037</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9378,10 +9378,10 @@
         </is>
       </c>
       <c r="I119">
-        <v>0.012</v>
+        <v>0.01</v>
       </c>
       <c r="J119">
-        <v>0.081</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
@@ -9432,21 +9432,21 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G120">
-        <v>0.043</v>
+        <v>0.047</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9454,10 +9454,10 @@
         </is>
       </c>
       <c r="I120">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J120">
-        <v>0.116</v>
+        <v>0.134</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
@@ -9471,23 +9471,23 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N120">
         <v>0</v>
       </c>
       <c r="O120">
-        <v>15262</v>
+        <v>43186</v>
       </c>
       <c r="P120">
-        <v>19.28</v>
+        <v>44.32</v>
       </c>
       <c r="Q120">
-        <v>3.19</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="R120">
-        <v>452048.49</v>
+        <v>1769713.22</v>
       </c>
     </row>
     <row r="121">
@@ -9508,21 +9508,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>SE11</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Stockholm</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G121">
-        <v>0.05</v>
+        <v>0.048</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9530,10 +9530,10 @@
         </is>
       </c>
       <c r="I121">
-        <v>0.011</v>
+        <v>0.01</v>
       </c>
       <c r="J121">
-        <v>0.147</v>
+        <v>0.136</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
@@ -9547,23 +9547,23 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N121">
         <v>0</v>
       </c>
       <c r="O121">
-        <v>19792</v>
+        <v>15262</v>
       </c>
       <c r="P121">
-        <v>20.31</v>
+        <v>19.28</v>
       </c>
       <c r="Q121">
-        <v>35.41</v>
+        <v>3.19</v>
       </c>
       <c r="R121">
-        <v>811071.84</v>
+        <v>452048.49</v>
       </c>
     </row>
   </sheetData>

--- a/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
+++ b/Code and data/Final data/Top_Bottom_Regions_per_Sector.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -486,10 +486,10 @@
         </is>
       </c>
       <c r="I2">
-        <v>0.495</v>
+        <v>0.738</v>
       </c>
       <c r="J2">
-        <v>0.711</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -507,19 +507,19 @@
         </is>
       </c>
       <c r="N2">
-        <v>6177767</v>
+        <v>6876932</v>
       </c>
       <c r="O2">
-        <v>558559</v>
+        <v>1386007</v>
       </c>
       <c r="P2">
-        <v>748.6900000000001</v>
+        <v>2180.71</v>
       </c>
       <c r="Q2">
-        <v>234.08</v>
+        <v>681.8200000000001</v>
       </c>
       <c r="R2">
-        <v>8641139.41</v>
+        <v>25169243.03</v>
       </c>
     </row>
     <row r="3">
@@ -540,21 +540,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G3">
-        <v>0.988</v>
+        <v>0.962</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -562,14 +562,14 @@
         </is>
       </c>
       <c r="I3">
-        <v>0.99</v>
+        <v>0.86</v>
       </c>
       <c r="J3">
-        <v>0.354</v>
+        <v>0.761</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Exposure-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -579,23 +579,23 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N3">
-        <v>7771088</v>
+        <v>3330456</v>
       </c>
       <c r="O3">
-        <v>888957</v>
+        <v>257727</v>
       </c>
       <c r="P3">
-        <v>1161.22</v>
+        <v>860.8099999999999</v>
       </c>
       <c r="Q3">
-        <v>281.13</v>
+        <v>209.63</v>
       </c>
       <c r="R3">
-        <v>10723428.75</v>
+        <v>4930103.2</v>
       </c>
     </row>
     <row r="4">
@@ -616,12 +616,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sterea Elláda</t>
+          <t>Peloponnisos</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.966</v>
+        <v>0.944</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -638,14 +638,14 @@
         </is>
       </c>
       <c r="I4">
-        <v>0.441</v>
+        <v>0.825</v>
       </c>
       <c r="J4">
-        <v>0.761</v>
+        <v>0.766</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -659,19 +659,19 @@
         </is>
       </c>
       <c r="N4">
-        <v>3330456</v>
+        <v>2060741</v>
       </c>
       <c r="O4">
-        <v>257727</v>
+        <v>115141</v>
       </c>
       <c r="P4">
-        <v>860.8099999999999</v>
+        <v>645.95</v>
       </c>
       <c r="Q4">
-        <v>209.63</v>
+        <v>157.3</v>
       </c>
       <c r="R4">
-        <v>4930103.2</v>
+        <v>3699531.08</v>
       </c>
     </row>
     <row r="5">
@@ -692,21 +692,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>ITG2</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Peloponnisos</t>
+          <t>Sardegna</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G5">
-        <v>0.871</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -714,14 +714,14 @@
         </is>
       </c>
       <c r="I5">
-        <v>0.359</v>
+        <v>0.879</v>
       </c>
       <c r="J5">
-        <v>0.766</v>
+        <v>0.711</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -731,23 +731,23 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N5">
-        <v>2060741</v>
+        <v>6177767</v>
       </c>
       <c r="O5">
-        <v>115141</v>
+        <v>558559</v>
       </c>
       <c r="P5">
-        <v>645.95</v>
+        <v>748.6900000000001</v>
       </c>
       <c r="Q5">
-        <v>157.3</v>
+        <v>234.08</v>
       </c>
       <c r="R5">
-        <v>3699531.08</v>
+        <v>8641139.41</v>
       </c>
     </row>
     <row r="6">
@@ -768,32 +768,32 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G6">
-        <v>0.74</v>
+        <v>0.923</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I6">
-        <v>0.214</v>
+        <v>0.611</v>
       </c>
       <c r="J6">
-        <v>0.9340000000000001</v>
+        <v>0.99</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -807,23 +807,23 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N6">
-        <v>6876932</v>
+        <v>3280006</v>
       </c>
       <c r="O6">
-        <v>1386007</v>
+        <v>342510</v>
       </c>
       <c r="P6">
-        <v>2180.71</v>
+        <v>1880.1</v>
       </c>
       <c r="Q6">
-        <v>681.8200000000001</v>
+        <v>383.57</v>
       </c>
       <c r="R6">
-        <v>25169243.03</v>
+        <v>9538553.960000001</v>
       </c>
     </row>
     <row r="7">
@@ -844,12 +844,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="I7">
-        <v>0.025</v>
+        <v>0.47</v>
       </c>
       <c r="J7">
-        <v>0.018</v>
+        <v>0.01</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -887,19 +887,19 @@
         </is>
       </c>
       <c r="N7">
-        <v>531401</v>
+        <v>3575300</v>
       </c>
       <c r="O7">
-        <v>3071397</v>
+        <v>3458269</v>
       </c>
       <c r="P7">
-        <v>14033.72</v>
+        <v>10466.87</v>
       </c>
       <c r="Q7">
-        <v>5831.56</v>
+        <v>4349.39</v>
       </c>
       <c r="R7">
-        <v>107779015.7</v>
+        <v>80385552.20999999</v>
       </c>
     </row>
     <row r="8">
@@ -920,12 +920,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -934,7 +934,7 @@
         </is>
       </c>
       <c r="G8">
-        <v>0.012</v>
+        <v>0.021</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -942,19 +942,19 @@
         </is>
       </c>
       <c r="I8">
-        <v>0.048</v>
+        <v>0.327</v>
       </c>
       <c r="J8">
-        <v>0.01</v>
+        <v>0.018</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -963,19 +963,19 @@
         </is>
       </c>
       <c r="N8">
-        <v>3575300</v>
+        <v>531401</v>
       </c>
       <c r="O8">
-        <v>3458269</v>
+        <v>3071397</v>
       </c>
       <c r="P8">
-        <v>10466.87</v>
+        <v>14033.72</v>
       </c>
       <c r="Q8">
-        <v>4349.39</v>
+        <v>5831.56</v>
       </c>
       <c r="R8">
-        <v>80385552.20999999</v>
+        <v>107779015.7</v>
       </c>
     </row>
     <row r="9">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="G9">
-        <v>0.097</v>
+        <v>0.2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I9">
-        <v>0.055</v>
+        <v>0.496</v>
       </c>
       <c r="J9">
         <v>0.094</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1072,36 +1072,36 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Midi-Pyrénées</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G10">
-        <v>0.099</v>
+        <v>0.242</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I10">
-        <v>0.034</v>
+        <v>0.412</v>
       </c>
       <c r="J10">
-        <v>0.156</v>
+        <v>0.15</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1115,19 +1115,19 @@
         </is>
       </c>
       <c r="N10">
-        <v>683183</v>
+        <v>159553</v>
       </c>
       <c r="O10">
-        <v>690041</v>
+        <v>682156</v>
       </c>
       <c r="P10">
-        <v>3328.96</v>
+        <v>1070.18</v>
       </c>
       <c r="Q10">
-        <v>270.27</v>
+        <v>219.43</v>
       </c>
       <c r="R10">
-        <v>28792983.21</v>
+        <v>18864500.95</v>
       </c>
     </row>
     <row r="11">
@@ -1148,36 +1148,36 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G11">
-        <v>0.1</v>
+        <v>0.243</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I11">
-        <v>0.036</v>
+        <v>0.399</v>
       </c>
       <c r="J11">
-        <v>0.15</v>
+        <v>0.156</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="N11">
-        <v>159553</v>
+        <v>683183</v>
       </c>
       <c r="O11">
-        <v>682156</v>
+        <v>690041</v>
       </c>
       <c r="P11">
-        <v>1070.18</v>
+        <v>3328.96</v>
       </c>
       <c r="Q11">
-        <v>219.43</v>
+        <v>270.27</v>
       </c>
       <c r="R11">
-        <v>18864500.95</v>
+        <v>28792983.21</v>
       </c>
     </row>
     <row r="12">
@@ -1238,15 +1238,15 @@
         </is>
       </c>
       <c r="G12">
-        <v>0.173</v>
+        <v>0.474</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I12">
-        <v>0.031</v>
+        <v>0.364</v>
       </c>
       <c r="J12">
         <v>0.522</v>
@@ -1300,32 +1300,32 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ES43</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Extremadura</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G13">
-        <v>0.168</v>
+        <v>0.457</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I13">
-        <v>0.026</v>
+        <v>0.218</v>
       </c>
       <c r="J13">
-        <v>0.597</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1343,19 +1343,19 @@
         </is>
       </c>
       <c r="N13">
-        <v>137081</v>
+        <v>55969</v>
       </c>
       <c r="O13">
-        <v>27085</v>
+        <v>227355</v>
       </c>
       <c r="P13">
-        <v>123.27</v>
+        <v>592.99</v>
       </c>
       <c r="Q13">
-        <v>40.4</v>
+        <v>307.42</v>
       </c>
       <c r="R13">
-        <v>4629062.5</v>
+        <v>15931427.45</v>
       </c>
     </row>
     <row r="14">
@@ -1376,32 +1376,32 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>BE34</t>
+          <t>BG32</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Prov. Luxembourg (BE)</t>
+          <t>Severen tsentralen</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G14">
-        <v>0.166</v>
+        <v>0.455</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I14">
-        <v>0.032</v>
+        <v>0.264</v>
       </c>
       <c r="J14">
-        <v>0.471</v>
+        <v>0.668</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1415,23 +1415,23 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N14">
-        <v>62764</v>
+        <v>119321</v>
       </c>
       <c r="O14">
-        <v>18402</v>
+        <v>14843</v>
       </c>
       <c r="P14">
-        <v>78.03</v>
+        <v>80.08</v>
       </c>
       <c r="Q14">
-        <v>26.34</v>
+        <v>67.14</v>
       </c>
       <c r="R14">
-        <v>2027563.68</v>
+        <v>1696569.53</v>
       </c>
     </row>
     <row r="15">
@@ -1452,32 +1452,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FRF2</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Champagne-Ardenne</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G15">
-        <v>0.165</v>
+        <v>0.449</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I15">
-        <v>0.034</v>
+        <v>0.199</v>
       </c>
       <c r="J15">
-        <v>0.441</v>
+        <v>0.865</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1486,28 +1486,28 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N15">
-        <v>602936</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>41664</v>
+        <v>164891</v>
       </c>
       <c r="P15">
-        <v>207.95</v>
+        <v>430.07</v>
       </c>
       <c r="Q15">
-        <v>35.74</v>
+        <v>222.96</v>
       </c>
       <c r="R15">
-        <v>6021671.25</v>
+        <v>11554402.49</v>
       </c>
     </row>
     <row r="16">
@@ -1528,32 +1528,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G16">
-        <v>0.164</v>
+        <v>0.448</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I16">
-        <v>0.039</v>
+        <v>0.266</v>
       </c>
       <c r="J16">
-        <v>0.38</v>
+        <v>0.643</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1567,23 +1567,23 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N16">
-        <v>222706</v>
+        <v>91307</v>
       </c>
       <c r="O16">
-        <v>18443</v>
+        <v>37486</v>
       </c>
       <c r="P16">
-        <v>120.32</v>
+        <v>95.38</v>
       </c>
       <c r="Q16">
-        <v>68.18000000000001</v>
+        <v>55.4</v>
       </c>
       <c r="R16">
-        <v>3940161.78</v>
+        <v>2574849.43</v>
       </c>
     </row>
     <row r="17">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>DE21</t>
+          <t>DE11</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oberbayern</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1618,7 +1618,7 @@
         </is>
       </c>
       <c r="G17">
-        <v>0.038</v>
+        <v>0.064</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="I17">
-        <v>0.01</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J17">
-        <v>0.09</v>
+        <v>0.097</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1647,19 +1647,19 @@
         </is>
       </c>
       <c r="N17">
-        <v>10246</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>60541</v>
+        <v>46545</v>
       </c>
       <c r="P17">
-        <v>652.27</v>
+        <v>501.47</v>
       </c>
       <c r="Q17">
-        <v>411.53</v>
+        <v>316.39</v>
       </c>
       <c r="R17">
-        <v>14406319.48</v>
+        <v>11075693.3</v>
       </c>
     </row>
     <row r="18">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DE11</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="G18">
-        <v>0.039</v>
+        <v>0.065</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1702,10 +1702,10 @@
         </is>
       </c>
       <c r="I18">
-        <v>0.01</v>
+        <v>0.094</v>
       </c>
       <c r="J18">
-        <v>0.097</v>
+        <v>0.09</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -1723,19 +1723,19 @@
         </is>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>10246</v>
       </c>
       <c r="O18">
-        <v>46545</v>
+        <v>60541</v>
       </c>
       <c r="P18">
-        <v>501.47</v>
+        <v>652.27</v>
       </c>
       <c r="Q18">
-        <v>316.39</v>
+        <v>411.53</v>
       </c>
       <c r="R18">
-        <v>11075693.3</v>
+        <v>14406319.48</v>
       </c>
     </row>
     <row r="19">
@@ -1770,7 +1770,7 @@
         </is>
       </c>
       <c r="G19">
-        <v>0.052</v>
+        <v>0.096</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1778,14 +1778,14 @@
         </is>
       </c>
       <c r="I19">
-        <v>0.01</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J19">
         <v>0.161</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DE71</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Darmstadt</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1846,7 +1846,7 @@
         </is>
       </c>
       <c r="G20">
-        <v>0.057</v>
+        <v>0.124</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1854,10 +1854,10 @@
         </is>
       </c>
       <c r="I20">
-        <v>0.011</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J20">
-        <v>0.176</v>
+        <v>0.233</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1875,19 +1875,19 @@
         </is>
       </c>
       <c r="N20">
-        <v>44811</v>
+        <v>0</v>
       </c>
       <c r="O20">
-        <v>16508</v>
+        <v>34762</v>
       </c>
       <c r="P20">
-        <v>177.86</v>
+        <v>374.52</v>
       </c>
       <c r="Q20">
-        <v>112.22</v>
+        <v>236.29</v>
       </c>
       <c r="R20">
-        <v>3928249.4</v>
+        <v>8271817.23</v>
       </c>
     </row>
     <row r="21">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>DE25</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Mittelfranken</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1922,7 +1922,7 @@
         </is>
       </c>
       <c r="G21">
-        <v>0.061</v>
+        <v>0.134</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1930,10 +1930,10 @@
         </is>
       </c>
       <c r="I21">
-        <v>0.011</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J21">
-        <v>0.205</v>
+        <v>0.262</v>
       </c>
       <c r="K21" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1951,19 +1951,19 @@
         </is>
       </c>
       <c r="N21">
-        <v>44932</v>
+        <v>0</v>
       </c>
       <c r="O21">
-        <v>9707</v>
+        <v>25781</v>
       </c>
       <c r="P21">
-        <v>104.58</v>
+        <v>277.77</v>
       </c>
       <c r="Q21">
-        <v>65.98</v>
+        <v>175.25</v>
       </c>
       <c r="R21">
-        <v>2309864.7</v>
+        <v>6134832.07</v>
       </c>
     </row>
     <row r="22">
@@ -1984,32 +1984,32 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>SI03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sud-Est</t>
+          <t>Vzhodna Slovenija</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G22">
-        <v>0.131</v>
+        <v>0.397</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I22">
-        <v>0.01</v>
+        <v>0.229</v>
       </c>
       <c r="J22">
-        <v>0.921</v>
+        <v>0.601</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -2023,23 +2023,23 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N22">
         <v>0</v>
       </c>
       <c r="O22">
-        <v>9584</v>
+        <v>37496</v>
       </c>
       <c r="P22">
-        <v>24.26</v>
+        <v>18.95</v>
       </c>
       <c r="Q22">
-        <v>10.58</v>
+        <v>9.9</v>
       </c>
       <c r="R22">
-        <v>274912.77</v>
+        <v>302861.42</v>
       </c>
     </row>
     <row r="23">
@@ -2060,32 +2060,32 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>BE10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Severozapaden</t>
+          <t>Région de Bruxelles-Capitale/ Brussels Hoofdstedelijk Gewest</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G23">
-        <v>0.13</v>
+        <v>0.386</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I23">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="J23">
-        <v>0.919</v>
+        <v>0.594</v>
       </c>
       <c r="K23" t="inlineStr">
         <is>
@@ -2106,16 +2106,16 @@
         <v>0</v>
       </c>
       <c r="O23">
-        <v>4087</v>
+        <v>3149</v>
       </c>
       <c r="P23">
-        <v>10.93</v>
+        <v>4.45</v>
       </c>
       <c r="Q23">
-        <v>12.2</v>
+        <v>2.02</v>
       </c>
       <c r="R23">
-        <v>174920.82</v>
+        <v>55074.65</v>
       </c>
     </row>
     <row r="24">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2150,18 +2150,18 @@
         </is>
       </c>
       <c r="G24">
-        <v>0.128</v>
+        <v>0.362</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I24">
-        <v>0.011</v>
+        <v>0.134</v>
       </c>
       <c r="J24">
-        <v>0.8149999999999999</v>
+        <v>0.866</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -2182,16 +2182,16 @@
         <v>0</v>
       </c>
       <c r="O24">
-        <v>88130</v>
+        <v>6794</v>
       </c>
       <c r="P24">
-        <v>219</v>
+        <v>16.88</v>
       </c>
       <c r="Q24">
-        <v>84.56999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="R24">
-        <v>3356693.07</v>
+        <v>258750.19</v>
       </c>
     </row>
     <row r="25">
@@ -2212,32 +2212,32 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EL53</t>
+          <t>SI04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Dytiki Makedonia</t>
+          <t>Zahodna Slovenija</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="G25">
-        <v>0.127</v>
+        <v>0.359</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I25">
-        <v>0.011</v>
+        <v>0.232</v>
       </c>
       <c r="J25">
-        <v>0.8070000000000001</v>
+        <v>0.493</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -2251,23 +2251,23 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>829</v>
       </c>
       <c r="O25">
-        <v>3106</v>
+        <v>21190</v>
       </c>
       <c r="P25">
-        <v>0.8</v>
+        <v>10.71</v>
       </c>
       <c r="Q25">
-        <v>10.99</v>
+        <v>5.6</v>
       </c>
       <c r="R25">
-        <v>53485.11</v>
+        <v>171161.13</v>
       </c>
     </row>
     <row r="26">
@@ -2288,32 +2288,32 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>BE32</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Prov. Hainaut</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="G26">
-        <v>0.126</v>
+        <v>0.357</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I26">
-        <v>0.01</v>
+        <v>0.22</v>
       </c>
       <c r="J26">
-        <v>0.866</v>
+        <v>0.517</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -2327,23 +2327,23 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N26">
         <v>0</v>
       </c>
       <c r="O26">
-        <v>6794</v>
+        <v>8309</v>
       </c>
       <c r="P26">
-        <v>16.88</v>
+        <v>11.74</v>
       </c>
       <c r="Q26">
-        <v>6.52</v>
+        <v>5.34</v>
       </c>
       <c r="R26">
-        <v>258750.19</v>
+        <v>145307.63</v>
       </c>
     </row>
     <row r="27">
@@ -2378,7 +2378,7 @@
         </is>
       </c>
       <c r="G27">
-        <v>0.036</v>
+        <v>0.079</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         </is>
       </c>
       <c r="I27">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="J27">
         <v>0.08400000000000001</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="G28">
-        <v>0.038</v>
+        <v>0.083</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="I28">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="J28">
         <v>0.091</v>
@@ -2516,21 +2516,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DE12</t>
+          <t>CY00</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Karlsruhe</t>
+          <t>Kýpros</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="G29">
-        <v>0.051</v>
+        <v>0.099</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2538,10 +2538,10 @@
         </is>
       </c>
       <c r="I29">
-        <v>0.01</v>
+        <v>0.023</v>
       </c>
       <c r="J29">
-        <v>0.155</v>
+        <v>0.624</v>
       </c>
       <c r="K29" t="inlineStr">
         <is>
@@ -2555,23 +2555,23 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N29">
         <v>0</v>
       </c>
       <c r="O29">
-        <v>7140</v>
+        <v>126</v>
       </c>
       <c r="P29">
-        <v>27.55</v>
+        <v>1.5</v>
       </c>
       <c r="Q29">
-        <v>13.95</v>
+        <v>3.4</v>
       </c>
       <c r="R29">
-        <v>200600.57</v>
+        <v>13236.96</v>
       </c>
     </row>
     <row r="30">
@@ -2592,21 +2592,21 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G30">
-        <v>0.053</v>
+        <v>0.121</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="I30">
-        <v>0.01</v>
+        <v>0.091</v>
       </c>
       <c r="J30">
-        <v>0.171</v>
+        <v>0.212</v>
       </c>
       <c r="K30" t="inlineStr">
         <is>
@@ -2638,16 +2638,16 @@
         <v>0</v>
       </c>
       <c r="O30">
-        <v>6963</v>
+        <v>5451</v>
       </c>
       <c r="P30">
-        <v>26.87</v>
+        <v>15.91</v>
       </c>
       <c r="Q30">
-        <v>13.61</v>
+        <v>2.13</v>
       </c>
       <c r="R30">
-        <v>195628.64</v>
+        <v>264704.17</v>
       </c>
     </row>
     <row r="31">
@@ -2668,21 +2668,21 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G31">
-        <v>0.057</v>
+        <v>0.123</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -2690,14 +2690,14 @@
         </is>
       </c>
       <c r="I31">
-        <v>0.01</v>
+        <v>0.126</v>
       </c>
       <c r="J31">
-        <v>0.195</v>
+        <v>0.155</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>0</v>
       </c>
       <c r="O31">
-        <v>3900</v>
+        <v>7140</v>
       </c>
       <c r="P31">
-        <v>1.72</v>
+        <v>27.55</v>
       </c>
       <c r="Q31">
-        <v>1.65</v>
+        <v>13.95</v>
       </c>
       <c r="R31">
-        <v>102071.15</v>
+        <v>200600.57</v>
       </c>
     </row>
     <row r="32">
@@ -2744,32 +2744,32 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>BE34</t>
+          <t>HU21</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Prov. Luxembourg (BE)</t>
+          <t>Közép-Dunántúl</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>HU</t>
         </is>
       </c>
       <c r="G32">
-        <v>0.161</v>
+        <v>0.545</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I32">
-        <v>0.042</v>
+        <v>0.411</v>
       </c>
       <c r="J32">
-        <v>0.337</v>
+        <v>0.597</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -2787,19 +2787,19 @@
         </is>
       </c>
       <c r="N32">
-        <v>112095</v>
+        <v>295376</v>
       </c>
       <c r="O32">
-        <v>6875</v>
+        <v>13765</v>
       </c>
       <c r="P32">
-        <v>38.3</v>
+        <v>64.03</v>
       </c>
       <c r="Q32">
-        <v>18.54</v>
+        <v>32.02</v>
       </c>
       <c r="R32">
-        <v>327698.66</v>
+        <v>353560.97</v>
       </c>
     </row>
     <row r="33">
@@ -2820,32 +2820,32 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>SE32</t>
+          <t>CZ04</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Mellersta Norrland</t>
+          <t>Severozápad</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G33">
-        <v>0.16</v>
+        <v>0.524</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I33">
-        <v>0.037</v>
+        <v>0.38</v>
       </c>
       <c r="J33">
-        <v>0.38</v>
+        <v>0.601</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -2859,23 +2859,23 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N33">
-        <v>179232</v>
+        <v>280066</v>
       </c>
       <c r="O33">
-        <v>33515</v>
+        <v>8573</v>
       </c>
       <c r="P33">
-        <v>123.85</v>
+        <v>45.06</v>
       </c>
       <c r="Q33">
-        <v>12.77</v>
+        <v>81.34</v>
       </c>
       <c r="R33">
-        <v>1443154.7</v>
+        <v>425416.92</v>
       </c>
     </row>
     <row r="34">
@@ -2910,15 +2910,15 @@
         </is>
       </c>
       <c r="G34">
-        <v>0.14</v>
+        <v>0.512</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I34">
-        <v>0.016</v>
+        <v>0.326</v>
       </c>
       <c r="J34">
         <v>0.67</v>
@@ -2972,12 +2972,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ITH2</t>
+          <t>ITF1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Provincia Autonoma di Trento</t>
+          <t>Abruzzo</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2986,18 +2986,18 @@
         </is>
       </c>
       <c r="G35">
-        <v>0.137</v>
+        <v>0.483</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I35">
-        <v>0.027</v>
+        <v>0.335</v>
       </c>
       <c r="J35">
-        <v>0.378</v>
+        <v>0.586</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -3011,23 +3011,23 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N35">
-        <v>217643</v>
+        <v>117043</v>
       </c>
       <c r="O35">
-        <v>19593</v>
+        <v>19354</v>
       </c>
       <c r="P35">
-        <v>137.29</v>
+        <v>135.62</v>
       </c>
       <c r="Q35">
-        <v>54.63</v>
+        <v>53.96</v>
       </c>
       <c r="R35">
-        <v>809829.72</v>
+        <v>799941.33</v>
       </c>
     </row>
     <row r="36">
@@ -3048,32 +3048,32 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CZ04</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Severozápad</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CZ</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G36">
-        <v>0.136</v>
+        <v>0.477</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I36">
-        <v>0.017</v>
+        <v>0.239</v>
       </c>
       <c r="J36">
-        <v>0.601</v>
+        <v>0.803</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -3087,23 +3087,23 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N36">
-        <v>280066</v>
+        <v>71852</v>
       </c>
       <c r="O36">
-        <v>8573</v>
+        <v>46821</v>
       </c>
       <c r="P36">
-        <v>45.06</v>
+        <v>328.08</v>
       </c>
       <c r="Q36">
-        <v>81.34</v>
+        <v>130.54</v>
       </c>
       <c r="R36">
-        <v>425416.92</v>
+        <v>1935215.28</v>
       </c>
     </row>
     <row r="37">
@@ -3146,14 +3146,14 @@
         </is>
       </c>
       <c r="I37">
-        <v>0.011</v>
+        <v>0.205</v>
       </c>
       <c r="J37">
         <v>0.01</v>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3214,7 +3214,7 @@
         </is>
       </c>
       <c r="G38">
-        <v>0.014</v>
+        <v>0.021</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3222,14 +3222,14 @@
         </is>
       </c>
       <c r="I38">
-        <v>0.01</v>
+        <v>0.18</v>
       </c>
       <c r="J38">
         <v>0.017</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3290,7 +3290,7 @@
         </is>
       </c>
       <c r="G39">
-        <v>0.04</v>
+        <v>0.116</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3298,14 +3298,14 @@
         </is>
       </c>
       <c r="I39">
-        <v>0.011</v>
+        <v>0.204</v>
       </c>
       <c r="J39">
         <v>0.08799999999999999</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3352,21 +3352,21 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DE12</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Karlsruhe</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G40">
-        <v>0.043</v>
+        <v>0.131</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3374,10 +3374,10 @@
         </is>
       </c>
       <c r="I40">
-        <v>0.014</v>
+        <v>0.164</v>
       </c>
       <c r="J40">
-        <v>0.081</v>
+        <v>0.131</v>
       </c>
       <c r="K40" t="inlineStr">
         <is>
@@ -3391,23 +3391,23 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N40">
-        <v>471622</v>
+        <v>5173</v>
       </c>
       <c r="O40">
-        <v>26427</v>
+        <v>3246</v>
       </c>
       <c r="P40">
-        <v>264.47</v>
+        <v>12.02</v>
       </c>
       <c r="Q40">
-        <v>277.01</v>
+        <v>3.82</v>
       </c>
       <c r="R40">
-        <v>1350468.02</v>
+        <v>203126.32</v>
       </c>
     </row>
     <row r="41">
@@ -3428,21 +3428,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>CZ01</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Praha</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="G41">
-        <v>0.043</v>
+        <v>0.131</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3450,40 +3450,40 @@
         </is>
       </c>
       <c r="I41">
-        <v>0.012</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="J41">
-        <v>0.097</v>
+        <v>0.248</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Vulnerability-driven</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N41">
-        <v>123605</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>12625</v>
+        <v>14511</v>
       </c>
       <c r="P41">
-        <v>126.34</v>
+        <v>76.28</v>
       </c>
       <c r="Q41">
-        <v>132.33</v>
+        <v>137.68</v>
       </c>
       <c r="R41">
-        <v>645130.8199999999</v>
+        <v>720099.88</v>
       </c>
     </row>
     <row r="42">
@@ -3504,17 +3504,17 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NL34</t>
+          <t>EL65</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Zeeland</t>
+          <t>Peloponnisos</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>NL</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G42">
@@ -3529,7 +3529,7 @@
         <v>0.99</v>
       </c>
       <c r="J42">
-        <v>0.518</v>
+        <v>0.765</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -3543,23 +3543,23 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N42">
-        <v>7484706</v>
+        <v>2047197</v>
       </c>
       <c r="O42">
-        <v>767408</v>
+        <v>2995</v>
       </c>
       <c r="P42">
-        <v>2893.03</v>
+        <v>40.63</v>
       </c>
       <c r="Q42">
-        <v>388.29</v>
+        <v>1.03</v>
       </c>
       <c r="R42">
-        <v>16174264.14</v>
+        <v>332084.95</v>
       </c>
     </row>
     <row r="43">
@@ -3580,12 +3580,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ITG2</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sardegna</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3594,18 +3594,18 @@
         </is>
       </c>
       <c r="G43">
-        <v>0.776</v>
+        <v>0.894</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I43">
-        <v>0.452</v>
+        <v>0.702</v>
       </c>
       <c r="J43">
-        <v>0.699</v>
+        <v>0.888</v>
       </c>
       <c r="K43" t="inlineStr">
         <is>
@@ -3623,19 +3623,19 @@
         </is>
       </c>
       <c r="N43">
-        <v>5677884</v>
+        <v>5886952</v>
       </c>
       <c r="O43">
-        <v>175700</v>
+        <v>428034</v>
       </c>
       <c r="P43">
-        <v>548.22</v>
+        <v>1335.55</v>
       </c>
       <c r="Q43">
-        <v>66.22</v>
+        <v>161.33</v>
       </c>
       <c r="R43">
-        <v>4154925.1</v>
+        <v>10122087.62</v>
       </c>
     </row>
     <row r="44">
@@ -3656,32 +3656,32 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>BG34</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Peloponnisos</t>
+          <t>Yugoiztochen</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G44">
-        <v>0.719</v>
+        <v>0.881</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I44">
-        <v>0.355</v>
+        <v>0.713</v>
       </c>
       <c r="J44">
-        <v>0.765</v>
+        <v>0.85</v>
       </c>
       <c r="K44" t="inlineStr">
         <is>
@@ -3699,19 +3699,19 @@
         </is>
       </c>
       <c r="N44">
-        <v>2047197</v>
+        <v>1630381</v>
       </c>
       <c r="O44">
-        <v>2995</v>
+        <v>23676</v>
       </c>
       <c r="P44">
-        <v>40.63</v>
+        <v>341.15</v>
       </c>
       <c r="Q44">
-        <v>1.03</v>
+        <v>50.42</v>
       </c>
       <c r="R44">
-        <v>332084.95</v>
+        <v>1151475.95</v>
       </c>
     </row>
     <row r="45">
@@ -3732,32 +3732,32 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G45">
-        <v>0.541</v>
+        <v>0.877</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I45">
-        <v>0.174</v>
+        <v>0.607</v>
       </c>
       <c r="J45">
-        <v>0.888</v>
+        <v>0.989</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -3771,23 +3771,23 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N45">
-        <v>5886952</v>
+        <v>835562</v>
       </c>
       <c r="O45">
-        <v>428034</v>
+        <v>34776</v>
       </c>
       <c r="P45">
-        <v>1335.55</v>
+        <v>669.79</v>
       </c>
       <c r="Q45">
-        <v>161.33</v>
+        <v>69.31</v>
       </c>
       <c r="R45">
-        <v>10122087.62</v>
+        <v>1468690.83</v>
       </c>
     </row>
     <row r="46">
@@ -3808,32 +3808,32 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>BE21</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Prov. Antwerpen</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G46">
-        <v>0.523</v>
+        <v>0.847</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I46">
-        <v>0.306</v>
+        <v>0.6820000000000001</v>
       </c>
       <c r="J46">
-        <v>0.471</v>
+        <v>0.824</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -3847,23 +3847,23 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N46">
-        <v>11781814</v>
+        <v>662920</v>
       </c>
       <c r="O46">
-        <v>1095262</v>
+        <v>59317</v>
       </c>
       <c r="P46">
-        <v>6318.37</v>
+        <v>185.08</v>
       </c>
       <c r="Q46">
-        <v>875.6799999999999</v>
+        <v>22.36</v>
       </c>
       <c r="R46">
-        <v>27504760.9</v>
+        <v>1402710.45</v>
       </c>
     </row>
     <row r="47">
@@ -3898,22 +3898,22 @@
         </is>
       </c>
       <c r="G47">
-        <v>0.049</v>
+        <v>0.211</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I47">
-        <v>0.012</v>
+        <v>0.383</v>
       </c>
       <c r="J47">
         <v>0.12</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>DE14</t>
+          <t>DE21</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tübingen</t>
+          <t>Oberbayern</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3974,27 +3974,27 @@
         </is>
       </c>
       <c r="G48">
-        <v>0.067</v>
+        <v>0.232</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I48">
-        <v>0.011</v>
+        <v>0.476</v>
       </c>
       <c r="J48">
-        <v>0.238</v>
+        <v>0.113</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -4003,19 +4003,19 @@
         </is>
       </c>
       <c r="N48">
-        <v>0</v>
+        <v>2567747</v>
       </c>
       <c r="O48">
-        <v>133351</v>
+        <v>1636666</v>
       </c>
       <c r="P48">
-        <v>467.22</v>
+        <v>5734.39</v>
       </c>
       <c r="Q48">
-        <v>154.6</v>
+        <v>1897.49</v>
       </c>
       <c r="R48">
-        <v>2094468.62</v>
+        <v>25706163.4</v>
       </c>
     </row>
     <row r="49">
@@ -4036,32 +4036,32 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DE91</t>
+          <t>MT00</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Braunschweig</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="G49">
-        <v>0.07000000000000001</v>
+        <v>0.283</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I49">
-        <v>0.012</v>
+        <v>0.116</v>
       </c>
       <c r="J49">
-        <v>0.228</v>
+        <v>0.652</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -4079,19 +4079,19 @@
         </is>
       </c>
       <c r="N49">
-        <v>585</v>
+        <v>0</v>
       </c>
       <c r="O49">
-        <v>176182</v>
+        <v>480</v>
       </c>
       <c r="P49">
-        <v>617.29</v>
+        <v>1.64</v>
       </c>
       <c r="Q49">
-        <v>204.26</v>
+        <v>25.48</v>
       </c>
       <c r="R49">
-        <v>2767186.65</v>
+        <v>14464.99</v>
       </c>
     </row>
     <row r="50">
@@ -4112,36 +4112,36 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Midi-Pyrénées</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G50">
-        <v>0.076</v>
+        <v>0.284</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I50">
-        <v>0.013</v>
+        <v>0.34</v>
       </c>
       <c r="J50">
-        <v>0.258</v>
+        <v>0.224</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4155,19 +4155,19 @@
         </is>
       </c>
       <c r="N50">
-        <v>40160</v>
+        <v>45956</v>
       </c>
       <c r="O50">
-        <v>116404</v>
+        <v>118812</v>
       </c>
       <c r="P50">
-        <v>729.64</v>
+        <v>508.6</v>
       </c>
       <c r="Q50">
-        <v>32.71</v>
+        <v>79.69</v>
       </c>
       <c r="R50">
-        <v>3615655.6</v>
+        <v>4023747.34</v>
       </c>
     </row>
     <row r="51">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>DE24</t>
+          <t>DE91</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Oberfranken</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -4202,22 +4202,22 @@
         </is>
       </c>
       <c r="G51">
-        <v>0.076</v>
+        <v>0.308</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I51">
-        <v>0.011</v>
+        <v>0.384</v>
       </c>
       <c r="J51">
-        <v>0.294</v>
+        <v>0.228</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4231,19 +4231,19 @@
         </is>
       </c>
       <c r="N51">
-        <v>0</v>
+        <v>585</v>
       </c>
       <c r="O51">
-        <v>80234</v>
+        <v>176182</v>
       </c>
       <c r="P51">
-        <v>281.12</v>
+        <v>617.29</v>
       </c>
       <c r="Q51">
-        <v>93.02</v>
+        <v>204.26</v>
       </c>
       <c r="R51">
-        <v>1260190.55</v>
+        <v>2767186.65</v>
       </c>
     </row>
     <row r="52">
@@ -4264,32 +4264,32 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>IE05</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Southern</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G52">
-        <v>0.177</v>
+        <v>0.569</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I52">
-        <v>0.049</v>
+        <v>0.322</v>
       </c>
       <c r="J52">
-        <v>0.347</v>
+        <v>0.828</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -4303,23 +4303,23 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N52">
-        <v>85614</v>
+        <v>9938</v>
       </c>
       <c r="O52">
-        <v>1449770</v>
+        <v>81507</v>
       </c>
       <c r="P52">
-        <v>129.9</v>
+        <v>29.3</v>
       </c>
       <c r="Q52">
-        <v>33.85</v>
+        <v>15.95</v>
       </c>
       <c r="R52">
-        <v>11019168.12</v>
+        <v>937314.9300000001</v>
       </c>
     </row>
     <row r="53">
@@ -4340,32 +4340,32 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>IE04</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Northern and Western</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G53">
-        <v>0.167</v>
+        <v>0.541</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I53">
-        <v>0.042</v>
+        <v>0.347</v>
       </c>
       <c r="J53">
-        <v>0.358</v>
+        <v>0.697</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -4379,23 +4379,23 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N53">
-        <v>9343</v>
+        <v>49033</v>
       </c>
       <c r="O53">
-        <v>648920</v>
+        <v>104872</v>
       </c>
       <c r="P53">
-        <v>58.15</v>
+        <v>37.7</v>
       </c>
       <c r="Q53">
-        <v>15.15</v>
+        <v>20.52</v>
       </c>
       <c r="R53">
-        <v>4932204.25</v>
+        <v>1206001.59</v>
       </c>
     </row>
     <row r="54">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BE31</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Prov. Brabant Wallon</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G54">
-        <v>0.167</v>
+        <v>0.54</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I54">
-        <v>0.036</v>
+        <v>0.311</v>
       </c>
       <c r="J54">
-        <v>0.419</v>
+        <v>0.777</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -4455,23 +4455,23 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N54">
-        <v>42339</v>
+        <v>0</v>
       </c>
       <c r="O54">
-        <v>183751</v>
+        <v>177017</v>
       </c>
       <c r="P54">
-        <v>81.45</v>
+        <v>63.63</v>
       </c>
       <c r="Q54">
-        <v>16.2</v>
+        <v>34.64</v>
       </c>
       <c r="R54">
-        <v>3218848.98</v>
+        <v>2035665.38</v>
       </c>
     </row>
     <row r="55">
@@ -4492,32 +4492,32 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>IE06</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Eastern and Midland</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G55">
-        <v>0.147</v>
+        <v>0.535</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I55">
-        <v>0.042</v>
+        <v>0.311</v>
       </c>
       <c r="J55">
-        <v>0.28</v>
+        <v>0.764</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -4531,23 +4531,23 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N55">
-        <v>63513</v>
+        <v>0</v>
       </c>
       <c r="O55">
-        <v>1408724</v>
+        <v>15979</v>
       </c>
       <c r="P55">
-        <v>126.23</v>
+        <v>5.74</v>
       </c>
       <c r="Q55">
-        <v>32.89</v>
+        <v>3.13</v>
       </c>
       <c r="R55">
-        <v>10707192.78</v>
+        <v>183756.96</v>
       </c>
     </row>
     <row r="56">
@@ -4568,32 +4568,32 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>HU32</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Észak-Alföld</t>
+          <t>Severozapaden</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G56">
-        <v>0.139</v>
+        <v>0.518</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I56">
-        <v>0.014</v>
+        <v>0.251</v>
       </c>
       <c r="J56">
-        <v>0.757</v>
+        <v>0.891</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -4611,19 +4611,19 @@
         </is>
       </c>
       <c r="N56">
-        <v>36185</v>
+        <v>0</v>
       </c>
       <c r="O56">
-        <v>130160</v>
+        <v>31918</v>
       </c>
       <c r="P56">
-        <v>101.51</v>
+        <v>17.79</v>
       </c>
       <c r="Q56">
-        <v>28.13</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="R56">
-        <v>1496348.22</v>
+        <v>291123.8</v>
       </c>
     </row>
     <row r="57">
@@ -4658,7 +4658,7 @@
         </is>
       </c>
       <c r="G57">
-        <v>0.033</v>
+        <v>0.11</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4666,14 +4666,14 @@
         </is>
       </c>
       <c r="I57">
-        <v>0.011</v>
+        <v>0.265</v>
       </c>
       <c r="J57">
         <v>0.063</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4734,7 +4734,7 @@
         </is>
       </c>
       <c r="G58">
-        <v>0.034</v>
+        <v>0.118</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4742,14 +4742,14 @@
         </is>
       </c>
       <c r="I58">
-        <v>0.011</v>
+        <v>0.265</v>
       </c>
       <c r="J58">
         <v>0.07000000000000001</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
@@ -4810,7 +4810,7 @@
         </is>
       </c>
       <c r="G59">
-        <v>0.044</v>
+        <v>0.157</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4818,14 +4818,14 @@
         </is>
       </c>
       <c r="I59">
-        <v>0.012</v>
+        <v>0.298</v>
       </c>
       <c r="J59">
         <v>0.096</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="G60">
-        <v>0.052</v>
+        <v>0.18</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4894,14 +4894,14 @@
         </is>
       </c>
       <c r="I60">
-        <v>0.012</v>
+        <v>0.265</v>
       </c>
       <c r="J60">
         <v>0.134</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -4962,7 +4962,7 @@
         </is>
       </c>
       <c r="G61">
-        <v>0.058</v>
+        <v>0.193</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4970,14 +4970,14 @@
         </is>
       </c>
       <c r="I61">
-        <v>0.013</v>
+        <v>0.265</v>
       </c>
       <c r="J61">
         <v>0.149</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sterea Elláda</t>
+          <t>Dytiki Elláda</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5038,22 +5038,22 @@
         </is>
       </c>
       <c r="G62">
-        <v>0.636</v>
+        <v>0.891</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I62">
-        <v>0.278</v>
+        <v>0.744</v>
       </c>
       <c r="J62">
-        <v>0.764</v>
+        <v>0.832</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5067,19 +5067,19 @@
         </is>
       </c>
       <c r="N62">
-        <v>2111231</v>
+        <v>745326</v>
       </c>
       <c r="O62">
-        <v>14420</v>
+        <v>6176</v>
       </c>
       <c r="P62">
-        <v>320.34</v>
+        <v>137.2</v>
       </c>
       <c r="Q62">
-        <v>24.07</v>
+        <v>10.31</v>
       </c>
       <c r="R62">
-        <v>115430.42</v>
+        <v>49438.11</v>
       </c>
     </row>
     <row r="63">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>EL63</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Dytiki Elláda</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5114,22 +5114,22 @@
         </is>
       </c>
       <c r="G63">
-        <v>0.5</v>
+        <v>0.864</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I63">
-        <v>0.158</v>
+        <v>0.764</v>
       </c>
       <c r="J63">
-        <v>0.832</v>
+        <v>0.764</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5143,19 +5143,19 @@
         </is>
       </c>
       <c r="N63">
-        <v>745326</v>
+        <v>2111231</v>
       </c>
       <c r="O63">
-        <v>6176</v>
+        <v>14420</v>
       </c>
       <c r="P63">
-        <v>137.2</v>
+        <v>320.34</v>
       </c>
       <c r="Q63">
-        <v>10.31</v>
+        <v>24.07</v>
       </c>
       <c r="R63">
-        <v>49438.11</v>
+        <v>115430.42</v>
       </c>
     </row>
     <row r="64">
@@ -5176,32 +5176,32 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ITF2</t>
+          <t>BG31</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Severozapaden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BG</t>
         </is>
       </c>
       <c r="G64">
-        <v>0.494</v>
+        <v>0.863</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I64">
-        <v>0.172</v>
+        <v>0.612</v>
       </c>
       <c r="J64">
-        <v>0.751</v>
+        <v>0.953</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -5215,23 +5215,23 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N64">
-        <v>746142</v>
+        <v>858645</v>
       </c>
       <c r="O64">
-        <v>14072</v>
+        <v>29796</v>
       </c>
       <c r="P64">
-        <v>113.9</v>
+        <v>282.64</v>
       </c>
       <c r="Q64">
-        <v>12.23</v>
+        <v>38.45</v>
       </c>
       <c r="R64">
-        <v>147454.31</v>
+        <v>274900.06</v>
       </c>
     </row>
     <row r="65">
@@ -5252,32 +5252,32 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PL72</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Świętokrzyskie</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G65">
-        <v>0.473</v>
+        <v>0.841</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I65">
-        <v>0.163</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="J65">
-        <v>0.722</v>
+        <v>0.98</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -5295,19 +5295,19 @@
         </is>
       </c>
       <c r="N65">
-        <v>4132364</v>
+        <v>939289</v>
       </c>
       <c r="O65">
-        <v>188035</v>
+        <v>14114</v>
       </c>
       <c r="P65">
-        <v>1349.77</v>
+        <v>701.59</v>
       </c>
       <c r="Q65">
-        <v>291.48</v>
+        <v>40.39</v>
       </c>
       <c r="R65">
-        <v>1829450.55</v>
+        <v>360575.55</v>
       </c>
     </row>
     <row r="66">
@@ -5328,32 +5328,32 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>BE35</t>
+          <t>RO31</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Prov. Namur</t>
+          <t>Sud-Muntenia</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G66">
-        <v>0.461</v>
+        <v>0.825</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I66">
-        <v>0.217</v>
+        <v>0.582</v>
       </c>
       <c r="J66">
-        <v>0.517</v>
+        <v>0.918</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -5367,23 +5367,23 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N66">
-        <v>781112</v>
+        <v>1960650</v>
       </c>
       <c r="O66">
-        <v>31562</v>
+        <v>24963</v>
       </c>
       <c r="P66">
-        <v>353.9</v>
+        <v>1240.89</v>
       </c>
       <c r="Q66">
-        <v>16.37</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="R66">
-        <v>343951.23</v>
+        <v>637739.45</v>
       </c>
     </row>
     <row r="67">
@@ -5418,22 +5418,22 @@
         </is>
       </c>
       <c r="G67">
-        <v>0.047</v>
+        <v>0.218</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I67">
-        <v>0.012</v>
+        <v>0.429</v>
       </c>
       <c r="J67">
         <v>0.113</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5494,22 +5494,22 @@
         </is>
       </c>
       <c r="G68">
-        <v>0.051</v>
+        <v>0.226</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I68">
-        <v>0.015</v>
+        <v>0.482</v>
       </c>
       <c r="J68">
         <v>0.107</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5556,41 +5556,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>DE12</t>
+          <t>DK01</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Karlsruhe</t>
+          <t>Hovedstaden</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="G69">
-        <v>0.066</v>
+        <v>0.261</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I69">
-        <v>0.014</v>
+        <v>0.258</v>
       </c>
       <c r="J69">
-        <v>0.178</v>
+        <v>0.255</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>ETS</t>
+          <t>CBAM</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5599,19 +5599,19 @@
         </is>
       </c>
       <c r="N69">
-        <v>454253</v>
+        <v>0</v>
       </c>
       <c r="O69">
-        <v>67320</v>
+        <v>13056</v>
       </c>
       <c r="P69">
-        <v>835</v>
+        <v>181.55</v>
       </c>
       <c r="Q69">
-        <v>111.84</v>
+        <v>7.31</v>
       </c>
       <c r="R69">
-        <v>721931.23</v>
+        <v>151664.14</v>
       </c>
     </row>
     <row r="70">
@@ -5632,36 +5632,36 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>DE60</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Hamburg</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G70">
-        <v>0.067</v>
+        <v>0.275</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I70">
-        <v>0.01</v>
+        <v>0.244</v>
       </c>
       <c r="J70">
-        <v>0.255</v>
+        <v>0.295</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -5678,16 +5678,16 @@
         <v>0</v>
       </c>
       <c r="O70">
-        <v>13056</v>
+        <v>7422</v>
       </c>
       <c r="P70">
-        <v>181.55</v>
+        <v>92.06</v>
       </c>
       <c r="Q70">
-        <v>7.31</v>
+        <v>12.33</v>
       </c>
       <c r="R70">
-        <v>151664.14</v>
+        <v>79589.62</v>
       </c>
     </row>
     <row r="71">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>DE60</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hamburg</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5722,27 +5722,27 @@
         </is>
       </c>
       <c r="G71">
-        <v>0.07199999999999999</v>
+        <v>0.289</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I71">
-        <v>0.01</v>
+        <v>0.44</v>
       </c>
       <c r="J71">
-        <v>0.295</v>
+        <v>0.178</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CBAM</t>
+          <t>ETS</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5751,19 +5751,19 @@
         </is>
       </c>
       <c r="N71">
-        <v>0</v>
+        <v>454253</v>
       </c>
       <c r="O71">
-        <v>7422</v>
+        <v>67320</v>
       </c>
       <c r="P71">
-        <v>92.06</v>
+        <v>835</v>
       </c>
       <c r="Q71">
-        <v>12.33</v>
+        <v>111.84</v>
       </c>
       <c r="R71">
-        <v>79589.62</v>
+        <v>721931.23</v>
       </c>
     </row>
     <row r="72">
@@ -5784,32 +5784,32 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>SE33</t>
+          <t>EL64</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Övre Norrland</t>
+          <t>Sterea Elláda</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G72">
-        <v>0.544</v>
+        <v>0.856</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I72">
-        <v>0.349</v>
+        <v>0.726</v>
       </c>
       <c r="J72">
-        <v>0.446</v>
+        <v>0.789</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -5827,19 +5827,19 @@
         </is>
       </c>
       <c r="N72">
-        <v>4030911</v>
+        <v>1163945</v>
       </c>
       <c r="O72">
-        <v>190114</v>
+        <v>119413</v>
       </c>
       <c r="P72">
-        <v>672.28</v>
+        <v>95.86</v>
       </c>
       <c r="Q72">
-        <v>0</v>
+        <v>138.1</v>
       </c>
       <c r="R72">
-        <v>2232388.82</v>
+        <v>560640.63</v>
       </c>
     </row>
     <row r="73">
@@ -5860,32 +5860,32 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>ES12</t>
+          <t>RO22</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Principado de Asturias</t>
+          <t>Sud-Est</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>RO</t>
         </is>
       </c>
       <c r="G73">
-        <v>0.517</v>
+        <v>0.824</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I73">
-        <v>0.294</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="J73">
-        <v>0.479</v>
+        <v>0.951</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -5903,19 +5903,19 @@
         </is>
       </c>
       <c r="N73">
-        <v>4131636</v>
+        <v>1434780</v>
       </c>
       <c r="O73">
-        <v>608545</v>
+        <v>105860</v>
       </c>
       <c r="P73">
-        <v>1081.7</v>
+        <v>470.04</v>
       </c>
       <c r="Q73">
-        <v>248.89</v>
+        <v>220.36</v>
       </c>
       <c r="R73">
-        <v>7061995.92</v>
+        <v>1880666.77</v>
       </c>
     </row>
     <row r="74">
@@ -5936,32 +5936,32 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>SK04</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Sterea Elláda</t>
+          <t>Východné Slovensko</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>EL</t>
+          <t>SK</t>
         </is>
       </c>
       <c r="G74">
-        <v>0.507</v>
+        <v>0.82</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I74">
-        <v>0.172</v>
+        <v>0.637</v>
       </c>
       <c r="J74">
-        <v>0.789</v>
+        <v>0.829</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -5975,23 +5975,23 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N74">
-        <v>1163945</v>
+        <v>5388284</v>
       </c>
       <c r="O74">
-        <v>119413</v>
+        <v>215473</v>
       </c>
       <c r="P74">
-        <v>95.86</v>
+        <v>2258.03</v>
       </c>
       <c r="Q74">
-        <v>138.1</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R74">
-        <v>560640.63</v>
+        <v>4826706.62</v>
       </c>
     </row>
     <row r="75">
@@ -6012,32 +6012,32 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>SK04</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Východné Slovensko</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>SK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G75">
-        <v>0.487</v>
+        <v>0.801</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Very High</t>
         </is>
       </c>
       <c r="I75">
-        <v>0.151</v>
+        <v>0.654</v>
       </c>
       <c r="J75">
-        <v>0.829</v>
+        <v>0.773</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6051,23 +6051,23 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N75">
-        <v>5388284</v>
+        <v>4351958</v>
       </c>
       <c r="O75">
-        <v>215473</v>
+        <v>1267020</v>
       </c>
       <c r="P75">
-        <v>2258.03</v>
+        <v>985.3</v>
       </c>
       <c r="Q75">
-        <v>97.59999999999999</v>
+        <v>393.91</v>
       </c>
       <c r="R75">
-        <v>4826706.62</v>
+        <v>9139782.189999999</v>
       </c>
     </row>
     <row r="76">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>ITC2</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Valle d’Aosta/Vallée d’Aoste</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6102,18 +6102,18 @@
         </is>
       </c>
       <c r="G76">
-        <v>0.41</v>
+        <v>0.767</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I76">
-        <v>0.156</v>
+        <v>0.516</v>
       </c>
       <c r="J76">
-        <v>0.572</v>
+        <v>0.903</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6127,23 +6127,23 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N76">
-        <v>87962</v>
+        <v>16397</v>
       </c>
       <c r="O76">
-        <v>172712</v>
+        <v>147276</v>
       </c>
       <c r="P76">
-        <v>134.31</v>
+        <v>114.53</v>
       </c>
       <c r="Q76">
-        <v>53.69</v>
+        <v>45.79</v>
       </c>
       <c r="R76">
-        <v>1245873.15</v>
+        <v>1062388.17</v>
       </c>
     </row>
     <row r="77">
@@ -6178,22 +6178,22 @@
         </is>
       </c>
       <c r="G77">
-        <v>0.048</v>
+        <v>0.228</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I77">
-        <v>0.011</v>
+        <v>0.412</v>
       </c>
       <c r="J77">
         <v>0.127</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6254,22 +6254,22 @@
         </is>
       </c>
       <c r="G78">
-        <v>0.049</v>
+        <v>0.232</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I78">
-        <v>0.011</v>
+        <v>0.403</v>
       </c>
       <c r="J78">
         <v>0.133</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6316,36 +6316,36 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>DE12</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Karlsruhe</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G79">
-        <v>0.062</v>
+        <v>0.274</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I79">
-        <v>0.012</v>
+        <v>0.315</v>
       </c>
       <c r="J79">
-        <v>0.198</v>
+        <v>0.227</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6359,19 +6359,19 @@
         </is>
       </c>
       <c r="N79">
-        <v>21411</v>
+        <v>0</v>
       </c>
       <c r="O79">
-        <v>173122</v>
+        <v>35098</v>
       </c>
       <c r="P79">
-        <v>757.54</v>
+        <v>306.53</v>
       </c>
       <c r="Q79">
-        <v>164.12</v>
+        <v>19.57</v>
       </c>
       <c r="R79">
-        <v>1988480.52</v>
+        <v>587231.1800000001</v>
       </c>
     </row>
     <row r="80">
@@ -6392,32 +6392,32 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FRJ2</t>
+          <t>LT01</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Midi-Pyrénées</t>
+          <t>Sostinės regionas</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="G80">
-        <v>0.064</v>
+        <v>0.277</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I80">
-        <v>0.011</v>
+        <v>0.173</v>
       </c>
       <c r="J80">
-        <v>0.227</v>
+        <v>0.422</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6431,23 +6431,23 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Institutions</t>
         </is>
       </c>
       <c r="N80">
         <v>0</v>
       </c>
       <c r="O80">
-        <v>35098</v>
+        <v>155</v>
       </c>
       <c r="P80">
-        <v>306.53</v>
+        <v>0.04</v>
       </c>
       <c r="Q80">
-        <v>19.57</v>
+        <v>0.08</v>
       </c>
       <c r="R80">
-        <v>587231.1800000001</v>
+        <v>2164.86</v>
       </c>
     </row>
     <row r="81">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6482,22 +6482,22 @@
         </is>
       </c>
       <c r="G81">
-        <v>0.067</v>
+        <v>0.294</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I81">
-        <v>0.013</v>
+        <v>0.408</v>
       </c>
       <c r="J81">
-        <v>0.213</v>
+        <v>0.198</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6511,19 +6511,19 @@
         </is>
       </c>
       <c r="N81">
-        <v>37878</v>
+        <v>21411</v>
       </c>
       <c r="O81">
-        <v>128381</v>
+        <v>173122</v>
       </c>
       <c r="P81">
-        <v>561.76</v>
+        <v>757.54</v>
       </c>
       <c r="Q81">
-        <v>121.71</v>
+        <v>164.12</v>
       </c>
       <c r="R81">
-        <v>1474591.88</v>
+        <v>1988480.52</v>
       </c>
     </row>
     <row r="82">
@@ -6544,32 +6544,32 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Dytiki Makedonia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G82">
-        <v>0.147</v>
+        <v>0.507</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I82">
-        <v>0.014</v>
+        <v>0.267</v>
       </c>
       <c r="J82">
-        <v>0.858</v>
+        <v>0.803</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
@@ -6590,16 +6590,16 @@
         <v>0</v>
       </c>
       <c r="O82">
-        <v>144473</v>
+        <v>9935</v>
       </c>
       <c r="P82">
-        <v>43.06</v>
+        <v>6.99</v>
       </c>
       <c r="Q82">
-        <v>65.48999999999999</v>
+        <v>3.33</v>
       </c>
       <c r="R82">
-        <v>2280771.98</v>
+        <v>64439.9</v>
       </c>
     </row>
     <row r="83">
@@ -6620,32 +6620,32 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>ITF6</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Calabria</t>
+          <t>Notio Aigaio</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G83">
-        <v>0.146</v>
+        <v>0.498</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I83">
-        <v>0.015</v>
+        <v>0.267</v>
       </c>
       <c r="J83">
-        <v>0.794</v>
+        <v>0.778</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -6659,23 +6659,23 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N83">
         <v>0</v>
       </c>
       <c r="O83">
-        <v>52080</v>
+        <v>10830</v>
       </c>
       <c r="P83">
-        <v>15.52</v>
+        <v>7.62</v>
       </c>
       <c r="Q83">
-        <v>23.61</v>
+        <v>3.63</v>
       </c>
       <c r="R83">
-        <v>822183.05</v>
+        <v>70250.95</v>
       </c>
     </row>
     <row r="84">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>EL64</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Sterea Elláda</t>
+          <t>Dytiki Elláda</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6710,18 +6710,18 @@
         </is>
       </c>
       <c r="G84">
-        <v>0.143</v>
+        <v>0.497</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I84">
-        <v>0.016</v>
+        <v>0.267</v>
       </c>
       <c r="J84">
-        <v>0.708</v>
+        <v>0.776</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -6742,16 +6742,16 @@
         <v>0</v>
       </c>
       <c r="O84">
-        <v>46816</v>
+        <v>20539</v>
       </c>
       <c r="P84">
-        <v>32.93</v>
+        <v>14.45</v>
       </c>
       <c r="Q84">
-        <v>15.67</v>
+        <v>6.87</v>
       </c>
       <c r="R84">
-        <v>303671.29</v>
+        <v>133224.33</v>
       </c>
     </row>
     <row r="85">
@@ -6772,32 +6772,32 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>BG34</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Yugoiztochen</t>
+          <t>Anatoliki Makedonia, Thraki</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G85">
-        <v>0.143</v>
+        <v>0.495</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I85">
-        <v>0.015</v>
+        <v>0.267</v>
       </c>
       <c r="J85">
-        <v>0.771</v>
+        <v>0.77</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -6818,16 +6818,16 @@
         <v>0</v>
       </c>
       <c r="O85">
-        <v>123396</v>
+        <v>22688</v>
       </c>
       <c r="P85">
-        <v>35.44</v>
+        <v>15.96</v>
       </c>
       <c r="Q85">
-        <v>92.62</v>
+        <v>7.59</v>
       </c>
       <c r="R85">
-        <v>1371390</v>
+        <v>147167.77</v>
       </c>
     </row>
     <row r="86">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6862,18 +6862,18 @@
         </is>
       </c>
       <c r="G86">
-        <v>0.143</v>
+        <v>0.492</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I86">
-        <v>0.014</v>
+        <v>0.236</v>
       </c>
       <c r="J86">
-        <v>0.8080000000000001</v>
+        <v>0.858</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -6894,16 +6894,16 @@
         <v>0</v>
       </c>
       <c r="O86">
-        <v>296403</v>
+        <v>144473</v>
       </c>
       <c r="P86">
-        <v>88.34999999999999</v>
+        <v>43.06</v>
       </c>
       <c r="Q86">
-        <v>134.37</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="R86">
-        <v>4679270.88</v>
+        <v>2280771.98</v>
       </c>
     </row>
     <row r="87">
@@ -6938,7 +6938,7 @@
         </is>
       </c>
       <c r="G87">
-        <v>0.034</v>
+        <v>0.077</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         </is>
       </c>
       <c r="I87">
-        <v>0.011</v>
+        <v>0.15</v>
       </c>
       <c r="J87">
         <v>0.068</v>
@@ -7014,7 +7014,7 @@
         </is>
       </c>
       <c r="G88">
-        <v>0.039</v>
+        <v>0.083</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         </is>
       </c>
       <c r="I88">
-        <v>0.013</v>
+        <v>0.15</v>
       </c>
       <c r="J88">
         <v>0.075</v>
@@ -7090,7 +7090,7 @@
         </is>
       </c>
       <c r="G89">
-        <v>0.053</v>
+        <v>0.129</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -7098,14 +7098,14 @@
         </is>
       </c>
       <c r="I89">
-        <v>0.012</v>
+        <v>0.151</v>
       </c>
       <c r="J89">
         <v>0.14</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7166,7 +7166,7 @@
         </is>
       </c>
       <c r="G90">
-        <v>0.054</v>
+        <v>0.138</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -7174,14 +7174,14 @@
         </is>
       </c>
       <c r="I90">
-        <v>0.011</v>
+        <v>0.15</v>
       </c>
       <c r="J90">
         <v>0.155</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
@@ -7242,7 +7242,7 @@
         </is>
       </c>
       <c r="G91">
-        <v>0.058</v>
+        <v>0.153</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
@@ -7250,14 +7250,14 @@
         </is>
       </c>
       <c r="I91">
-        <v>0.011</v>
+        <v>0.15</v>
       </c>
       <c r="J91">
         <v>0.183</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
@@ -7304,32 +7304,32 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>HU31</t>
+          <t>EL53</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Észak-Magyarország</t>
+          <t>Dytiki Makedonia</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G92">
-        <v>0.157</v>
+        <v>0.606</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="I92">
-        <v>0.017</v>
+        <v>0.378</v>
       </c>
       <c r="J92">
-        <v>0.773</v>
+        <v>0.791</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7343,23 +7343,23 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N92">
         <v>0</v>
       </c>
       <c r="O92">
-        <v>260030</v>
+        <v>968</v>
       </c>
       <c r="P92">
-        <v>57.56</v>
+        <v>0.18</v>
       </c>
       <c r="Q92">
-        <v>23.9</v>
+        <v>0.17</v>
       </c>
       <c r="R92">
-        <v>3625407.71</v>
+        <v>5810.03</v>
       </c>
     </row>
     <row r="93">
@@ -7380,32 +7380,32 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>HU23</t>
+          <t>EL42</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dél-Dunántúl</t>
+          <t>Notio Aigaio</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G93">
-        <v>0.152</v>
+        <v>0.594</v>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I93">
-        <v>0.017</v>
+        <v>0.377</v>
       </c>
       <c r="J93">
-        <v>0.745</v>
+        <v>0.765</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7426,16 +7426,16 @@
         <v>0</v>
       </c>
       <c r="O93">
-        <v>153517</v>
+        <v>1450</v>
       </c>
       <c r="P93">
-        <v>33.98</v>
+        <v>0.27</v>
       </c>
       <c r="Q93">
-        <v>14.11</v>
+        <v>0.26</v>
       </c>
       <c r="R93">
-        <v>2140375.24</v>
+        <v>8703.41</v>
       </c>
     </row>
     <row r="94">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>EL65</t>
+          <t>EL63</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Peloponnisos</t>
+          <t>Dytiki Elláda</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7470,18 +7470,18 @@
         </is>
       </c>
       <c r="G94">
-        <v>0.147</v>
+        <v>0.594</v>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I94">
-        <v>0.017</v>
+        <v>0.377</v>
       </c>
       <c r="J94">
-        <v>0.7</v>
+        <v>0.764</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7502,16 +7502,16 @@
         <v>0</v>
       </c>
       <c r="O94">
-        <v>41080</v>
+        <v>8053</v>
       </c>
       <c r="P94">
-        <v>7.64</v>
+        <v>1.5</v>
       </c>
       <c r="Q94">
-        <v>7.36</v>
+        <v>1.44</v>
       </c>
       <c r="R94">
-        <v>246608.06</v>
+        <v>48340.86</v>
       </c>
     </row>
     <row r="95">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>HU12</t>
+          <t>EL51</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Pest</t>
+          <t>Anatoliki Makedonia, Thraki</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G95">
-        <v>0.141</v>
+        <v>0.591</v>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I95">
-        <v>0.018</v>
+        <v>0.377</v>
       </c>
       <c r="J95">
-        <v>0.624</v>
+        <v>0.758</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7571,23 +7571,23 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N95">
         <v>0</v>
       </c>
       <c r="O95">
-        <v>270480</v>
+        <v>11008</v>
       </c>
       <c r="P95">
-        <v>59.87</v>
+        <v>2.05</v>
       </c>
       <c r="Q95">
-        <v>24.86</v>
+        <v>1.97</v>
       </c>
       <c r="R95">
-        <v>3771099.29</v>
+        <v>66080.58</v>
       </c>
     </row>
     <row r="96">
@@ -7608,32 +7608,32 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>ITG1</t>
+          <t>EL54</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Sicilia</t>
+          <t>Ipeiros</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>EL</t>
         </is>
       </c>
       <c r="G96">
-        <v>0.141</v>
+        <v>0.572</v>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I96">
-        <v>0.013</v>
+        <v>0.379</v>
       </c>
       <c r="J96">
-        <v>0.828</v>
+        <v>0.709</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7647,23 +7647,23 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N96">
         <v>0</v>
       </c>
       <c r="O96">
-        <v>122138</v>
+        <v>1281</v>
       </c>
       <c r="P96">
-        <v>37.65</v>
+        <v>0.24</v>
       </c>
       <c r="Q96">
-        <v>30.88</v>
+        <v>0.23</v>
       </c>
       <c r="R96">
-        <v>1640775.09</v>
+        <v>7688.62</v>
       </c>
     </row>
     <row r="97">
@@ -7698,7 +7698,7 @@
         </is>
       </c>
       <c r="G97">
-        <v>0.032</v>
+        <v>0.066</v>
       </c>
       <c r="H97" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="I97">
-        <v>0.011</v>
+        <v>0.136</v>
       </c>
       <c r="J97">
         <v>0.062</v>
@@ -7774,7 +7774,7 @@
         </is>
       </c>
       <c r="G98">
-        <v>0.034</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H98" t="inlineStr">
         <is>
@@ -7782,7 +7782,7 @@
         </is>
       </c>
       <c r="I98">
-        <v>0.011</v>
+        <v>0.136</v>
       </c>
       <c r="J98">
         <v>0.06900000000000001</v>
@@ -7850,7 +7850,7 @@
         </is>
       </c>
       <c r="G99">
-        <v>0.038</v>
+        <v>0.105</v>
       </c>
       <c r="H99" t="inlineStr">
         <is>
@@ -7858,7 +7858,7 @@
         </is>
       </c>
       <c r="I99">
-        <v>0.011</v>
+        <v>0.176</v>
       </c>
       <c r="J99">
         <v>0.089</v>
@@ -7926,7 +7926,7 @@
         </is>
       </c>
       <c r="G100">
-        <v>0.049</v>
+        <v>0.116</v>
       </c>
       <c r="H100" t="inlineStr">
         <is>
@@ -7934,14 +7934,14 @@
         </is>
       </c>
       <c r="I100">
-        <v>0.011</v>
+        <v>0.136</v>
       </c>
       <c r="J100">
         <v>0.134</v>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7988,21 +7988,21 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G101">
-        <v>0.05</v>
+        <v>0.125</v>
       </c>
       <c r="H101" t="inlineStr">
         <is>
@@ -8010,14 +8010,14 @@
         </is>
       </c>
       <c r="I101">
-        <v>0.011</v>
+        <v>0.136</v>
       </c>
       <c r="J101">
-        <v>0.139</v>
+        <v>0.149</v>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -8027,23 +8027,23 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N101">
         <v>0</v>
       </c>
       <c r="O101">
-        <v>30645</v>
+        <v>23767</v>
       </c>
       <c r="P101">
-        <v>6.32</v>
+        <v>17.5</v>
       </c>
       <c r="Q101">
-        <v>3.62</v>
+        <v>19.31</v>
       </c>
       <c r="R101">
-        <v>985589.2</v>
+        <v>998863.6899999999</v>
       </c>
     </row>
     <row r="102">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>ITF5</t>
+          <t>ITG1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Basilicata</t>
+          <t>Sicilia</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8078,18 +8078,18 @@
         </is>
       </c>
       <c r="G102">
-        <v>0.175</v>
+        <v>0.5659999999999999</v>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I102">
-        <v>0.025</v>
+        <v>0.305</v>
       </c>
       <c r="J102">
-        <v>0.676</v>
+        <v>0.865</v>
       </c>
       <c r="K102" t="inlineStr">
         <is>
@@ -8103,23 +8103,23 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N102">
         <v>0</v>
       </c>
       <c r="O102">
-        <v>143902</v>
+        <v>68359</v>
       </c>
       <c r="P102">
-        <v>39.69</v>
+        <v>18.85</v>
       </c>
       <c r="Q102">
-        <v>27.23</v>
+        <v>12.93</v>
       </c>
       <c r="R102">
-        <v>1929245.25</v>
+        <v>916469.9399999999</v>
       </c>
     </row>
     <row r="103">
@@ -8140,12 +8140,12 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>ITF2</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Molise</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8154,18 +8154,18 @@
         </is>
       </c>
       <c r="G103">
-        <v>0.167</v>
+        <v>0.552</v>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I103">
-        <v>0.021</v>
+        <v>0.309</v>
       </c>
       <c r="J103">
-        <v>0.718</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="K103" t="inlineStr">
         <is>
@@ -8179,23 +8179,23 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N103">
-        <v>0</v>
+        <v>20202</v>
       </c>
       <c r="O103">
-        <v>52120</v>
+        <v>444867</v>
       </c>
       <c r="P103">
-        <v>14.37</v>
+        <v>122.7</v>
       </c>
       <c r="Q103">
-        <v>9.859999999999999</v>
+        <v>84.17</v>
       </c>
       <c r="R103">
-        <v>698757.04</v>
+        <v>5964174.91</v>
       </c>
     </row>
     <row r="104">
@@ -8216,12 +8216,12 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITF6</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Calabria</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8230,18 +8230,18 @@
         </is>
       </c>
       <c r="G104">
-        <v>0.154</v>
+        <v>0.543</v>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I104">
-        <v>0.016</v>
+        <v>0.305</v>
       </c>
       <c r="J104">
-        <v>0.8139999999999999</v>
+        <v>0.801</v>
       </c>
       <c r="K104" t="inlineStr">
         <is>
@@ -8259,19 +8259,19 @@
         </is>
       </c>
       <c r="N104">
-        <v>20202</v>
+        <v>0</v>
       </c>
       <c r="O104">
-        <v>444867</v>
+        <v>9236</v>
       </c>
       <c r="P104">
-        <v>122.7</v>
+        <v>2.55</v>
       </c>
       <c r="Q104">
-        <v>84.17</v>
+        <v>1.75</v>
       </c>
       <c r="R104">
-        <v>5964174.91</v>
+        <v>123821.2</v>
       </c>
     </row>
     <row r="105">
@@ -8292,32 +8292,32 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>HU22</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Nyugat-Dunántúl</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>HU</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G105">
-        <v>0.144</v>
+        <v>0.523</v>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I105">
-        <v>0.017</v>
+        <v>0.31</v>
       </c>
       <c r="J105">
-        <v>0.67</v>
+        <v>0.734</v>
       </c>
       <c r="K105" t="inlineStr">
         <is>
@@ -8331,23 +8331,23 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N105">
-        <v>8595</v>
+        <v>13422</v>
       </c>
       <c r="O105">
-        <v>286998</v>
+        <v>224936</v>
       </c>
       <c r="P105">
-        <v>73.09</v>
+        <v>62.04</v>
       </c>
       <c r="Q105">
-        <v>107.16</v>
+        <v>42.56</v>
       </c>
       <c r="R105">
-        <v>7478236.76</v>
+        <v>3015637.45</v>
       </c>
     </row>
     <row r="106">
@@ -8368,32 +8368,32 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>RO31</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sud-Muntenia</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G106">
-        <v>0.142</v>
+        <v>0.512</v>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I106">
-        <v>0.013</v>
+        <v>0.305</v>
       </c>
       <c r="J106">
-        <v>0.854</v>
+        <v>0.718</v>
       </c>
       <c r="K106" t="inlineStr">
         <is>
@@ -8411,19 +8411,19 @@
         </is>
       </c>
       <c r="N106">
-        <v>50567</v>
+        <v>0</v>
       </c>
       <c r="O106">
-        <v>123303</v>
+        <v>52120</v>
       </c>
       <c r="P106">
-        <v>22.11</v>
+        <v>14.37</v>
       </c>
       <c r="Q106">
-        <v>68.05</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="R106">
-        <v>2513284.1</v>
+        <v>698757.04</v>
       </c>
     </row>
     <row r="107">
@@ -8458,7 +8458,7 @@
         </is>
       </c>
       <c r="G107">
-        <v>0.041</v>
+        <v>0.104</v>
       </c>
       <c r="H107" t="inlineStr">
         <is>
@@ -8466,14 +8466,14 @@
         </is>
       </c>
       <c r="I107">
-        <v>0.015</v>
+        <v>0.211</v>
       </c>
       <c r="J107">
         <v>0.073</v>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -8534,7 +8534,7 @@
         </is>
       </c>
       <c r="G108">
-        <v>0.042</v>
+        <v>0.108</v>
       </c>
       <c r="H108" t="inlineStr">
         <is>
@@ -8542,14 +8542,14 @@
         </is>
       </c>
       <c r="I108">
-        <v>0.014</v>
+        <v>0.205</v>
       </c>
       <c r="J108">
         <v>0.08</v>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>Balanced</t>
+          <t>Exposure-driven</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -8596,21 +8596,21 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>DE12</t>
+          <t>LU00</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Karlsruhe</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>LU</t>
         </is>
       </c>
       <c r="G109">
-        <v>0.055</v>
+        <v>0.128</v>
       </c>
       <c r="H109" t="inlineStr">
         <is>
@@ -8618,10 +8618,10 @@
         </is>
       </c>
       <c r="I109">
-        <v>0.013</v>
+        <v>0.057</v>
       </c>
       <c r="J109">
-        <v>0.145</v>
+        <v>0.369</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
@@ -8639,19 +8639,19 @@
         </is>
       </c>
       <c r="N109">
-        <v>45701</v>
+        <v>0</v>
       </c>
       <c r="O109">
-        <v>256023</v>
+        <v>2049</v>
       </c>
       <c r="P109">
-        <v>231.98</v>
+        <v>0.99</v>
       </c>
       <c r="Q109">
-        <v>209.8</v>
+        <v>0.38</v>
       </c>
       <c r="R109">
-        <v>9249367.83</v>
+        <v>100966.09</v>
       </c>
     </row>
     <row r="110">
@@ -8672,21 +8672,21 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>DK01</t>
+          <t>FRJ2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Hovedstaden</t>
+          <t>Midi-Pyrénées</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>DK</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="G110">
-        <v>0.056</v>
+        <v>0.149</v>
       </c>
       <c r="H110" t="inlineStr">
         <is>
@@ -8694,14 +8694,14 @@
         </is>
       </c>
       <c r="I110">
-        <v>0.01</v>
+        <v>0.176</v>
       </c>
       <c r="J110">
-        <v>0.187</v>
+        <v>0.149</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -8711,23 +8711,23 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="N110">
-        <v>0</v>
+        <v>4673</v>
       </c>
       <c r="O110">
-        <v>5033</v>
+        <v>159924</v>
       </c>
       <c r="P110">
-        <v>1.17</v>
+        <v>112.04</v>
       </c>
       <c r="Q110">
-        <v>0.75</v>
+        <v>36.76</v>
       </c>
       <c r="R110">
-        <v>71680.19</v>
+        <v>9779748.880000001</v>
       </c>
     </row>
     <row r="111">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>DEB3</t>
+          <t>DE12</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Rheinhessen-Pfalz</t>
+          <t>Karlsruhe</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8762,7 +8762,7 @@
         </is>
       </c>
       <c r="G111">
-        <v>0.056</v>
+        <v>0.168</v>
       </c>
       <c r="H111" t="inlineStr">
         <is>
@@ -8770,14 +8770,14 @@
         </is>
       </c>
       <c r="I111">
-        <v>0.012</v>
+        <v>0.219</v>
       </c>
       <c r="J111">
-        <v>0.16</v>
+        <v>0.145</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -8791,19 +8791,19 @@
         </is>
       </c>
       <c r="N111">
-        <v>15455</v>
+        <v>45701</v>
       </c>
       <c r="O111">
-        <v>112913</v>
+        <v>256023</v>
       </c>
       <c r="P111">
-        <v>102.31</v>
+        <v>231.98</v>
       </c>
       <c r="Q111">
-        <v>92.53</v>
+        <v>209.8</v>
       </c>
       <c r="R111">
-        <v>4079202</v>
+        <v>9249367.83</v>
       </c>
     </row>
     <row r="112">
@@ -8838,15 +8838,15 @@
         </is>
       </c>
       <c r="G112">
-        <v>0.134</v>
+        <v>0.434</v>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I112">
-        <v>0.012</v>
+        <v>0.195</v>
       </c>
       <c r="J112">
         <v>0.827</v>
@@ -8900,32 +8900,32 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>BG31</t>
+          <t>ITF3</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Severozapaden</t>
+          <t>Campania</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>BG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G113">
-        <v>0.13</v>
+        <v>0.419</v>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I113">
-        <v>0.011</v>
+        <v>0.195</v>
       </c>
       <c r="J113">
-        <v>0.89</v>
+        <v>0.776</v>
       </c>
       <c r="K113" t="inlineStr">
         <is>
@@ -8939,23 +8939,23 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Institutions</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="N113">
         <v>0</v>
       </c>
       <c r="O113">
-        <v>9006</v>
+        <v>112924</v>
       </c>
       <c r="P113">
-        <v>4.94</v>
+        <v>48.51</v>
       </c>
       <c r="Q113">
-        <v>9.67</v>
+        <v>45.62</v>
       </c>
       <c r="R113">
-        <v>154843.1</v>
+        <v>1865207.41</v>
       </c>
     </row>
     <row r="114">
@@ -8990,15 +8990,15 @@
         </is>
       </c>
       <c r="G114">
-        <v>0.127</v>
+        <v>0.415</v>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="I114">
-        <v>0.012</v>
+        <v>0.195</v>
       </c>
       <c r="J114">
         <v>0.763</v>
@@ -9052,12 +9052,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>ITF3</t>
+          <t>ITF4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Campania</t>
+          <t>Puglia</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -9066,18 +9066,18 @@
         </is>
       </c>
       <c r="G115">
-        <v>0.127</v>
+        <v>0.394</v>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I115">
-        <v>0.011</v>
+        <v>0.195</v>
       </c>
       <c r="J115">
-        <v>0.776</v>
+        <v>0.697</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
@@ -9098,16 +9098,16 @@
         <v>0</v>
       </c>
       <c r="O115">
-        <v>112924</v>
+        <v>116778</v>
       </c>
       <c r="P115">
-        <v>48.51</v>
+        <v>50.16</v>
       </c>
       <c r="Q115">
-        <v>45.62</v>
+        <v>47.18</v>
       </c>
       <c r="R115">
-        <v>1865207.41</v>
+        <v>1928854.55</v>
       </c>
     </row>
     <row r="116">
@@ -9128,32 +9128,32 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>RO22</t>
+          <t>ITF2</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sud-Est</t>
+          <t>Molise</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>RO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="G116">
-        <v>0.126</v>
+        <v>0.389</v>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Very Low</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="I116">
-        <v>0.01</v>
+        <v>0.195</v>
       </c>
       <c r="J116">
-        <v>0.85</v>
+        <v>0.68</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
@@ -9174,16 +9174,16 @@
         <v>0</v>
       </c>
       <c r="O116">
-        <v>10497</v>
+        <v>4568</v>
       </c>
       <c r="P116">
-        <v>15.96</v>
+        <v>1.96</v>
       </c>
       <c r="Q116">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="R116">
-        <v>270621.74</v>
+        <v>75453.37</v>
       </c>
     </row>
     <row r="117">
@@ -9218,7 +9218,7 @@
         </is>
       </c>
       <c r="G117">
-        <v>0.031</v>
+        <v>0.05</v>
       </c>
       <c r="H117" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
         </is>
       </c>
       <c r="I117">
-        <v>0.01</v>
+        <v>0.099</v>
       </c>
       <c r="J117">
         <v>0.063</v>
@@ -9294,7 +9294,7 @@
         </is>
       </c>
       <c r="G118">
-        <v>0.033</v>
+        <v>0.054</v>
       </c>
       <c r="H118" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         </is>
       </c>
       <c r="I118">
-        <v>0.01</v>
+        <v>0.099</v>
       </c>
       <c r="J118">
         <v>0.06900000000000001</v>
@@ -9370,7 +9370,7 @@
         </is>
       </c>
       <c r="G119">
-        <v>0.037</v>
+        <v>0.081</v>
       </c>
       <c r="H119" t="inlineStr">
         <is>
@@ -9378,7 +9378,7 @@
         </is>
       </c>
       <c r="I119">
-        <v>0.01</v>
+        <v>0.128</v>
       </c>
       <c r="J119">
         <v>0.08599999999999999</v>
@@ -9446,7 +9446,7 @@
         </is>
       </c>
       <c r="G120">
-        <v>0.047</v>
+        <v>0.093</v>
       </c>
       <c r="H120" t="inlineStr">
         <is>
@@ -9454,14 +9454,14 @@
         </is>
       </c>
       <c r="I120">
-        <v>0.01</v>
+        <v>0.099</v>
       </c>
       <c r="J120">
         <v>0.134</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -9508,21 +9508,21 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>SE11</t>
+          <t>DEB3</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Stockholm</t>
+          <t>Rheinhessen-Pfalz</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="G121">
-        <v>0.048</v>
+        <v>0.1</v>
       </c>
       <c r="H121" t="inlineStr">
         <is>
@@ -9530,14 +9530,14 @@
         </is>
       </c>
       <c r="I121">
-        <v>0.01</v>
+        <v>0.099</v>
       </c>
       <c r="J121">
-        <v>0.136</v>
+        <v>0.149</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>Vulnerability-driven</t>
+          <t>Balanced</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -9547,23 +9547,23 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="N121">
         <v>0</v>
       </c>
       <c r="O121">
-        <v>15262</v>
+        <v>19792</v>
       </c>
       <c r="P121">
-        <v>19.28</v>
+        <v>20.31</v>
       </c>
       <c r="Q121">
-        <v>3.19</v>
+        <v>35.41</v>
       </c>
       <c r="R121">
-        <v>452048.49</v>
+        <v>811071.84</v>
       </c>
     </row>
   </sheetData>
